--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.5%</t>
+          <t>-149.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-180.9%</t>
+          <t>-181.0%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-27.0%</t>
         </is>
       </c>
     </row>
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.824942797582457</v>
+        <v>-4.825487912358348</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.002292753516324</v>
+        <v>2.002074707605968</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.4304809165993803</v>
+        <v>0.42993580182349</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.190914846822683</v>
+        <v>4.190587777957149</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>424.9%</t>
+          <t>425.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.1%</t>
+          <t>-636.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.0%</t>
+          <t>-173.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.6%</t>
+          <t>-143.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-181.0%</t>
+          <t>-173.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-22.6%</t>
         </is>
       </c>
     </row>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82805292879205</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279189</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.78093391139299</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632784</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883077</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242297</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496266</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577003</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942109</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767452</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003606</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508374</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417709</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205904</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264171</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742308</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803199</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809506</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.108086654605097</v>
+        <v>-4.035935555608145</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.135320754105625</v>
+        <v>1.164181193704406</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4927100574034022</v>
+        <v>0.5648611564003547</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.074537874703454</v>
+        <v>3.117828534101625</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798544</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.995709653422425</v>
+        <v>-3.923558554425472</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.185762850409362</v>
+        <v>1.214623290008143</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4927100574034022</v>
+        <v>0.5648611564003547</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.080029170534121</v>
+        <v>3.123319829932293</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498872</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.023490051323778</v>
+        <v>-3.951338952326825</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.186147893017359</v>
+        <v>1.21500833261614</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4649296595020492</v>
+        <v>0.5370807584990016</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.074858133561849</v>
+        <v>3.11814879296002</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705329</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.141870724053916</v>
+        <v>-4.069719625056964</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9771513439259574</v>
+        <v>1.006011783524738</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.397711807351073</v>
+        <v>0.4698629063480254</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.872883142271916</v>
+        <v>2.916173801670087</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729276</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.250484802497247</v>
+        <v>-4.178333703500295</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.053855373267831</v>
+        <v>1.082715812866612</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.397711807351073</v>
+        <v>0.4698629063480254</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.993032802991122</v>
+        <v>3.036323462389293</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190775</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.215075764249105</v>
+        <v>-4.142924665252152</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082532014669411</v>
+        <v>1.111392454268192</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.397711807351073</v>
+        <v>0.4698629063480254</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.007545829093444</v>
+        <v>3.050836488491616</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.176692101690954</v>
+        <v>-4.104541002694001</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.09530492103504</v>
+        <v>1.124165360633821</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4360954699092242</v>
+        <v>0.5082465689061766</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.027995467970704</v>
+        <v>3.071286127368876</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532493</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.999575771655787</v>
+        <v>-3.927424672658835</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.162880481894408</v>
+        <v>1.191740921493189</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4360954699092242</v>
+        <v>0.5082465689061766</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.024724496816006</v>
+        <v>3.068015156214178</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793911</v>
+        <v>3.741328448793907</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.044668016489333</v>
+        <v>-3.97251691749238</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145526975722903</v>
+        <v>1.174387415321684</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3741994267398344</v>
+        <v>0.4463505257367868</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.988270262676285</v>
+        <v>3.031560922074457</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.865292595250565</v>
+        <v>-3.793141496253613</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.211064119524824</v>
+        <v>1.239924559123605</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.530976184910553</v>
+        <v>0.6031272839075055</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.076123292885131</v>
+        <v>3.119413952283302</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982236</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.910306808771172</v>
+        <v>-3.838155709774219</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.173865889448172</v>
+        <v>1.202726329046953</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5006272895959484</v>
+        <v>0.5727783885929009</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.038721411027958</v>
+        <v>3.082012070426129</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509543</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.177311319043607</v>
+        <v>-4.105160220046654</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.072755647678143</v>
+        <v>1.101616087276924</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3062642515529998</v>
+        <v>0.3784153505499523</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.927795150541134</v>
+        <v>2.971085809939306</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.27850910048078</v>
+        <v>-4.206358001483827</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031480456999776</v>
+        <v>1.060340896598557</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2378554380076806</v>
+        <v>0.3100065370046331</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.885953784310444</v>
+        <v>2.929244443708616</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815463</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.271998133866467</v>
+        <v>-4.199847034869514</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.031684805199817</v>
+        <v>1.060545244798599</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2378554380076806</v>
+        <v>0.3100065370046331</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.883553745864761</v>
+        <v>2.926844405262933</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.25296000615917</v>
+        <v>-4.180808907162217</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.035824775490981</v>
+        <v>1.064685215089762</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1796718266764861</v>
+        <v>0.2518229256734386</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.845168298274289</v>
+        <v>2.88845895767246</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131257</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.30547580843399</v>
+        <v>-4.233324709437038</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.134112856215243</v>
+        <v>1.162973295814024</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1796718266764861</v>
+        <v>0.2518229256734386</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.964462699908479</v>
+        <v>3.007753359306651</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.319342569767908</v>
+        <v>-4.247191470770955</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.12939948066781</v>
+        <v>1.158259920266591</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1418139099426631</v>
+        <v>0.2139650089396156</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.942581278854319</v>
+        <v>2.985871938252491</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789128</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.274538398227978</v>
+        <v>-4.202387299231026</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.153329679680708</v>
+        <v>1.182190119279489</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1418139099426631</v>
+        <v>0.2139650089396156</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.948589809251245</v>
+        <v>2.991880468649417</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.126795427992976</v>
+        <v>-4.054644328996023</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.110377089051908</v>
+        <v>1.139237528650689</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3096212671775463</v>
+        <v>0.3817723661744988</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.947224444869375</v>
+        <v>2.990515104267546</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.210616649267674</v>
+        <v>-4.138465550270721</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.07964222207351</v>
+        <v>1.108502661672291</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3096212671775463</v>
+        <v>0.3817723661744988</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.950018066400856</v>
+        <v>2.993308725799027</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394736</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.20446394321489</v>
+        <v>-4.132312844217937</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.082765652886282</v>
+        <v>1.111626092485063</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3157739732303306</v>
+        <v>0.3879250722272831</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.954372038424184</v>
+        <v>2.997662697822356</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890618</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.221273241365392</v>
+        <v>-4.149122142368439</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.075122410366191</v>
+        <v>1.103982849964972</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2989646750798289</v>
+        <v>0.3711157740767814</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.943366936273994</v>
+        <v>2.986657595672165</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798433</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.158975242589269</v>
+        <v>-4.086824143592317</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.166377163673461</v>
+        <v>1.195237603272242</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.344258939354271</v>
+        <v>0.4164100383512235</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.03687904863548</v>
+        <v>3.080169708033651</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992198</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.957185044924111</v>
+        <v>-3.885033945927159</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.049385244453652</v>
+        <v>1.078245684052433</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5422771315234254</v>
+        <v>0.6144282305203779</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.9579819656511</v>
+        <v>3.001272625049271</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.008071757610306</v>
+        <v>-3.935920658613353</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.099320791701349</v>
+        <v>1.12818123130013</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4913904188372309</v>
+        <v>0.5635415178341834</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.997740170361558</v>
+        <v>3.041030829759729</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319551</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.921461014960499</v>
+        <v>-3.849309915963546</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.148592824877315</v>
+        <v>1.177453264476096</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5700161500423891</v>
+        <v>0.6421672490393416</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.059543345200697</v>
+        <v>3.102834004598868</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489391</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.981670312965783</v>
+        <v>-3.909519213968831</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.123045086499873</v>
+        <v>1.151905526098654</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5098068520371046</v>
+        <v>0.5819579510340571</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.021953747222198</v>
+        <v>3.065244406620369</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.905248266533857</v>
+        <v>-3.833097167536904</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.152105523112573</v>
+        <v>1.180965962711354</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5098068520371046</v>
+        <v>0.5819579510340571</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.020445365262126</v>
+        <v>3.063736024660298</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316255</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.860875134895288</v>
+        <v>-3.788724035898335</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.169717643203436</v>
+        <v>1.198578082802217</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5541799836756732</v>
+        <v>0.6263310826726257</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.046932111680703</v>
+        <v>3.090222771078875</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105973</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.883355485754173</v>
+        <v>-3.81120438675722</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.155119296998473</v>
+        <v>1.183979736597254</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5541799836756732</v>
+        <v>0.6263310826726257</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.041325905819294</v>
+        <v>3.084616565217465</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190331</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.835699755193117</v>
+        <v>-3.763548656196164</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.1805633462507</v>
+        <v>1.209423785849481</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6018357142367289</v>
+        <v>0.6739868132336814</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.076301101183732</v>
+        <v>3.119591760581903</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569624</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.735181596694362</v>
+        <v>-3.66303049769741</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.225662983024926</v>
+        <v>1.254523422623707</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7023538727354834</v>
+        <v>0.7745049717324359</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.14150436965771</v>
+        <v>3.184795029055881</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.8288088775573</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.71927626726201</v>
+        <v>-3.647125168265057</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.21877978727374</v>
+        <v>1.247640226872521</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6232412120262445</v>
+        <v>0.695392311023197</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.080791445708039</v>
+        <v>3.12408210510621</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932775</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.674437865653612</v>
+        <v>-3.602286766656659</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.240812850527727</v>
+        <v>1.269673290126509</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.627784644971114</v>
+        <v>0.6999357439680665</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.087615208085589</v>
+        <v>3.13090586748376</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.817932354917055</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.69393632189562</v>
+        <v>-3.621785222898667</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.237174407662002</v>
+        <v>1.266034847260783</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5797000036912097</v>
+        <v>0.6518511026881622</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.062925362948724</v>
+        <v>3.106216022346896</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405966</v>
+        <v>3.826684745405963</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.649733484809719</v>
+        <v>-3.577582385812767</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.260735145024199</v>
+        <v>1.289595584622981</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6239028407771101</v>
+        <v>0.6960539397740626</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.095326667728102</v>
+        <v>3.138617327126273</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265648</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.686712512473163</v>
+        <v>-3.61456141347621</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.24435353442807</v>
+        <v>1.273213974026851</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6608767425684406</v>
+        <v>0.7330278415653931</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.115921009272148</v>
+        <v>3.159211668670319</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284886</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.52842109493389</v>
+        <v>-3.456269995936938</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.358917866626818</v>
+        <v>1.3877783062256</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6608767425684406</v>
+        <v>0.7330278415653931</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.167168774455187</v>
+        <v>3.210459433853359</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321028</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.320779091299414</v>
+        <v>-3.248627992302461</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.440415372674862</v>
+        <v>1.469275812273643</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8685187462029168</v>
+        <v>0.9406698451998693</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.290194681230126</v>
+        <v>3.333485340628298</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475145</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.269746998576886</v>
+        <v>-3.197595899579933</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.455776438002143</v>
+        <v>1.484636877600924</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9195508389254448</v>
+        <v>0.9917019379223972</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.315762165101913</v>
+        <v>3.359052824500084</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404859</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.20452281744968</v>
+        <v>-3.132371718452728</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.49905351454573</v>
+        <v>1.527913954144511</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9847750200526504</v>
+        <v>1.056926119049603</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.372084077870941</v>
+        <v>3.415374737269112</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882563</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.167095797378547</v>
+        <v>-3.094944698381594</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.509985294873464</v>
+        <v>1.538845734472245</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9900265580818322</v>
+        <v>1.062177657078784</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.371195972987731</v>
+        <v>3.414486632385902</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992666</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.187207453413255</v>
+        <v>-3.115056354416302</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.503197424790821</v>
+        <v>1.532057864389602</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.001053903079251</v>
+        <v>1.073205002076204</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.379069172317422</v>
+        <v>3.422359831715593</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636293</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.13346263898605</v>
+        <v>-3.061311539989097</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.685253121582914</v>
+        <v>1.714113561181695</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.011117212519713</v>
+        <v>1.083268311516666</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.54566492900291</v>
+        <v>3.588955588401082</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957631</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.058680377961037</v>
+        <v>-2.986529278964085</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.835278935210736</v>
+        <v>1.864139374809517</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.085899473544726</v>
+        <v>1.158050572541678</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.710647194835735</v>
+        <v>3.753937854233906</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998761</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.032596293697229</v>
+        <v>-2.960445194700277</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.837420544930118</v>
+        <v>1.866280984528899</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.085899473544726</v>
+        <v>1.158050572541678</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.702355170849594</v>
+        <v>3.745645830247765</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896935</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.944718380588109</v>
+        <v>-2.872567281591156</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.870764905757546</v>
+        <v>1.899625345356327</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.201825115968077</v>
+        <v>1.27397621496503</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.770103751887384</v>
+        <v>3.813394411285556</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.935825919194825</v>
+        <v>-2.863674820197873</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.891876296041651</v>
+        <v>1.920736735640432</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.201825115968077</v>
+        <v>1.27397621496503</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.787658157614175</v>
+        <v>3.830948817012347</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945371</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.104302036164703</v>
+        <v>-3.032150937167751</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.816340896658284</v>
+        <v>1.845201336257065</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.173877280251497</v>
+        <v>1.246028379248449</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.762744503588811</v>
+        <v>3.806035162986983</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782713</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.40650250730312</v>
+        <v>-2.334351408306167</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.076730405390779</v>
+        <v>2.10559084498956</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.103529220881086</v>
+        <v>1.175680319878038</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.701805365154426</v>
+        <v>3.745096024552598</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632641</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.383781403619968</v>
+        <v>-2.311630304623015</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.076482869360945</v>
+        <v>2.105343308959725</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.103529220881086</v>
+        <v>1.175680319878038</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.692469387651331</v>
+        <v>3.735760047049502</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777678</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.51298321691401</v>
+        <v>-2.440832117917057</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.183708269894496</v>
+        <v>2.212568709493278</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9743274075870436</v>
+        <v>1.046478506583996</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.773854425526075</v>
+        <v>3.817145084924246</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644417</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.667764223692266</v>
+        <v>-2.595613124695313</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.158873689676841</v>
+        <v>2.187734129275622</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9409597335325675</v>
+        <v>1.01311083252952</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.790911643587036</v>
+        <v>3.834202302985207</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.660709533477092</v>
+        <v>-2.588558434480139</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.158370921752455</v>
+        <v>2.187231361351237</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9480144237477413</v>
+        <v>1.020165522744694</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.791819813705685</v>
+        <v>3.835110473103856</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331121</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.633758309150604</v>
+        <v>-2.561607210153651</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.179157565127792</v>
+        <v>2.208018004726573</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9628947697754604</v>
+        <v>1.035045868772413</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.810754174967058</v>
+        <v>3.854044834365229</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784113</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.76971131720692</v>
+        <v>-2.697560218209968</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.308879494050225</v>
+        <v>2.337739933649006</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9628947697754604</v>
+        <v>1.035045868772413</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.994857307112018</v>
+        <v>4.03814796651019</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.792119435011792</v>
+        <v>-2.71996833601484</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.29203294183127</v>
+        <v>2.320893381430051</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9628947697754604</v>
+        <v>1.035045868772413</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.986974002015011</v>
+        <v>4.030264661413183</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155037</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.820343670589393</v>
+        <v>-2.74819257159244</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.282797247149867</v>
+        <v>2.311657686748648</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.980871522226769</v>
+        <v>1.053022621223721</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999814053035434</v>
+        <v>4.043104712433605</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161982</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.829784596477923</v>
+        <v>-2.75763349748097</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.335274594516302</v>
+        <v>2.364135034115083</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.103298639770161</v>
+        <v>1.175449738767113</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.129524041283315</v>
+        <v>4.172814700681487</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321639</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.882058203813564</v>
+        <v>-2.809907104816611</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.317256246127346</v>
+        <v>2.346116685726128</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.051025032434519</v>
+        <v>1.123176131431471</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.101050971427232</v>
+        <v>4.144341630825403</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347709</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.95838818141447</v>
+        <v>-2.886237082417517</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.284836067980759</v>
+        <v>2.31369650757954</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.051025032434519</v>
+        <v>1.123176131431471</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.099162784321007</v>
+        <v>4.142453443719178</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.160641901738823</v>
+        <v>-3.08849080274187</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.19875480945388</v>
+        <v>2.227615249052661</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8487713121101657</v>
+        <v>0.9209224111071179</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.972630781729257</v>
+        <v>4.015921441127428</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234307</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.322210327266078</v>
+        <v>-3.250059228269126</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.132561449453131</v>
+        <v>2.161421889051911</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7219883883122863</v>
+        <v>0.7941394873092386</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.894995037660682</v>
+        <v>3.938285697058853</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389353</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.454511619363632</v>
+        <v>-3.382360520366679</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.092714339480028</v>
+        <v>2.121574779078809</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7219883883122863</v>
+        <v>0.7941394873092386</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.908068444526601</v>
+        <v>3.951359103924772</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378396</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.640379930202862</v>
+        <v>-3.568228831205909</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.010372211927276</v>
+        <v>2.039232651526057</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5634227949923386</v>
+        <v>0.6355738939892909</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.804934285317572</v>
+        <v>3.848224944715743</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.668280717312335</v>
+        <v>-3.596129618315382</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.997735938210488</v>
+        <v>2.02659637780927</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5288258708494038</v>
+        <v>0.6009769698463561</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.782700171958813</v>
+        <v>3.825990831356984</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.790806820015229</v>
+        <v>-3.718655721018276</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.94548994110653</v>
+        <v>1.974350380705311</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4062997681465099</v>
+        <v>0.4784508671434622</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.705948954314275</v>
+        <v>3.749239613712447</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585941</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.021321316200817</v>
+        <v>-3.949170217203864</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.919990102222798</v>
+        <v>1.948850541821579</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1757852719609212</v>
+        <v>0.2479363709578735</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.634346216193426</v>
+        <v>3.677636875591597</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.278042134195641</v>
+        <v>-4.205891035198688</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.957613494026716</v>
+        <v>1.986473933625497</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1395217968140586</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.709609190708984</v>
+        <v>3.752899850107156</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237098</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.432028551971781</v>
+        <v>-4.359877452974828</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.964999196061899</v>
+        <v>1.99385963566068</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1395217968140586</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.778589459854624</v>
+        <v>3.821880119252795</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423391</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.381506648144115</v>
+        <v>-4.309355549147162</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.971259159713087</v>
+        <v>2.000119599311867</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1395217968140586</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.764640661974745</v>
+        <v>3.807931321372916</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.63398180215184</v>
+        <v>-4.561830703154887</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.882139587165411</v>
+        <v>1.911000026764192</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1395217968140586</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.776511151030159</v>
+        <v>3.81980181042833</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.926877558631252</v>
+        <v>-4.854726459634299</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.76619181909259</v>
+        <v>1.795052258691371</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1395217968140586</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.777721685549102</v>
+        <v>3.821012344947274</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251949</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.084421630360693</v>
+        <v>-5.012270531363741</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.707295932628135</v>
+        <v>1.736156372226915</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.0004688926768318669</v>
+        <v>0.07261999167378413</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.741702344692259</v>
+        <v>3.78499300409043</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.362386025943967</v>
+        <v>-5.290234926947014</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.591188027131015</v>
+        <v>1.620048466729795</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.08915084160865239</v>
+        <v>-0.01699974261170012</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.683008356857158</v>
+        <v>3.72629901625533</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.479353718582858</v>
+        <v>-5.407202619585905</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.706605006774502</v>
+        <v>1.735465446373283</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.08915084160865239</v>
+        <v>-0.01699974261170012</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.845212413556202</v>
+        <v>3.888503072954373</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.564071660803811</v>
+        <v>-5.491920561806858</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.667564467849935</v>
+        <v>1.696424907448716</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1742668705366988</v>
+        <v>-0.1021157715397465</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.788989434163188</v>
+        <v>3.83228009356136</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586815</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.646006479072694</v>
+        <v>-5.573855380075742</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.645019958110873</v>
+        <v>1.673880397709654</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1842016161237789</v>
+        <v>-0.1120505171268267</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.793258004379431</v>
+        <v>3.836548663777603</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.747982601321102</v>
+        <v>-5.675831502324149</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.613155147667412</v>
+        <v>1.642015587266193</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2861777383721865</v>
+        <v>-0.2140266393752343</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.740997969486289</v>
+        <v>3.784288628884461</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.63797631784388</v>
+        <v>-5.565825218846927</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.649310548302476</v>
+        <v>1.678170987901257</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2629731664549113</v>
+        <v>-0.190822067457959</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.74707359988083</v>
+        <v>3.790364259279001</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818526</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.494916742102955</v>
+        <v>-5.422765643106002</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.710784389320821</v>
+        <v>1.739644828919602</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.254959739864932</v>
+        <v>-0.1828086408679798</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.756131666556792</v>
+        <v>3.799422325954963</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051791</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.193470016631117</v>
+        <v>-5.121318917634165</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.838623962392092</v>
+        <v>1.867484401990873</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.1186380846038575</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.94426058472243</v>
+        <v>3.987551244120602</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067963</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.218060260866301</v>
+        <v>-5.145909161869349</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.829759042450729</v>
+        <v>1.85861948204951</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.1186380846038575</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.945231762475141</v>
+        <v>3.988522421873312</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.167021884859781</v>
+        <v>-5.094870785862828</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.851017297233092</v>
+        <v>1.879877736831873</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.1186380846038575</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.946074666854896</v>
+        <v>3.989365326253068</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969547</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.12588258999315</v>
+        <v>-5.053731490996197</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.88651111405389</v>
+        <v>1.915371553652671</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.08762628047353604</v>
+        <v>0.1597773794704883</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.98979634264902</v>
+        <v>4.033087002047191</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700483</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.015276449913548</v>
+        <v>-4.943125350916596</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.746937566209665</v>
+        <v>1.775798005808446</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1982324205531381</v>
+        <v>0.2703835195500903</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.872344022820716</v>
+        <v>3.915634682218887</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077645</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.145857184444391</v>
+        <v>-5.073706085447438</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.698207316471292</v>
+        <v>1.727067756070073</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.1398027850192478</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.797497626176173</v>
+        <v>3.840788285574345</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.981360850253429</v>
+        <v>-4.909209751256476</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.748432669223759</v>
+        <v>1.77729310882254</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.1398027850192478</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781924445252256</v>
+        <v>3.825215104650427</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077631</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.008730782937861</v>
+        <v>-4.936579683940908</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.736672406586416</v>
+        <v>1.765532846185197</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.1398027850192478</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.781112155688686</v>
+        <v>3.824402815086857</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.019115977827751</v>
+        <v>-4.946964878830798</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.742387107755532</v>
+        <v>1.771247547354314</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.05726649113240623</v>
+        <v>0.1294175901293585</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784749817879825</v>
+        <v>3.828040477277996</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735286</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.037704136549976</v>
+        <v>-4.965553037553023</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.805788850043068</v>
+        <v>1.834649289641849</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.03867833241018087</v>
+        <v>0.1108294314071331</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.844433928422915</v>
+        <v>3.887724587821086</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.038002683246011</v>
+        <v>-4.965851584249059</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.802538442182952</v>
+        <v>1.831398881781733</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.03867833241018087</v>
+        <v>0.1108294314071331</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.841302939241213</v>
+        <v>3.884593598639384</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108861</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.937179549555584</v>
+        <v>-4.865028450558631</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.847398590598514</v>
+        <v>1.876259030197295</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.05114254789453471</v>
+        <v>0.123293646891487</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.853312363471217</v>
+        <v>3.896603022869388</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812147</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.746398188803177</v>
+        <v>-4.674247089806224</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.923840388378021</v>
+        <v>1.952700827976801</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2419239086469421</v>
+        <v>0.3140750076438943</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.967910433401205</v>
+        <v>4.011201092799376</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906083</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.727881334761356</v>
+        <v>-4.655730235764404</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.911083975732345</v>
+        <v>1.939944415331126</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2548540380721503</v>
+        <v>0.3270051370691026</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.955505356793926</v>
+        <v>3.998796016192098</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912988</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.702688150260038</v>
+        <v>-4.630537051263086</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.956128186144931</v>
+        <v>1.984988625743712</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2800472225734686</v>
+        <v>0.3521983215704209</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.005588204106775</v>
+        <v>4.048878863504947</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539897</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.690634023347076</v>
+        <v>-4.618482924350123</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.954636404811554</v>
+        <v>1.983496844410335</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2921013494864315</v>
+        <v>0.3642524484833837</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.006507248155991</v>
+        <v>4.049797907554162</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.697257270037434</v>
+        <v>-4.625106171040481</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.953867736319546</v>
+        <v>1.982728175918327</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.2854781027960731</v>
+        <v>0.3576292017930254</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.004413930325912</v>
+        <v>4.047704589724083</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.594376680508841</v>
+        <v>-4.522225581511888</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.007870998008866</v>
+        <v>2.036731437607647</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4605097913216183</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.07899330992095</v>
+        <v>4.122283969319121</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760318</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.617818719688928</v>
+        <v>-4.545667620691975</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.018696852510425</v>
+        <v>2.047557292109206</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4605097913216183</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.099195980094544</v>
+        <v>4.142486639492716</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781708</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.635891227980539</v>
+        <v>-4.563740128983587</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.011467849193781</v>
+        <v>2.040328288792562</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4605097913216183</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.099195980094544</v>
+        <v>4.142486639492716</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082837</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.867065021857171</v>
+        <v>-4.794913922860219</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.879250245236594</v>
+        <v>1.908110684835375</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4605097913216183</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.059447893688011</v>
+        <v>4.102738553086183</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.835779001316716</v>
+        <v>-4.763627902319763</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.898787272449717</v>
+        <v>1.927647712048498</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4196447128651214</v>
+        <v>0.4917958118620737</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.085242125009224</v>
+        <v>4.128532784407396</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.836108583773318</v>
+        <v>3.843046999204358</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.825487912358348</v>
+        <v>-4.752266344484506</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.002074707605968</v>
+        <v>2.031363334755504</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.42993580182349</v>
+        <v>0.5031573696973306</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.190587777957149</v>
+        <v>4.234520718681454</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>425.1%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.8%</t>
+          <t>-644.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-173.1%</t>
+          <t>-176.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-143.2%</t>
+          <t>-151.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-173.7%</t>
+          <t>-180.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-26.9%</t>
         </is>
       </c>
     </row>
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.035935555608145</v>
+        <v>-4.108086654605097</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.164181193704406</v>
+        <v>1.135320754105625</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5648611564003547</v>
+        <v>0.4927100574034022</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.117828534101625</v>
+        <v>3.074537874703454</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.923558554425472</v>
+        <v>-3.995709653422425</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.214623290008143</v>
+        <v>1.185762850409362</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5648611564003547</v>
+        <v>0.4927100574034022</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.123319829932293</v>
+        <v>3.080029170534121</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.951338952326825</v>
+        <v>-4.023490051323778</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.21500833261614</v>
+        <v>1.186147893017359</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5370807584990016</v>
+        <v>0.4649296595020492</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.11814879296002</v>
+        <v>3.074858133561849</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.069719625056964</v>
+        <v>-4.141870724053916</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.006011783524738</v>
+        <v>0.9771513439259574</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4698629063480254</v>
+        <v>0.397711807351073</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.916173801670087</v>
+        <v>2.872883142271916</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.178333703500295</v>
+        <v>-4.250484802497247</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.082715812866612</v>
+        <v>1.053855373267831</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4698629063480254</v>
+        <v>0.397711807351073</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.036323462389293</v>
+        <v>2.993032802991122</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.142924665252152</v>
+        <v>-4.215075764249105</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.111392454268192</v>
+        <v>1.082532014669411</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4698629063480254</v>
+        <v>0.397711807351073</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.050836488491616</v>
+        <v>3.007545829093444</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.104541002694001</v>
+        <v>-4.176692101690954</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.124165360633821</v>
+        <v>1.09530492103504</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5082465689061766</v>
+        <v>0.4360954699092242</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.071286127368876</v>
+        <v>3.027995467970704</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.927424672658835</v>
+        <v>-3.999575771655787</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.191740921493189</v>
+        <v>1.162880481894408</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5082465689061766</v>
+        <v>0.4360954699092242</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.068015156214178</v>
+        <v>3.024724496816006</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.97251691749238</v>
+        <v>-4.044668016489333</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.174387415321684</v>
+        <v>1.145526975722903</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4463505257367868</v>
+        <v>0.3741994267398344</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.031560922074457</v>
+        <v>2.988270262676285</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.793141496253613</v>
+        <v>-3.865292595250565</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.239924559123605</v>
+        <v>1.211064119524824</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6031272839075055</v>
+        <v>0.530976184910553</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.119413952283302</v>
+        <v>3.076123292885131</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.838155709774219</v>
+        <v>-3.910306808771172</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.202726329046953</v>
+        <v>1.173865889448172</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5727783885929009</v>
+        <v>0.5006272895959484</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.082012070426129</v>
+        <v>3.038721411027958</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.105160220046654</v>
+        <v>-4.177311319043607</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.101616087276924</v>
+        <v>1.072755647678143</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3784153505499523</v>
+        <v>0.3062642515529998</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.971085809939306</v>
+        <v>2.927795150541134</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.206358001483827</v>
+        <v>-4.27850910048078</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.060340896598557</v>
+        <v>1.031480456999776</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3100065370046331</v>
+        <v>0.2378554380076806</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.929244443708616</v>
+        <v>2.885953784310444</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.199847034869514</v>
+        <v>-4.271998133866467</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.060545244798599</v>
+        <v>1.031684805199817</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3100065370046331</v>
+        <v>0.2378554380076806</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.926844405262933</v>
+        <v>2.883553745864761</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.180808907162217</v>
+        <v>-4.25296000615917</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.064685215089762</v>
+        <v>1.035824775490981</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2518229256734386</v>
+        <v>0.1796718266764861</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.88845895767246</v>
+        <v>2.845168298274289</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.233324709437038</v>
+        <v>-4.30547580843399</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.162973295814024</v>
+        <v>1.134112856215243</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2518229256734386</v>
+        <v>0.1796718266764861</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.007753359306651</v>
+        <v>2.964462699908479</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.247191470770955</v>
+        <v>-4.319342569767908</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.158259920266591</v>
+        <v>1.12939948066781</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2139650089396156</v>
+        <v>0.1418139099426631</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.985871938252491</v>
+        <v>2.942581278854319</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.202387299231026</v>
+        <v>-4.274538398227978</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.182190119279489</v>
+        <v>1.153329679680708</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2139650089396156</v>
+        <v>0.1418139099426631</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.991880468649417</v>
+        <v>2.948589809251245</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.054644328996023</v>
+        <v>-4.126795427992976</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.139237528650689</v>
+        <v>1.110377089051908</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3817723661744988</v>
+        <v>0.3096212671775463</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.990515104267546</v>
+        <v>2.947224444869375</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.138465550270721</v>
+        <v>-4.210616649267674</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.108502661672291</v>
+        <v>1.07964222207351</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3817723661744988</v>
+        <v>0.3096212671775463</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.993308725799027</v>
+        <v>2.950018066400856</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.132312844217937</v>
+        <v>-4.20446394321489</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.111626092485063</v>
+        <v>1.082765652886282</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3879250722272831</v>
+        <v>0.3157739732303306</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.997662697822356</v>
+        <v>2.954372038424184</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.149122142368439</v>
+        <v>-4.221273241365392</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.103982849964972</v>
+        <v>1.075122410366191</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3711157740767814</v>
+        <v>0.2989646750798289</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.986657595672165</v>
+        <v>2.943366936273994</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.086824143592317</v>
+        <v>-4.158975242589269</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.195237603272242</v>
+        <v>1.166377163673461</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4164100383512235</v>
+        <v>0.344258939354271</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.080169708033651</v>
+        <v>3.03687904863548</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.885033945927159</v>
+        <v>-3.957185044924111</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.078245684052433</v>
+        <v>1.049385244453652</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6144282305203779</v>
+        <v>0.5422771315234254</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.001272625049271</v>
+        <v>2.9579819656511</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.935920658613353</v>
+        <v>-4.008071757610306</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.12818123130013</v>
+        <v>1.099320791701349</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5635415178341834</v>
+        <v>0.4913904188372309</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.041030829759729</v>
+        <v>2.997740170361558</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.849309915963546</v>
+        <v>-3.921461014960499</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.177453264476096</v>
+        <v>1.148592824877315</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6421672490393416</v>
+        <v>0.5700161500423891</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.102834004598868</v>
+        <v>3.059543345200697</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.909519213968831</v>
+        <v>-3.981670312965783</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.151905526098654</v>
+        <v>1.123045086499873</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5819579510340571</v>
+        <v>0.5098068520371046</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.065244406620369</v>
+        <v>3.021953747222198</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.833097167536904</v>
+        <v>-3.905248266533857</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.180965962711354</v>
+        <v>1.152105523112573</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5819579510340571</v>
+        <v>0.5098068520371046</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.063736024660298</v>
+        <v>3.020445365262126</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.788724035898335</v>
+        <v>-3.860875134895288</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.198578082802217</v>
+        <v>1.169717643203436</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6263310826726257</v>
+        <v>0.5541799836756732</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.090222771078875</v>
+        <v>3.046932111680703</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.81120438675722</v>
+        <v>-3.883355485754173</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.183979736597254</v>
+        <v>1.155119296998473</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6263310826726257</v>
+        <v>0.5541799836756732</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.084616565217465</v>
+        <v>3.041325905819294</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.763548656196164</v>
+        <v>-3.835699755193117</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.209423785849481</v>
+        <v>1.1805633462507</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6739868132336814</v>
+        <v>0.6018357142367289</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.119591760581903</v>
+        <v>3.076301101183732</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.66303049769741</v>
+        <v>-3.735181596694362</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.254523422623707</v>
+        <v>1.225662983024926</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7745049717324359</v>
+        <v>0.7023538727354834</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.184795029055881</v>
+        <v>3.14150436965771</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.647125168265057</v>
+        <v>-3.71927626726201</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.247640226872521</v>
+        <v>1.21877978727374</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.695392311023197</v>
+        <v>0.6232412120262445</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.12408210510621</v>
+        <v>3.080791445708039</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.602286766656659</v>
+        <v>-3.674437865653612</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.269673290126509</v>
+        <v>1.240812850527727</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6999357439680665</v>
+        <v>0.627784644971114</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.13090586748376</v>
+        <v>3.087615208085589</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.621785222898667</v>
+        <v>-3.69393632189562</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.266034847260783</v>
+        <v>1.237174407662002</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6518511026881622</v>
+        <v>0.5797000036912097</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.106216022346896</v>
+        <v>3.062925362948724</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.577582385812767</v>
+        <v>-3.649733484809719</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.289595584622981</v>
+        <v>1.260735145024199</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6960539397740626</v>
+        <v>0.6239028407771101</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.138617327126273</v>
+        <v>3.095326667728102</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.61456141347621</v>
+        <v>-3.686712512473163</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.273213974026851</v>
+        <v>1.24435353442807</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7330278415653931</v>
+        <v>0.6608767425684406</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.159211668670319</v>
+        <v>3.115921009272148</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.456269995936938</v>
+        <v>-3.52842109493389</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.3877783062256</v>
+        <v>1.358917866626818</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7330278415653931</v>
+        <v>0.6608767425684406</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.210459433853359</v>
+        <v>3.167168774455187</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.248627992302461</v>
+        <v>-3.320779091299414</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.469275812273643</v>
+        <v>1.440415372674862</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9406698451998693</v>
+        <v>0.8685187462029168</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.333485340628298</v>
+        <v>3.290194681230126</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.197595899579933</v>
+        <v>-3.269746998576886</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.484636877600924</v>
+        <v>1.455776438002143</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9917019379223972</v>
+        <v>0.9195508389254448</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.359052824500084</v>
+        <v>3.315762165101913</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.132371718452728</v>
+        <v>-3.20452281744968</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.527913954144511</v>
+        <v>1.49905351454573</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.056926119049603</v>
+        <v>0.9847750200526504</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.415374737269112</v>
+        <v>3.372084077870941</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.094944698381594</v>
+        <v>-3.167095797378547</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.538845734472245</v>
+        <v>1.509985294873464</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.062177657078784</v>
+        <v>0.9900265580818322</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.414486632385902</v>
+        <v>3.371195972987731</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.115056354416302</v>
+        <v>-3.187207453413255</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.532057864389602</v>
+        <v>1.503197424790821</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.073205002076204</v>
+        <v>1.001053903079251</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.422359831715593</v>
+        <v>3.379069172317422</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.061311539989097</v>
+        <v>-3.13346263898605</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.714113561181695</v>
+        <v>1.685253121582914</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.083268311516666</v>
+        <v>1.011117212519713</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.588955588401082</v>
+        <v>3.54566492900291</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.986529278964085</v>
+        <v>-3.058680377961037</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.864139374809517</v>
+        <v>1.835278935210736</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.158050572541678</v>
+        <v>1.085899473544726</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.753937854233906</v>
+        <v>3.710647194835735</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.960445194700277</v>
+        <v>-3.032596293697229</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.866280984528899</v>
+        <v>1.837420544930118</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.158050572541678</v>
+        <v>1.085899473544726</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.745645830247765</v>
+        <v>3.702355170849594</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.872567281591156</v>
+        <v>-2.944718380588109</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.899625345356327</v>
+        <v>1.870764905757546</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.27397621496503</v>
+        <v>1.201825115968077</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.813394411285556</v>
+        <v>3.770103751887384</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.863674820197873</v>
+        <v>-2.935825919194825</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.920736735640432</v>
+        <v>1.891876296041651</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.27397621496503</v>
+        <v>1.201825115968077</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.830948817012347</v>
+        <v>3.787658157614175</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.032150937167751</v>
+        <v>-3.104302036164703</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.845201336257065</v>
+        <v>1.816340896658284</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.246028379248449</v>
+        <v>1.173877280251497</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.806035162986983</v>
+        <v>3.762744503588811</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.334351408306167</v>
+        <v>-2.40650250730312</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.10559084498956</v>
+        <v>2.076730405390779</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.175680319878038</v>
+        <v>1.103529220881086</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.745096024552598</v>
+        <v>3.701805365154426</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.311630304623015</v>
+        <v>-2.383781403619968</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.105343308959725</v>
+        <v>2.076482869360945</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.175680319878038</v>
+        <v>1.103529220881086</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.735760047049502</v>
+        <v>3.692469387651331</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.440832117917057</v>
+        <v>-2.51298321691401</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.212568709493278</v>
+        <v>2.183708269894496</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.046478506583996</v>
+        <v>0.9743274075870436</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.817145084924246</v>
+        <v>3.773854425526075</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.595613124695313</v>
+        <v>-2.667764223692266</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.187734129275622</v>
+        <v>2.158873689676841</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.01311083252952</v>
+        <v>0.9409597335325675</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.834202302985207</v>
+        <v>3.790911643587036</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.588558434480139</v>
+        <v>-2.660709533477092</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.187231361351237</v>
+        <v>2.158370921752455</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.020165522744694</v>
+        <v>0.9480144237477413</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.835110473103856</v>
+        <v>3.791819813705685</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.561607210153651</v>
+        <v>-2.633758309150604</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.208018004726573</v>
+        <v>2.179157565127792</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.035045868772413</v>
+        <v>0.9628947697754604</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.854044834365229</v>
+        <v>3.810754174967058</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.697560218209968</v>
+        <v>-2.76971131720692</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.337739933649006</v>
+        <v>2.308879494050225</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.035045868772413</v>
+        <v>0.9628947697754604</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.03814796651019</v>
+        <v>3.994857307112018</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.71996833601484</v>
+        <v>-2.792119435011792</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.320893381430051</v>
+        <v>2.29203294183127</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.035045868772413</v>
+        <v>0.9628947697754604</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.030264661413183</v>
+        <v>3.986974002015011</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.74819257159244</v>
+        <v>-2.820343670589393</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.311657686748648</v>
+        <v>2.282797247149867</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.053022621223721</v>
+        <v>0.980871522226769</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.043104712433605</v>
+        <v>3.999814053035434</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.75763349748097</v>
+        <v>-2.829784596477923</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.364135034115083</v>
+        <v>2.335274594516302</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.175449738767113</v>
+        <v>1.103298639770161</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.172814700681487</v>
+        <v>4.129524041283315</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.809907104816611</v>
+        <v>-2.882058203813564</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.346116685726128</v>
+        <v>2.317256246127346</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.123176131431471</v>
+        <v>1.051025032434519</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.144341630825403</v>
+        <v>4.101050971427232</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.886237082417517</v>
+        <v>-2.95838818141447</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.31369650757954</v>
+        <v>2.284836067980759</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.123176131431471</v>
+        <v>1.051025032434519</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.142453443719178</v>
+        <v>4.099162784321007</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.08849080274187</v>
+        <v>-3.160641901738823</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.227615249052661</v>
+        <v>2.19875480945388</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9209224111071179</v>
+        <v>0.8487713121101657</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.015921441127428</v>
+        <v>3.972630781729257</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.250059228269126</v>
+        <v>-3.322210327266078</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.161421889051911</v>
+        <v>2.132561449453131</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7941394873092386</v>
+        <v>0.7219883883122863</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.938285697058853</v>
+        <v>3.894995037660682</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.382360520366679</v>
+        <v>-3.454511619363632</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.121574779078809</v>
+        <v>2.092714339480028</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7941394873092386</v>
+        <v>0.7219883883122863</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.951359103924772</v>
+        <v>3.908068444526601</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.568228831205909</v>
+        <v>-3.640379930202862</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.039232651526057</v>
+        <v>2.010372211927276</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6355738939892909</v>
+        <v>0.5634227949923386</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.848224944715743</v>
+        <v>3.804934285317572</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.596129618315382</v>
+        <v>-3.668280717312335</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.02659637780927</v>
+        <v>1.997735938210488</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6009769698463561</v>
+        <v>0.5288258708494038</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.825990831356984</v>
+        <v>3.782700171958813</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.718655721018276</v>
+        <v>-3.790806820015229</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.974350380705311</v>
+        <v>1.94548994110653</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4784508671434622</v>
+        <v>0.4062997681465099</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.749239613712447</v>
+        <v>3.705948954314275</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.949170217203864</v>
+        <v>-4.021321316200817</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.948850541821579</v>
+        <v>1.919990102222798</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2479363709578735</v>
+        <v>0.1757852719609212</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.677636875591597</v>
+        <v>3.634346216193426</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.205891035198688</v>
+        <v>-4.278042134195641</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.986473933625497</v>
+        <v>1.957613494026716</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1395217968140586</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.752899850107156</v>
+        <v>3.709609190708984</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.359877452974828</v>
+        <v>-4.432028551971781</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.99385963566068</v>
+        <v>1.964999196061899</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1395217968140586</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.821880119252795</v>
+        <v>3.778589459854624</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.309355549147162</v>
+        <v>-4.381506648144115</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.000119599311867</v>
+        <v>1.971259159713087</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1395217968140586</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.807931321372916</v>
+        <v>3.764640661974745</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.561830703154887</v>
+        <v>-4.63398180215184</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.911000026764192</v>
+        <v>1.882139587165411</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1395217968140586</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.81980181042833</v>
+        <v>3.776511151030159</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.854726459634299</v>
+        <v>-4.926877558631252</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.795052258691371</v>
+        <v>1.76619181909259</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1395217968140586</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.821012344947274</v>
+        <v>3.777721685549102</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.012270531363741</v>
+        <v>-5.084421630360693</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.736156372226915</v>
+        <v>1.707295932628135</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.07261999167378413</v>
+        <v>0.0004688926768318669</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.78499300409043</v>
+        <v>3.741702344692259</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.290234926947014</v>
+        <v>-5.362386025943967</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.620048466729795</v>
+        <v>1.591188027131015</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.01699974261170012</v>
+        <v>-0.08915084160865239</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.72629901625533</v>
+        <v>3.683008356857158</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.407202619585905</v>
+        <v>-5.479353718582858</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.735465446373283</v>
+        <v>1.706605006774502</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.01699974261170012</v>
+        <v>-0.08915084160865239</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.888503072954373</v>
+        <v>3.845212413556202</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.491920561806858</v>
+        <v>-5.564071660803811</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.696424907448716</v>
+        <v>1.667564467849935</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1021157715397465</v>
+        <v>-0.1742668705366988</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.83228009356136</v>
+        <v>3.788989434163188</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.573855380075742</v>
+        <v>-5.646006479072694</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.673880397709654</v>
+        <v>1.645019958110873</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1120505171268267</v>
+        <v>-0.1842016161237789</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.836548663777603</v>
+        <v>3.793258004379431</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.675831502324149</v>
+        <v>-5.747982601321102</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.642015587266193</v>
+        <v>1.613155147667412</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2140266393752343</v>
+        <v>-0.2861777383721865</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.784288628884461</v>
+        <v>3.740997969486289</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.565825218846927</v>
+        <v>-5.63797631784388</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.678170987901257</v>
+        <v>1.649310548302476</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.190822067457959</v>
+        <v>-0.2629731664549113</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.790364259279001</v>
+        <v>3.74707359988083</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.422765643106002</v>
+        <v>-5.494916742102955</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.739644828919602</v>
+        <v>1.710784389320821</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1828086408679798</v>
+        <v>-0.254959739864932</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.799422325954963</v>
+        <v>3.756131666556792</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.121318917634165</v>
+        <v>-5.193470016631117</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.867484401990873</v>
+        <v>1.838623962392092</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1186380846038575</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.987551244120602</v>
+        <v>3.94426058472243</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.145909161869349</v>
+        <v>-5.218060260866301</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.85861948204951</v>
+        <v>1.829759042450729</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1186380846038575</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.988522421873312</v>
+        <v>3.945231762475141</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.094870785862828</v>
+        <v>-5.167021884859781</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.879877736831873</v>
+        <v>1.851017297233092</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1186380846038575</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.989365326253068</v>
+        <v>3.946074666854896</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.053731490996197</v>
+        <v>-5.12588258999315</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.915371553652671</v>
+        <v>1.88651111405389</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1597773794704883</v>
+        <v>0.08762628047353604</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.033087002047191</v>
+        <v>3.98979634264902</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.943125350916596</v>
+        <v>-5.015276449913548</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.775798005808446</v>
+        <v>1.746937566209665</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2703835195500903</v>
+        <v>0.1982324205531381</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.915634682218887</v>
+        <v>3.872344022820716</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.073706085447438</v>
+        <v>-5.145857184444391</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.727067756070073</v>
+        <v>1.698207316471292</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1398027850192478</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.840788285574345</v>
+        <v>3.797497626176173</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.909209751256476</v>
+        <v>-4.981360850253429</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.77729310882254</v>
+        <v>1.748432669223759</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1398027850192478</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.825215104650427</v>
+        <v>3.781924445252256</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.936579683940908</v>
+        <v>-5.008730782937861</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.765532846185197</v>
+        <v>1.736672406586416</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1398027850192478</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.824402815086857</v>
+        <v>3.781112155688686</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.946964878830798</v>
+        <v>-5.019115977827751</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.771247547354314</v>
+        <v>1.742387107755532</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1294175901293585</v>
+        <v>0.05726649113240623</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.828040477277996</v>
+        <v>3.784749817879825</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.965553037553023</v>
+        <v>-5.037704136549976</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.834649289641849</v>
+        <v>1.805788850043068</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1108294314071331</v>
+        <v>0.03867833241018087</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.887724587821086</v>
+        <v>3.844433928422915</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.965851584249059</v>
+        <v>-5.038002683246011</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.831398881781733</v>
+        <v>1.802538442182952</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1108294314071331</v>
+        <v>0.03867833241018087</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.884593598639384</v>
+        <v>3.841302939241213</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.865028450558631</v>
+        <v>-4.937179549555584</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.876259030197295</v>
+        <v>1.847398590598514</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.123293646891487</v>
+        <v>0.05114254789453471</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.896603022869388</v>
+        <v>3.853312363471217</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.674247089806224</v>
+        <v>-4.746398188803177</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.952700827976801</v>
+        <v>1.923840388378021</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3140750076438943</v>
+        <v>0.2419239086469421</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.011201092799376</v>
+        <v>3.967910433401205</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.655730235764404</v>
+        <v>-4.727881334761356</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.939944415331126</v>
+        <v>1.911083975732345</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3270051370691026</v>
+        <v>0.2548540380721503</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.998796016192098</v>
+        <v>3.955505356793926</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.630537051263086</v>
+        <v>-4.702688150260038</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.984988625743712</v>
+        <v>1.956128186144931</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3521983215704209</v>
+        <v>0.2800472225734686</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.048878863504947</v>
+        <v>4.005588204106775</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.618482924350123</v>
+        <v>-4.690634023347076</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.983496844410335</v>
+        <v>1.954636404811554</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3642524484833837</v>
+        <v>0.2921013494864315</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.049797907554162</v>
+        <v>4.006507248155991</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.625106171040481</v>
+        <v>-4.697257270037434</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.982728175918327</v>
+        <v>1.953867736319546</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.3576292017930254</v>
+        <v>0.2854781027960731</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.047704589724083</v>
+        <v>4.004413930325912</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.522225581511888</v>
+        <v>-4.594376680508841</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.036731437607647</v>
+        <v>2.007870998008866</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4605097913216183</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.122283969319121</v>
+        <v>4.07899330992095</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.545667620691975</v>
+        <v>-4.617818719688928</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.047557292109206</v>
+        <v>2.018696852510425</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4605097913216183</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.142486639492716</v>
+        <v>4.099195980094544</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.563740128983587</v>
+        <v>-4.635891227980539</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.040328288792562</v>
+        <v>2.011467849193781</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4605097913216183</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.142486639492716</v>
+        <v>4.099195980094544</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.794913922860219</v>
+        <v>-4.867065021857171</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.908110684835375</v>
+        <v>1.879250245236594</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4605097913216183</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.102738553086183</v>
+        <v>4.059447893688011</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.763627902319763</v>
+        <v>-4.835779001316716</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.927647712048498</v>
+        <v>1.898787272449717</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4917958118620737</v>
+        <v>0.4196447128651214</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.128532784407396</v>
+        <v>4.085242125009224</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.843046999204358</v>
+        <v>3.425734224211403</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.752266344484506</v>
+        <v>-4.824417443481459</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.031363334755504</v>
+        <v>2.002502895156724</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.5031573696973306</v>
+        <v>0.4310062707003783</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.234520718681454</v>
+        <v>4.191230059283282</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>93.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>425.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.0%</t>
+          <t>-638.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.0%</t>
+          <t>-173.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.1%</t>
+          <t>-142.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-180.9%</t>
+          <t>-175.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2051"/>
+  <dimension ref="A1:G2052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.108086654605097</v>
+        <v>-4.042435379642678</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.135320754105625</v>
+        <v>1.161581264090593</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4927100574034022</v>
+        <v>0.5583613323658223</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.074537874703454</v>
+        <v>3.113928639680906</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.995709653422425</v>
+        <v>-3.930058378460005</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.185762850409362</v>
+        <v>1.21202336039433</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4927100574034022</v>
+        <v>0.5583613323658223</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.080029170534121</v>
+        <v>3.119419935511573</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.023490051323778</v>
+        <v>-3.957838776361358</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.186147893017359</v>
+        <v>1.212408403002327</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4649296595020492</v>
+        <v>0.5305809344644692</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.074858133561849</v>
+        <v>3.114248898539301</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.141870724053916</v>
+        <v>-4.076219449091496</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9771513439259574</v>
+        <v>1.003411853910925</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.397711807351073</v>
+        <v>0.463363082313493</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.872883142271916</v>
+        <v>2.912273907249368</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.250484802497247</v>
+        <v>-4.184833527534828</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.053855373267831</v>
+        <v>1.080115883252799</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.397711807351073</v>
+        <v>0.463363082313493</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.993032802991122</v>
+        <v>3.032423567968574</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.215075764249105</v>
+        <v>-4.149424489286685</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082532014669411</v>
+        <v>1.108792524654379</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.397711807351073</v>
+        <v>0.463363082313493</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.007545829093444</v>
+        <v>3.046936594070897</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.176692101690954</v>
+        <v>-4.111040826728534</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.09530492103504</v>
+        <v>1.121565431020008</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4360954699092242</v>
+        <v>0.5017467448716442</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.027995467970704</v>
+        <v>3.067386232948156</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.999575771655787</v>
+        <v>-3.933924496693368</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.162880481894408</v>
+        <v>1.189140991879376</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4360954699092242</v>
+        <v>0.5017467448716442</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.024724496816006</v>
+        <v>3.064115261793458</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.044668016489333</v>
+        <v>-3.979016741526913</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145526975722903</v>
+        <v>1.171787485707871</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3741994267398344</v>
+        <v>0.4398507017022544</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.988270262676285</v>
+        <v>3.027661027653737</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.865292595250565</v>
+        <v>-3.799641320288146</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.211064119524824</v>
+        <v>1.237324629509792</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.530976184910553</v>
+        <v>0.5966274598729731</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.076123292885131</v>
+        <v>3.115514057862583</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.910306808771172</v>
+        <v>-3.844655533808752</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.173865889448172</v>
+        <v>1.20012639943314</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5006272895959484</v>
+        <v>0.5662785645583684</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.038721411027958</v>
+        <v>3.07811217600541</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.177311319043607</v>
+        <v>-4.111660044081187</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.072755647678143</v>
+        <v>1.099016157663111</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3062642515529998</v>
+        <v>0.3719155265154199</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.927795150541134</v>
+        <v>2.967185915518586</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.27850910048078</v>
+        <v>-4.21285782551836</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031480456999776</v>
+        <v>1.057740966984744</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2378554380076806</v>
+        <v>0.3035067129701007</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.885953784310444</v>
+        <v>2.925344549287896</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.271998133866467</v>
+        <v>-4.206346858904047</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.031684805199817</v>
+        <v>1.057945315184785</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2378554380076806</v>
+        <v>0.3035067129701007</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.883553745864761</v>
+        <v>2.922944510842213</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.25296000615917</v>
+        <v>-4.18730873119675</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.035824775490981</v>
+        <v>1.062085285475949</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1796718266764861</v>
+        <v>0.2453231016389061</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.845168298274289</v>
+        <v>2.884559063251741</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.30547580843399</v>
+        <v>-4.239824533471571</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.134112856215243</v>
+        <v>1.160373366200211</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1796718266764861</v>
+        <v>0.2453231016389061</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.964462699908479</v>
+        <v>3.003853464885931</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.319342569767908</v>
+        <v>-4.253691294805488</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.12939948066781</v>
+        <v>1.155659990652778</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1418139099426631</v>
+        <v>0.2074651849050832</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.942581278854319</v>
+        <v>2.981972043831771</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.274538398227978</v>
+        <v>-4.208887123265558</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.153329679680708</v>
+        <v>1.179590189665676</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1418139099426631</v>
+        <v>0.2074651849050832</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.948589809251245</v>
+        <v>2.987980574228697</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.126795427992976</v>
+        <v>-4.061144153030556</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.110377089051908</v>
+        <v>1.136637599036876</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3096212671775463</v>
+        <v>0.3752725421399664</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.947224444869375</v>
+        <v>2.986615209846827</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.210616649267674</v>
+        <v>-4.144965374305254</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.07964222207351</v>
+        <v>1.105902732058478</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3096212671775463</v>
+        <v>0.3752725421399664</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.950018066400856</v>
+        <v>2.989408831378308</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.20446394321489</v>
+        <v>-4.13881266825247</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.082765652886282</v>
+        <v>1.10902616287125</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3157739732303306</v>
+        <v>0.3814252481927506</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.954372038424184</v>
+        <v>2.993762803401637</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.221273241365392</v>
+        <v>-4.155621966402972</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.075122410366191</v>
+        <v>1.101382920351159</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2989646750798289</v>
+        <v>0.364615950042249</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.943366936273994</v>
+        <v>2.982757701251446</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.158975242589269</v>
+        <v>-4.09332396762685</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.166377163673461</v>
+        <v>1.192637673658429</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.344258939354271</v>
+        <v>0.4099102143166911</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.03687904863548</v>
+        <v>3.076269813612932</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.957185044924111</v>
+        <v>-3.891533769961692</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.049385244453652</v>
+        <v>1.075645754438619</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5422771315234254</v>
+        <v>0.6079284064858455</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.9579819656511</v>
+        <v>2.997372730628552</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.008071757610306</v>
+        <v>-3.942420482647886</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.099320791701349</v>
+        <v>1.125581301686317</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4913904188372309</v>
+        <v>0.557041693799651</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.997740170361558</v>
+        <v>3.03713093533901</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.921461014960499</v>
+        <v>-3.855809739998079</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.148592824877315</v>
+        <v>1.174853334862283</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5700161500423891</v>
+        <v>0.6356674250048092</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.059543345200697</v>
+        <v>3.098934110178149</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.981670312965783</v>
+        <v>-3.916019038003363</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.123045086499873</v>
+        <v>1.149305596484841</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5098068520371046</v>
+        <v>0.5754581269995247</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.021953747222198</v>
+        <v>3.06134451219965</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.905248266533857</v>
+        <v>-3.839596991571437</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.152105523112573</v>
+        <v>1.178366033097541</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5098068520371046</v>
+        <v>0.5754581269995247</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.020445365262126</v>
+        <v>3.059836130239578</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.860875134895288</v>
+        <v>-3.795223859932868</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.169717643203436</v>
+        <v>1.195978153188404</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5541799836756732</v>
+        <v>0.6198312586380933</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.046932111680703</v>
+        <v>3.086322876658155</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.883355485754173</v>
+        <v>-3.817704210791753</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.155119296998473</v>
+        <v>1.181379806983441</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5541799836756732</v>
+        <v>0.6198312586380933</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.041325905819294</v>
+        <v>3.080716670796746</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.835699755193117</v>
+        <v>-3.770048480230697</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.1805633462507</v>
+        <v>1.206823856235668</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6018357142367289</v>
+        <v>0.667486989199149</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.076301101183732</v>
+        <v>3.115691866161184</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.735181596694362</v>
+        <v>-3.669530321731942</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.225662983024926</v>
+        <v>1.251923493009894</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7023538727354834</v>
+        <v>0.7680051476979035</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.14150436965771</v>
+        <v>3.180895134635162</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.71927626726201</v>
+        <v>-3.65362499229959</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.21877978727374</v>
+        <v>1.245040297258708</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6232412120262445</v>
+        <v>0.6888924869886646</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.080791445708039</v>
+        <v>3.120182210685491</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.674437865653612</v>
+        <v>-3.608786590691192</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.240812850527727</v>
+        <v>1.267073360512695</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.627784644971114</v>
+        <v>0.693435919933534</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.087615208085589</v>
+        <v>3.127005973063041</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.69393632189562</v>
+        <v>-3.6282850469332</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.237174407662002</v>
+        <v>1.26343491764697</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5797000036912097</v>
+        <v>0.6453512786536297</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.062925362948724</v>
+        <v>3.102316127926176</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.649733484809719</v>
+        <v>-3.5840822098473</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.260735145024199</v>
+        <v>1.286995655009167</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6239028407771101</v>
+        <v>0.6895541157395302</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.095326667728102</v>
+        <v>3.134717432705554</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.686712512473163</v>
+        <v>-3.621061237510743</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.24435353442807</v>
+        <v>1.270614044413038</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6608767425684406</v>
+        <v>0.7265280175308607</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.115921009272148</v>
+        <v>3.155311774249599</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.52842109493389</v>
+        <v>-3.46276981997147</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.358917866626818</v>
+        <v>1.385178376611786</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6608767425684406</v>
+        <v>0.7265280175308607</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.167168774455187</v>
+        <v>3.206559539432639</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.320779091299414</v>
+        <v>-3.255127816336994</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.440415372674862</v>
+        <v>1.46667588265983</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8685187462029168</v>
+        <v>0.9341700211653369</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.290194681230126</v>
+        <v>3.329585446207578</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.269746998576886</v>
+        <v>-3.204095723614466</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.455776438002143</v>
+        <v>1.482036947987111</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9195508389254448</v>
+        <v>0.9852021138878648</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.315762165101913</v>
+        <v>3.355152930079365</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.20452281744968</v>
+        <v>-3.13887154248726</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.49905351454573</v>
+        <v>1.525314024530698</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9847750200526504</v>
+        <v>1.05042629501507</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.372084077870941</v>
+        <v>3.411474842848393</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.167095797378547</v>
+        <v>-3.101444522416127</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.509985294873464</v>
+        <v>1.536245804858432</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9900265580818322</v>
+        <v>1.055677833044252</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.371195972987731</v>
+        <v>3.410586737965182</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.187207453413255</v>
+        <v>-3.121556178450835</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.503197424790821</v>
+        <v>1.529457934775789</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.001053903079251</v>
+        <v>1.066705178041671</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.379069172317422</v>
+        <v>3.418459937294874</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.13346263898605</v>
+        <v>-3.06781136402363</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.685253121582914</v>
+        <v>1.711513631567882</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.011117212519713</v>
+        <v>1.076768487482133</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.54566492900291</v>
+        <v>3.585055693980362</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.058680377961037</v>
+        <v>-2.993029102998618</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.835278935210736</v>
+        <v>1.861539445195704</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.085899473544726</v>
+        <v>1.151550748507146</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.710647194835735</v>
+        <v>3.750037959813187</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.032596293697229</v>
+        <v>-2.96694501873481</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.837420544930118</v>
+        <v>1.863681054915086</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.085899473544726</v>
+        <v>1.151550748507146</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.702355170849594</v>
+        <v>3.741745935827046</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.944718380588109</v>
+        <v>-2.879067105625689</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.870764905757546</v>
+        <v>1.897025415742514</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.201825115968077</v>
+        <v>1.267476390930497</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.770103751887384</v>
+        <v>3.809494516864836</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.935825919194825</v>
+        <v>-2.870174644232406</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.891876296041651</v>
+        <v>1.918136806026619</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.201825115968077</v>
+        <v>1.267476390930497</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.787658157614175</v>
+        <v>3.827048922591628</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.104302036164703</v>
+        <v>-3.038650761202284</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.816340896658284</v>
+        <v>1.842601406643252</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.173877280251497</v>
+        <v>1.239528555213916</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.762744503588811</v>
+        <v>3.802135268566263</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.40650250730312</v>
+        <v>-2.3408512323407</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.076730405390779</v>
+        <v>2.102990915375747</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.103529220881086</v>
+        <v>1.169180495843506</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.701805365154426</v>
+        <v>3.741196130131879</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.383781403619968</v>
+        <v>-2.318130128657548</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.076482869360945</v>
+        <v>2.102743379345912</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.103529220881086</v>
+        <v>1.169180495843506</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.692469387651331</v>
+        <v>3.731860152628783</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.51298321691401</v>
+        <v>-2.44733194195159</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.183708269894496</v>
+        <v>2.209968779879464</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9743274075870436</v>
+        <v>1.039978682549463</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.773854425526075</v>
+        <v>3.813245190503527</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.667764223692266</v>
+        <v>-2.602112948729846</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.158873689676841</v>
+        <v>2.185134199661809</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9409597335325675</v>
+        <v>1.006611008494987</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.790911643587036</v>
+        <v>3.830302408564488</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.660709533477092</v>
+        <v>-2.595058258514672</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.158370921752455</v>
+        <v>2.184631431737423</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9480144237477413</v>
+        <v>1.013665698710161</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.791819813705685</v>
+        <v>3.831210578683137</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.633758309150604</v>
+        <v>-2.568107034188184</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.179157565127792</v>
+        <v>2.20541807511276</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9628947697754604</v>
+        <v>1.02854604473788</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.810754174967058</v>
+        <v>3.85014493994451</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.76971131720692</v>
+        <v>-2.7040600422445</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.308879494050225</v>
+        <v>2.335140004035194</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9628947697754604</v>
+        <v>1.02854604473788</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.994857307112018</v>
+        <v>4.03424807208947</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.792119435011792</v>
+        <v>-2.726468160049373</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.29203294183127</v>
+        <v>2.318293451816237</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9628947697754604</v>
+        <v>1.02854604473788</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.986974002015011</v>
+        <v>4.026364766992463</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.820343670589393</v>
+        <v>-2.754692395626973</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.282797247149867</v>
+        <v>2.309057757134835</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.980871522226769</v>
+        <v>1.046522797189189</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999814053035434</v>
+        <v>4.039204818012886</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.829784596477923</v>
+        <v>-2.764133321515503</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.335274594516302</v>
+        <v>2.36153510450127</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.103298639770161</v>
+        <v>1.16894991473258</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.129524041283315</v>
+        <v>4.168914806260767</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.882058203813564</v>
+        <v>-2.816406928851144</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.317256246127346</v>
+        <v>2.343516756112314</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.051025032434519</v>
+        <v>1.116676307396939</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.101050971427232</v>
+        <v>4.140441736404684</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.95838818141447</v>
+        <v>-2.89273690645205</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.284836067980759</v>
+        <v>2.311096577965727</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.051025032434519</v>
+        <v>1.116676307396939</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.099162784321007</v>
+        <v>4.138553549298459</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.160641901738823</v>
+        <v>-3.094990626776403</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.19875480945388</v>
+        <v>2.225015319438848</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8487713121101657</v>
+        <v>0.9144225870725855</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.972630781729257</v>
+        <v>4.012021546706709</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.322210327266078</v>
+        <v>-3.256559052303658</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.132561449453131</v>
+        <v>2.158821959438098</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7219883883122863</v>
+        <v>0.7876396632747061</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.894995037660682</v>
+        <v>3.934385802638134</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.454511619363632</v>
+        <v>-3.388860344401212</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.092714339480028</v>
+        <v>2.118974849464996</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7219883883122863</v>
+        <v>0.7876396632747061</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.908068444526601</v>
+        <v>3.947459209504053</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.640379930202862</v>
+        <v>-3.574728655240442</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.010372211927276</v>
+        <v>2.036632721912244</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5634227949923386</v>
+        <v>0.6290740699547585</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.804934285317572</v>
+        <v>3.844325050295024</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.668280717312335</v>
+        <v>-3.602629442349915</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.997735938210488</v>
+        <v>2.023996448195456</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5288258708494038</v>
+        <v>0.5944771458118236</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.782700171958813</v>
+        <v>3.822090936936265</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.790806820015229</v>
+        <v>-3.725155545052809</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.94548994110653</v>
+        <v>1.971750451091498</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4062997681465099</v>
+        <v>0.4719510431089298</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.705948954314275</v>
+        <v>3.745339719291727</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.021321316200817</v>
+        <v>-3.955670041238397</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.919990102222798</v>
+        <v>1.946250612207766</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1757852719609212</v>
+        <v>0.241436546923341</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.634346216193426</v>
+        <v>3.673736981170878</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.278042134195641</v>
+        <v>-4.212390859233221</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.957613494026716</v>
+        <v>1.983874004011684</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1330219727795262</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.709609190708984</v>
+        <v>3.748999955686436</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.432028551971781</v>
+        <v>-4.366377277009361</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.964999196061899</v>
+        <v>1.991259706046868</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1330219727795262</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.778589459854624</v>
+        <v>3.817980224832076</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.381506648144115</v>
+        <v>-4.315855373181695</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.971259159713087</v>
+        <v>1.997519669698054</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1330219727795262</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.764640661974745</v>
+        <v>3.804031426952196</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.63398180215184</v>
+        <v>-4.56833052718942</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.882139587165411</v>
+        <v>1.908400097150379</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1330219727795262</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.776511151030159</v>
+        <v>3.81590191600761</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.926877558631252</v>
+        <v>-4.861226283668832</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.76619181909259</v>
+        <v>1.792452329077558</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.1330219727795262</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.777721685549102</v>
+        <v>3.817112450526554</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.084421630360693</v>
+        <v>-5.018770355398273</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.707295932628135</v>
+        <v>1.733556442613102</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.0004688926768318669</v>
+        <v>0.06612016763925171</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.741702344692259</v>
+        <v>3.781093109669711</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.362386025943967</v>
+        <v>-5.296734750981547</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.591188027131015</v>
+        <v>1.617448537115982</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.08915084160865239</v>
+        <v>-0.02349956664623254</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.683008356857158</v>
+        <v>3.72239912183461</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.479353718582858</v>
+        <v>-5.413702443620438</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.706605006774502</v>
+        <v>1.73286551675947</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.08915084160865239</v>
+        <v>-0.02349956664623254</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.845212413556202</v>
+        <v>3.884603178533654</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.564071660803811</v>
+        <v>-5.498420385841391</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.667564467849935</v>
+        <v>1.693824977834903</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1742668705366988</v>
+        <v>-0.1086155955742789</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.788989434163188</v>
+        <v>3.82838019914064</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.646006479072694</v>
+        <v>-5.580355204110274</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.645019958110873</v>
+        <v>1.671280468095841</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1842016161237789</v>
+        <v>-0.1185503411613591</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.793258004379431</v>
+        <v>3.832648769356883</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.747982601321102</v>
+        <v>-5.682331326358682</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.613155147667412</v>
+        <v>1.63941565765238</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2861777383721865</v>
+        <v>-0.2205264634097667</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.740997969486289</v>
+        <v>3.780388734463741</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.63797631784388</v>
+        <v>-5.57232504288146</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.649310548302476</v>
+        <v>1.675571058287444</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2629731664549113</v>
+        <v>-0.1973218914924915</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.74707359988083</v>
+        <v>3.786464364858282</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.494916742102955</v>
+        <v>-5.429265467140535</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.710784389320821</v>
+        <v>1.737044899305789</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.254959739864932</v>
+        <v>-0.1893084649025122</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.756131666556792</v>
+        <v>3.795522431534244</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.193470016631117</v>
+        <v>-5.127818741668698</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.838623962392092</v>
+        <v>1.86488447237706</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.1121382605693251</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.94426058472243</v>
+        <v>3.983651349699882</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.218060260866301</v>
+        <v>-5.152408985903882</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.829759042450729</v>
+        <v>1.856019552435697</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.1121382605693251</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.945231762475141</v>
+        <v>3.984622527452593</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.167021884859781</v>
+        <v>-5.101370609897361</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.851017297233092</v>
+        <v>1.87727780721806</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.1121382605693251</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.946074666854896</v>
+        <v>3.985465431832347</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.12588258999315</v>
+        <v>-5.06023131503073</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.88651111405389</v>
+        <v>1.912771624038858</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.08762628047353604</v>
+        <v>0.1532775554359559</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.98979634264902</v>
+        <v>4.029187107626472</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.015276449913548</v>
+        <v>-4.949625174951128</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.746937566209665</v>
+        <v>1.773198076194633</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1982324205531381</v>
+        <v>0.2638836955155579</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.872344022820716</v>
+        <v>3.911734787798167</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.145857184444391</v>
+        <v>-5.080205909481971</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.698207316471292</v>
+        <v>1.72446782645626</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.1333029609847154</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.797497626176173</v>
+        <v>3.836888391153626</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.981360850253429</v>
+        <v>-4.915709575291009</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.748432669223759</v>
+        <v>1.774693179208727</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.1333029609847154</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781924445252256</v>
+        <v>3.821315210229708</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.008730782937861</v>
+        <v>-4.943079507975441</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.736672406586416</v>
+        <v>1.762932916571384</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.1333029609847154</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.781112155688686</v>
+        <v>3.820502920666138</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.019115977827751</v>
+        <v>-4.953464702865331</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.742387107755532</v>
+        <v>1.768647617740501</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.05726649113240623</v>
+        <v>0.1229177660948261</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784749817879825</v>
+        <v>3.824140582857277</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.037704136549976</v>
+        <v>-4.972052861587556</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.805788850043068</v>
+        <v>1.832049360028036</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.03867833241018087</v>
+        <v>0.1043296073726007</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.844433928422915</v>
+        <v>3.883824693400367</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.038002683246011</v>
+        <v>-4.972351408283592</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.802538442182952</v>
+        <v>1.82879895216792</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.03867833241018087</v>
+        <v>0.1043296073726007</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.841302939241213</v>
+        <v>3.880693704218665</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.937179549555584</v>
+        <v>-4.871528274593164</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.847398590598514</v>
+        <v>1.873659100583482</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.05114254789453471</v>
+        <v>0.1167938228569546</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.853312363471217</v>
+        <v>3.892703128448669</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.746398188803177</v>
+        <v>-4.680746913840757</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.923840388378021</v>
+        <v>1.950100898362988</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2419239086469421</v>
+        <v>0.3075751836093619</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.967910433401205</v>
+        <v>4.007301198378657</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.727881334761356</v>
+        <v>-4.662230059798937</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.911083975732345</v>
+        <v>1.937344485717313</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2548540380721503</v>
+        <v>0.3205053130345701</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.955505356793926</v>
+        <v>3.994896121771378</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.702688150260038</v>
+        <v>-4.637036875297619</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.956128186144931</v>
+        <v>1.982388696129899</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2800472225734686</v>
+        <v>0.3456984975358885</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.005588204106775</v>
+        <v>4.044978969084227</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.690634023347076</v>
+        <v>-4.624982748384656</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.954636404811554</v>
+        <v>1.980896914796522</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2921013494864315</v>
+        <v>0.3577526244488513</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.006507248155991</v>
+        <v>4.045898013133443</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.697257270037434</v>
+        <v>-4.631605995075014</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.953867736319546</v>
+        <v>1.980128246304514</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.2854781027960731</v>
+        <v>0.351129377758493</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.004413930325912</v>
+        <v>4.043804695303364</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.594376680508841</v>
+        <v>-4.528725405546421</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.007870998008866</v>
+        <v>2.034131507993834</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4540099672870859</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.07899330992095</v>
+        <v>4.118384074898402</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.617818719688928</v>
+        <v>-4.552167444726508</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.018696852510425</v>
+        <v>2.044957362495393</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4540099672870859</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.099195980094544</v>
+        <v>4.138586745071996</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.635891227980539</v>
+        <v>-4.570239953018119</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.011467849193781</v>
+        <v>2.037728359178749</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4540099672870859</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.099195980094544</v>
+        <v>4.138586745071996</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.867065021857171</v>
+        <v>-4.801413746894752</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.879250245236594</v>
+        <v>1.905510755221562</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4540099672870859</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.059447893688011</v>
+        <v>4.098838658665462</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.835779001316716</v>
+        <v>-4.770127726354296</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.898787272449717</v>
+        <v>1.925047782434684</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4196447128651214</v>
+        <v>0.4852959878275412</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.085242125009224</v>
+        <v>4.124632889986676</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,45 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.425734224211403</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.824417443481459</v>
+        <v>-4.767653037221812</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.002502895156724</v>
+        <v>2.025208657660582</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.4310062707003783</v>
+        <v>0.4877706769600263</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.191230059283282</v>
+        <v>4.225288703039071</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="2" t="n">
+        <v>45514</v>
+      </c>
+      <c r="B2052" t="n">
+        <v>3.844759842392993</v>
+      </c>
+      <c r="C2052" t="n">
+        <v>4.054259468735554</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>-4.767653037221812</v>
+      </c>
+      <c r="E2052" t="n">
+        <v>2.025208657660582</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>0.4877706769600263</v>
+      </c>
+      <c r="G2052" t="n">
+        <v>4.047323265721921</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>425.1%</t>
+          <t>424.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-638.3%</t>
+          <t>-643.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-173.7%</t>
+          <t>-186.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>-89.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-142.9%</t>
+          <t>-157.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-175.2%</t>
+          <t>-182.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-50.2%</t>
         </is>
       </c>
     </row>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.042435379642678</v>
+        <v>-4.108086654605097</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.161581264090593</v>
+        <v>1.135320754105625</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5583613323658223</v>
+        <v>0.4927100574034022</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.113928639680906</v>
+        <v>3.074537874703454</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.930058378460005</v>
+        <v>-3.995709653422425</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.21202336039433</v>
+        <v>1.185762850409362</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5583613323658223</v>
+        <v>0.4927100574034022</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.119419935511573</v>
+        <v>3.080029170534121</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.957838776361358</v>
+        <v>-4.023490051323778</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.212408403002327</v>
+        <v>1.186147893017359</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5305809344644692</v>
+        <v>0.4649296595020492</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.114248898539301</v>
+        <v>3.074858133561849</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705329</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.076219449091496</v>
+        <v>-4.141870724053916</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.003411853910925</v>
+        <v>0.9771513439259574</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.463363082313493</v>
+        <v>0.397711807351073</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.912273907249368</v>
+        <v>2.872883142271916</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.184833527534828</v>
+        <v>-4.250484802497247</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.080115883252799</v>
+        <v>1.053855373267831</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.463363082313493</v>
+        <v>0.397711807351073</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.032423567968574</v>
+        <v>2.993032802991122</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.149424489286685</v>
+        <v>-4.215075764249105</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.108792524654379</v>
+        <v>1.082532014669411</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.463363082313493</v>
+        <v>0.397711807351073</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.046936594070897</v>
+        <v>3.007545829093444</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.111040826728534</v>
+        <v>-4.176692101690954</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.121565431020008</v>
+        <v>1.09530492103504</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5017467448716442</v>
+        <v>0.4360954699092242</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.067386232948156</v>
+        <v>3.027995467970704</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.933924496693368</v>
+        <v>-3.999575771655787</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.189140991879376</v>
+        <v>1.162880481894408</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5017467448716442</v>
+        <v>0.4360954699092242</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.064115261793458</v>
+        <v>3.024724496816006</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793907</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.979016741526913</v>
+        <v>-4.044668016489333</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.171787485707871</v>
+        <v>1.145526975722903</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4398507017022544</v>
+        <v>0.3741994267398344</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.027661027653737</v>
+        <v>2.988270262676285</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.799641320288146</v>
+        <v>-3.865292595250565</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.237324629509792</v>
+        <v>1.211064119524824</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5966274598729731</v>
+        <v>0.530976184910553</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.115514057862583</v>
+        <v>3.076123292885131</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.844655533808752</v>
+        <v>-3.910306808771172</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.20012639943314</v>
+        <v>1.173865889448172</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5662785645583684</v>
+        <v>0.5006272895959484</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.07811217600541</v>
+        <v>3.038721411027958</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.111660044081187</v>
+        <v>-4.177311319043607</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.099016157663111</v>
+        <v>1.072755647678143</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3719155265154199</v>
+        <v>0.3062642515529998</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.967185915518586</v>
+        <v>2.927795150541134</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.21285782551836</v>
+        <v>-4.27850910048078</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.057740966984744</v>
+        <v>1.031480456999776</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3035067129701007</v>
+        <v>0.2378554380076806</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.925344549287896</v>
+        <v>2.885953784310444</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.206346858904047</v>
+        <v>-4.271998133866467</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.057945315184785</v>
+        <v>1.031684805199817</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3035067129701007</v>
+        <v>0.2378554380076806</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.922944510842213</v>
+        <v>2.883553745864761</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.18730873119675</v>
+        <v>-4.25296000615917</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.062085285475949</v>
+        <v>1.035824775490981</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2453231016389061</v>
+        <v>0.1796718266764861</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.884559063251741</v>
+        <v>2.845168298274289</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.239824533471571</v>
+        <v>-4.30547580843399</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.160373366200211</v>
+        <v>1.134112856215243</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2453231016389061</v>
+        <v>0.1796718266764861</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.003853464885931</v>
+        <v>2.964462699908479</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.253691294805488</v>
+        <v>-4.319342569767908</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.155659990652778</v>
+        <v>1.12939948066781</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2074651849050832</v>
+        <v>0.1418139099426631</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.981972043831771</v>
+        <v>2.942581278854319</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.208887123265558</v>
+        <v>-4.274538398227978</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.179590189665676</v>
+        <v>1.153329679680708</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2074651849050832</v>
+        <v>0.1418139099426631</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.987980574228697</v>
+        <v>2.948589809251245</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.061144153030556</v>
+        <v>-4.126795427992976</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.136637599036876</v>
+        <v>1.110377089051908</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3752725421399664</v>
+        <v>0.3096212671775463</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.986615209846827</v>
+        <v>2.947224444869375</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.144965374305254</v>
+        <v>-4.210616649267674</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.105902732058478</v>
+        <v>1.07964222207351</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3752725421399664</v>
+        <v>0.3096212671775463</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.989408831378308</v>
+        <v>2.950018066400856</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.13881266825247</v>
+        <v>-4.20446394321489</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.10902616287125</v>
+        <v>1.082765652886282</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3814252481927506</v>
+        <v>0.3157739732303306</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.993762803401637</v>
+        <v>2.954372038424184</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.155621966402972</v>
+        <v>-4.221273241365392</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.101382920351159</v>
+        <v>1.075122410366191</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.364615950042249</v>
+        <v>0.2989646750798289</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.982757701251446</v>
+        <v>2.943366936273994</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.09332396762685</v>
+        <v>-4.158975242589269</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.192637673658429</v>
+        <v>1.166377163673461</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4099102143166911</v>
+        <v>0.344258939354271</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.076269813612932</v>
+        <v>3.03687904863548</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.891533769961692</v>
+        <v>-3.957185044924111</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.075645754438619</v>
+        <v>1.049385244453652</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6079284064858455</v>
+        <v>0.5422771315234254</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.997372730628552</v>
+        <v>2.9579819656511</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.942420482647886</v>
+        <v>-4.008071757610306</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.125581301686317</v>
+        <v>1.099320791701349</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.557041693799651</v>
+        <v>0.4913904188372309</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.03713093533901</v>
+        <v>2.997740170361558</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.855809739998079</v>
+        <v>-3.921461014960499</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.174853334862283</v>
+        <v>1.148592824877315</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6356674250048092</v>
+        <v>0.5700161500423891</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.098934110178149</v>
+        <v>3.059543345200697</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.916019038003363</v>
+        <v>-3.981670312965783</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.149305596484841</v>
+        <v>1.123045086499873</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5754581269995247</v>
+        <v>0.5098068520371046</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.06134451219965</v>
+        <v>3.021953747222198</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.839596991571437</v>
+        <v>-3.905248266533857</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.178366033097541</v>
+        <v>1.152105523112573</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5754581269995247</v>
+        <v>0.5098068520371046</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.059836130239578</v>
+        <v>3.020445365262126</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.795223859932868</v>
+        <v>-3.860875134895288</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.195978153188404</v>
+        <v>1.169717643203436</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6198312586380933</v>
+        <v>0.5541799836756732</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.086322876658155</v>
+        <v>3.046932111680703</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.817704210791753</v>
+        <v>-3.883355485754173</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.181379806983441</v>
+        <v>1.155119296998473</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6198312586380933</v>
+        <v>0.5541799836756732</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.080716670796746</v>
+        <v>3.041325905819294</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.770048480230697</v>
+        <v>-3.835699755193117</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.206823856235668</v>
+        <v>1.1805633462507</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.667486989199149</v>
+        <v>0.6018357142367289</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.115691866161184</v>
+        <v>3.076301101183732</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.669530321731942</v>
+        <v>-3.735181596694362</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.251923493009894</v>
+        <v>1.225662983024926</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7680051476979035</v>
+        <v>0.7023538727354834</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.180895134635162</v>
+        <v>3.14150436965771</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.65362499229959</v>
+        <v>-3.71927626726201</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.245040297258708</v>
+        <v>1.21877978727374</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6888924869886646</v>
+        <v>0.6232412120262445</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.120182210685491</v>
+        <v>3.080791445708039</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.608786590691192</v>
+        <v>-3.674437865653612</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.267073360512695</v>
+        <v>1.240812850527727</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.693435919933534</v>
+        <v>0.627784644971114</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.127005973063041</v>
+        <v>3.087615208085589</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917055</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.6282850469332</v>
+        <v>-3.686352557018726</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.26343491764697</v>
+        <v>1.24020791361276</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6453512786536297</v>
+        <v>0.5642532065548681</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.102316127926176</v>
+        <v>3.053657284666919</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405963</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.5840822098473</v>
+        <v>-3.642149719932826</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.286995655009167</v>
+        <v>1.263768650974957</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6895541157395302</v>
+        <v>0.6084560436407686</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.134717432705554</v>
+        <v>3.086058589446297</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265648</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.621061237510743</v>
+        <v>-3.679128747596269</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.270614044413038</v>
+        <v>1.247387040378827</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7265280175308607</v>
+        <v>0.6454299454320991</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.155311774249599</v>
+        <v>3.106652930990343</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284882</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.46276981997147</v>
+        <v>-3.520837330056997</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.385178376611786</v>
+        <v>1.361951372577576</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7265280175308607</v>
+        <v>0.6454299454320991</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.206559539432639</v>
+        <v>3.157900696173382</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.255127816336994</v>
+        <v>-3.31319532642252</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.46667588265983</v>
+        <v>1.443448878625619</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9341700211653369</v>
+        <v>0.8530719490665752</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.329585446207578</v>
+        <v>3.280926602948321</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.204095723614466</v>
+        <v>-3.262163233699992</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.482036947987111</v>
+        <v>1.458809943952901</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9852021138878648</v>
+        <v>0.9041040417891032</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.355152930079365</v>
+        <v>3.306494086820108</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.13887154248726</v>
+        <v>-3.196939052572787</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.525314024530698</v>
+        <v>1.502087020496488</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.05042629501507</v>
+        <v>0.9693282229163088</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.411474842848393</v>
+        <v>3.362815999589136</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.101444522416127</v>
+        <v>-3.159512032501653</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.536245804858432</v>
+        <v>1.513018800824222</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.055677833044252</v>
+        <v>0.9745797609454905</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.410586737965182</v>
+        <v>3.361927894705925</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.121556178450835</v>
+        <v>-3.179623688536361</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.529457934775789</v>
+        <v>1.506230930741579</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.066705178041671</v>
+        <v>0.9856071059429097</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.418459937294874</v>
+        <v>3.369801094035617</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.06781136402363</v>
+        <v>-3.125878874109156</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.711513631567882</v>
+        <v>1.688286627533671</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.076768487482133</v>
+        <v>0.9956704153833718</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.585055693980362</v>
+        <v>3.536396850721105</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.993029102998618</v>
+        <v>-3.051096613084144</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.861539445195704</v>
+        <v>1.838312441161494</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.151550748507146</v>
+        <v>1.070452676408384</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.750037959813187</v>
+        <v>3.70137911655393</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.96694501873481</v>
+        <v>-3.025012528820336</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.863681054915086</v>
+        <v>1.840454050880876</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.151550748507146</v>
+        <v>1.070452676408384</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.741745935827046</v>
+        <v>3.693087092567789</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.879067105625689</v>
+        <v>-2.937134615711215</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.897025415742514</v>
+        <v>1.873798411708304</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.267476390930497</v>
+        <v>1.186378318831736</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.809494516864836</v>
+        <v>3.760835673605579</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.870174644232406</v>
+        <v>-2.928242154317932</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.918136806026619</v>
+        <v>1.894909801992408</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.267476390930497</v>
+        <v>1.186378318831736</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.827048922591628</v>
+        <v>3.778390079332371</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.038650761202284</v>
+        <v>-3.09671827128781</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.842601406643252</v>
+        <v>1.819374402609041</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.239528555213916</v>
+        <v>1.158430483115155</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.802135268566263</v>
+        <v>3.753476425307006</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.3408512323407</v>
+        <v>-2.398918742426226</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.102990915375747</v>
+        <v>2.079763911341536</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.169180495843506</v>
+        <v>1.088082423744744</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.741196130131879</v>
+        <v>3.692537286872621</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.318130128657548</v>
+        <v>-2.376197638743074</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.102743379345912</v>
+        <v>2.079516375311702</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.169180495843506</v>
+        <v>1.088082423744744</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.731860152628783</v>
+        <v>3.683201309369526</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.44733194195159</v>
+        <v>-2.505399452037116</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.209968779879464</v>
+        <v>2.186741775845254</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.039978682549463</v>
+        <v>0.9588806104507019</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.813245190503527</v>
+        <v>3.76458634724427</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.602112948729846</v>
+        <v>-2.660180458815372</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.185134199661809</v>
+        <v>2.161907195627598</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.006611008494987</v>
+        <v>0.9255129363962258</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.830302408564488</v>
+        <v>3.78164356530523</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.595058258514672</v>
+        <v>-2.653125768600198</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.184631431737423</v>
+        <v>2.161404427703213</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.013665698710161</v>
+        <v>0.9325676266113996</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.831210578683137</v>
+        <v>3.78255173542388</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.568107034188184</v>
+        <v>-2.62617454427371</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.20541807511276</v>
+        <v>2.18219107107855</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.02854604473788</v>
+        <v>0.9474479726391187</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.85014493994451</v>
+        <v>3.801486096685253</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.7040600422445</v>
+        <v>-2.762127552330027</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.335140004035194</v>
+        <v>2.311913000000983</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.02854604473788</v>
+        <v>0.9474479726391187</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.03424807208947</v>
+        <v>3.985589228830213</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.726468160049373</v>
+        <v>-2.784535670134899</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.318293451816237</v>
+        <v>2.295066447782027</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.02854604473788</v>
+        <v>0.9474479726391187</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.026364766992463</v>
+        <v>3.977705923733206</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.754692395626973</v>
+        <v>-2.812759905712499</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.309057757134835</v>
+        <v>2.285830753100624</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.046522797189189</v>
+        <v>0.9654247250904273</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.039204818012886</v>
+        <v>3.990545974753629</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.764133321515503</v>
+        <v>-2.822200831601029</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.36153510450127</v>
+        <v>2.33830810046706</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.16894991473258</v>
+        <v>1.087851842633819</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.168914806260767</v>
+        <v>4.120255963001511</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.816406928851144</v>
+        <v>-2.87447443893667</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.343516756112314</v>
+        <v>2.320289752078104</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.116676307396939</v>
+        <v>1.035578235298177</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.140441736404684</v>
+        <v>4.091782893145426</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.89273690645205</v>
+        <v>-2.950804416537576</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.311096577965727</v>
+        <v>2.287869573931517</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.116676307396939</v>
+        <v>1.035578235298177</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.138553549298459</v>
+        <v>4.089894706039201</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.094990626776403</v>
+        <v>-3.153058136861929</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.225015319438848</v>
+        <v>2.201788315404638</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9144225870725855</v>
+        <v>0.833324514973824</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.012021546706709</v>
+        <v>3.963362703447452</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.256559052303658</v>
+        <v>-3.314626562389185</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.158821959438098</v>
+        <v>2.135594955403888</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7876396632747061</v>
+        <v>0.7065415911759446</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.934385802638134</v>
+        <v>3.885726959378877</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.388860344401212</v>
+        <v>-3.446927854486738</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.118974849464996</v>
+        <v>2.095747845430785</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7876396632747061</v>
+        <v>0.7065415911759446</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.947459209504053</v>
+        <v>3.898800366244795</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.574728655240442</v>
+        <v>-3.632796165325968</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.036632721912244</v>
+        <v>2.013405717878033</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6290740699547585</v>
+        <v>0.5479759978559969</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.844325050295024</v>
+        <v>3.795666207035767</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.602629442349915</v>
+        <v>-3.660696952435441</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.023996448195456</v>
+        <v>2.000769444161246</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5944771458118236</v>
+        <v>0.5133790737130621</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.822090936936265</v>
+        <v>3.773432093677008</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.725155545052809</v>
+        <v>-3.783223055138335</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.971750451091498</v>
+        <v>1.948523447057287</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4719510431089298</v>
+        <v>0.3908529710101682</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.745339719291727</v>
+        <v>3.69668087603247</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.955670041238397</v>
+        <v>-4.013737551323923</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.946250612207766</v>
+        <v>1.923023608173556</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.241436546923341</v>
+        <v>0.1603384748245795</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.673736981170878</v>
+        <v>3.625078137911621</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.212390859233221</v>
+        <v>-4.270458369318748</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.983874004011684</v>
+        <v>1.960646999977473</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1330219727795262</v>
+        <v>0.05192390068076469</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.748999955686436</v>
+        <v>3.700341112427179</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.366377277009361</v>
+        <v>-4.424444787094888</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.991259706046868</v>
+        <v>1.968032702012656</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1330219727795262</v>
+        <v>0.05192390068076469</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.817980224832076</v>
+        <v>3.769321381572819</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.315855373181695</v>
+        <v>-4.373922883267222</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.997519669698054</v>
+        <v>1.974292665663844</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1330219727795262</v>
+        <v>0.05192390068076469</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.804031426952196</v>
+        <v>3.75537258369294</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.56833052718942</v>
+        <v>-4.626398037274947</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.908400097150379</v>
+        <v>1.885173093116168</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1330219727795262</v>
+        <v>0.05192390068076469</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.81590191600761</v>
+        <v>3.767243072748354</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.861226283668832</v>
+        <v>-4.919293793754359</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.792452329077558</v>
+        <v>1.769225325043347</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1330219727795262</v>
+        <v>0.05192390068076469</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.817112450526554</v>
+        <v>3.768453607267297</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.018770355398273</v>
+        <v>-5.0768378654838</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.733556442613102</v>
+        <v>1.710329438578892</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.06612016763925171</v>
+        <v>-0.01497790445950981</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.781093109669711</v>
+        <v>3.732434266410454</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.296734750981547</v>
+        <v>-5.354802261067074</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.617448537115982</v>
+        <v>1.594221533081772</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.02349956664623254</v>
+        <v>-0.1045976387449941</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.72239912183461</v>
+        <v>3.673740278575353</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.413702443620438</v>
+        <v>-5.471769953705965</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.73286551675947</v>
+        <v>1.709638512725259</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.02349956664623254</v>
+        <v>-0.1045976387449941</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.884603178533654</v>
+        <v>3.835944335274397</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.498420385841391</v>
+        <v>-5.556487895926918</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.693824977834903</v>
+        <v>1.670597973800692</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1086155955742789</v>
+        <v>-0.1897136676730404</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.82838019914064</v>
+        <v>3.779721355881383</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.580355204110274</v>
+        <v>-5.638422714195801</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.671280468095841</v>
+        <v>1.64805346406163</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1185503411613591</v>
+        <v>-0.1996484132601206</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.832648769356883</v>
+        <v>3.783989926097627</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.682331326358682</v>
+        <v>-5.740398836444209</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.63941565765238</v>
+        <v>1.61618865361817</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2205264634097667</v>
+        <v>-0.3016245355085282</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.780388734463741</v>
+        <v>3.731729891204485</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.57232504288146</v>
+        <v>-5.630392552966987</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.675571058287444</v>
+        <v>1.652344054253233</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1973218914924915</v>
+        <v>-0.278419963591253</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.786464364858282</v>
+        <v>3.737805521599025</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.429265467140535</v>
+        <v>-5.487332977226062</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.737044899305789</v>
+        <v>1.713817895271578</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1893084649025122</v>
+        <v>-0.2704065370012737</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.795522431534244</v>
+        <v>3.746863588274987</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.127818741668698</v>
+        <v>-5.185886251754225</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.86488447237706</v>
+        <v>1.841657468342849</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1121382605693251</v>
+        <v>0.03104018847056356</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.983651349699882</v>
+        <v>3.934992506440625</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.805998658009189</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.152408985903882</v>
+        <v>-5.210476495989409</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.856019552435697</v>
+        <v>1.721451635299678</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1121382605693251</v>
+        <v>0.03104018847056356</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.984622527452593</v>
+        <v>3.824622771091528</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.806841562388945</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.101370609897361</v>
+        <v>-5.159438119982888</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.87727780721806</v>
+        <v>1.742709890082041</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1121382605693251</v>
+        <v>0.03104018847056356</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.985465431832347</v>
+        <v>3.825465675471283</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.82587966126309</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.06023131503073</v>
+        <v>-5.118298825116257</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.912771624038858</v>
+        <v>1.778203706902839</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1532775554359559</v>
+        <v>0.07217948333719437</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.029187107626472</v>
+        <v>3.869187351265407</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.642063657387025</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.949625174951128</v>
+        <v>-5.007692685036655</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.773198076194633</v>
+        <v>1.638630159058615</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2638836955155579</v>
+        <v>0.1827856234167964</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.911734787798167</v>
+        <v>3.751735031437103</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.645565701460988</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.080205909481971</v>
+        <v>-5.138273419567498</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.72446782645626</v>
+        <v>1.589899909320241</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1333029609847154</v>
+        <v>0.05220488888595387</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.836888391153626</v>
+        <v>3.676888634792561</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.629992520537071</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.915709575291009</v>
+        <v>-4.973777085376536</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.774693179208727</v>
+        <v>1.640125262072708</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1333029609847154</v>
+        <v>0.05220488888595387</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.821315210229708</v>
+        <v>3.661315453868644</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.629180230973501</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.943079507975441</v>
+        <v>-5.001147018060968</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.762932916571384</v>
+        <v>1.628364999435365</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1333029609847154</v>
+        <v>0.05220488888595387</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.820502920666138</v>
+        <v>3.660503164305073</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.639049010098573</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.953464702865331</v>
+        <v>-5.011532212950858</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.768647617740501</v>
+        <v>1.634079700604482</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1229177660948261</v>
+        <v>0.04181969399606456</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.824140582857277</v>
+        <v>3.664140826496212</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.709886015874998</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.972052861587556</v>
+        <v>-5.030120371673083</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.832049360028036</v>
+        <v>1.697481442892017</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1043296073726007</v>
+        <v>0.0232315352738392</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.883824693400367</v>
+        <v>3.723824937039302</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.706755026693297</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.972351408283592</v>
+        <v>-5.030418918369119</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.82879895216792</v>
+        <v>1.694231035031901</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1043296073726007</v>
+        <v>0.0232315352738392</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.880693704218665</v>
+        <v>3.720693947857601</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.711285921632688</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.871528274593164</v>
+        <v>-4.929595784678691</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.873659100583482</v>
+        <v>1.739091183447464</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1167938228569546</v>
+        <v>0.03569575075819303</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.892703128448669</v>
+        <v>3.732703372087604</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.711415175111231</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.680746913840757</v>
+        <v>-4.738814423926284</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.950100898362988</v>
+        <v>1.81553298122697</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3075751836093619</v>
+        <v>0.2264771115106004</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.007301198378657</v>
+        <v>3.847301442017592</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.691252020848828</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.662230059798937</v>
+        <v>-4.720297569884464</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.937344485717313</v>
+        <v>1.802776568581295</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3205053130345701</v>
+        <v>0.2394072409358086</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.994896121771378</v>
+        <v>3.834896365410313</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.726218957460886</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.637036875297619</v>
+        <v>-4.695104385383146</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.982388696129899</v>
+        <v>1.84782077899388</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3456984975358885</v>
+        <v>0.264600425437127</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.044978969084227</v>
+        <v>3.884979212723163</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.719905525362324</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.624982748384656</v>
+        <v>-4.683050258470183</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.980896914796522</v>
+        <v>1.846328997660503</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3577526244488513</v>
+        <v>0.2766545523500898</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.045898013133443</v>
+        <v>3.885898256772378</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.72178615554646</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.631605995075014</v>
+        <v>-4.689673505160541</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.980128246304514</v>
+        <v>1.845560329168496</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.351129377758493</v>
+        <v>0.2700313056597314</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.043804695303364</v>
+        <v>3.883804938942299</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.734637181424342</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.528725405546421</v>
+        <v>-4.586792915631948</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.034131507993834</v>
+        <v>1.899563590857815</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4540099672870859</v>
+        <v>0.3729118951883243</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.118384074898402</v>
+        <v>3.958384318537338</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.754839851597937</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.552167444726508</v>
+        <v>-4.610234954812035</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.044957362495393</v>
+        <v>1.910389445359375</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4540099672870859</v>
+        <v>0.3729118951883243</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.138586745071996</v>
+        <v>3.978586988710932</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.754839851597937</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.570239953018119</v>
+        <v>-4.628307463103646</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.037728359178749</v>
+        <v>1.90316044204273</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4540099672870859</v>
+        <v>0.3729118951883243</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.138586745071996</v>
+        <v>3.978586988710932</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.715091765191403</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.801413746894752</v>
+        <v>-4.859481256980279</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.905510755221562</v>
+        <v>1.770942838085544</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4540099672870859</v>
+        <v>0.3729118951883243</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.098838658665462</v>
+        <v>3.938838902304398</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.722114384188343</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.770127726354296</v>
+        <v>-4.828195236439823</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.925047782434684</v>
+        <v>1.790479865298666</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4852959878275412</v>
+        <v>0.4041979157287797</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.124632889986676</v>
+        <v>3.964633133625611</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.821285383761248</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.767653037221812</v>
+        <v>-4.816833678604566</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.025208657660582</v>
+        <v>1.894195488005673</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.4877706769600263</v>
+        <v>0.4155594735640366</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.225288703039071</v>
+        <v>4.07062106789967</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.844759842392993</v>
+        <v>3.839895672009696</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.054259468735554</v>
+        <v>3.965621508548687</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.767653037221812</v>
+        <v>-4.816833678604566</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.025208657660582</v>
+        <v>1.894195488005673</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.4877706769600263</v>
+        <v>0.4155594735640366</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.047323265721921</v>
+        <v>3.958685305535055</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>126.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-613.8%</t>
+          <t>-628.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>424.9%</t>
+          <t>419.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.3%</t>
+          <t>-671.6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-245.9%</t>
+          <t>-251.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.8%</t>
+          <t>-187.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.9%</t>
+          <t>-151.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.4%</t>
+          <t>-180.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-54.9%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4594793927979829</v>
+        <v>-0.6020243034993515</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.937180580893785</v>
+        <v>2.880162616613238</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.4480901561431815</v>
+        <v>-0.5906350668445501</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.939561071674946</v>
+        <v>2.882543107394399</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8658441796900185</v>
+        <v>-1.008389090391387</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.770386353761275</v>
+        <v>2.713368389480727</v>
       </c>
       <c r="F1847" t="n">
         <v>1.126693817913202</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.15597584629545</v>
+        <v>-1.298520756996818</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.654199903718024</v>
+        <v>2.597181939437477</v>
       </c>
       <c r="F1848" t="n">
         <v>1.150775612653382</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.363979904648527</v>
+        <v>-1.506524815349896</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.575890424930718</v>
+        <v>2.518872460650171</v>
       </c>
       <c r="F1849" t="n">
         <v>1.150775612653382</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.426158315809497</v>
+        <v>-1.568703226510866</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.546100516804318</v>
+        <v>2.489082552523771</v>
       </c>
       <c r="F1850" t="n">
         <v>1.088597201492412</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.79222704295415</v>
+        <v>-1.934771953655518</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.392757325252906</v>
+        <v>2.335739360972359</v>
       </c>
       <c r="F1851" t="n">
         <v>0.722528474347759</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.000717824405834</v>
+        <v>-2.143262735107203</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.329699302411001</v>
+        <v>2.272681338130453</v>
       </c>
       <c r="F1852" t="n">
         <v>0.5140376928960746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.247919009171056</v>
+        <v>-2.390463919872424</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.238917578913481</v>
+        <v>2.181899614632933</v>
       </c>
       <c r="F1853" t="n">
         <v>0.534191046394887</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.740304037195153</v>
+        <v>-2.882848947896521</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.043069959747574</v>
+        <v>1.986051995467027</v>
       </c>
       <c r="F1854" t="n">
         <v>0.04180601837079029</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.125484428125225</v>
+        <v>-3.268029338826594</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.887540342188408</v>
+        <v>1.830522377907861</v>
       </c>
       <c r="F1855" t="n">
         <v>0.04180601837079029</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.375355108139807</v>
+        <v>-3.517900018841175</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.789361193637192</v>
+        <v>1.732343229356645</v>
       </c>
       <c r="F1856" t="n">
         <v>0.07806873820125354</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.581866885026828</v>
+        <v>-3.724411795728197</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.702862541538641</v>
+        <v>1.645844577258094</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.128443038685768</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.901210960107329</v>
+        <v>-4.043755870808699</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.5768978382067</v>
+        <v>1.519879873926153</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.128443038685768</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.287420791383104</v>
+        <v>-4.429965702084474</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.408746793163795</v>
+        <v>1.351728828883247</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.2192159784032113</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.522114785515656</v>
+        <v>-4.664659696217027</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.303153970512864</v>
+        <v>1.246136006232317</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.2128797111739561</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.857777432746109</v>
+        <v>-5.000322343447479</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.167469503276648</v>
+        <v>1.110451538996101</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.2808106966628609</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.93422176294898</v>
+        <v>-5.076766673650351</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.143379331429741</v>
+        <v>1.086361367149194</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.200365187569199</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.299349145587727</v>
+        <v>-5.441894056289097</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.996582893380074</v>
+        <v>0.9395649290995265</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4966759718682116</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.707937922768406</v>
+        <v>-5.850482833469776</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8319089265225617</v>
+        <v>0.7748909622420137</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.90526474904889</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.821698334791271</v>
+        <v>-5.964243245492641</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7815901941848762</v>
+        <v>0.7245722299043287</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.90526474904889</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.238090209078268</v>
+        <v>-6.380635119779638</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6130274950789545</v>
+        <v>0.556009530798407</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.90526474904889</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.599263838895256</v>
+        <v>-6.741808749596626</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4788167338208384</v>
+        <v>0.4217987695402909</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.90526474904889</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.942522358538275</v>
+        <v>-7.085067269239645</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3376128911093264</v>
+        <v>0.2805949268287784</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.90526474904889</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.990725175780619</v>
+        <v>-7.133270086481989</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3167366842673895</v>
+        <v>0.2597187199868416</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.90526474904889</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.287386517590816</v>
+        <v>-7.429931428292186</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2018511234725189</v>
+        <v>0.1448331591919709</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.9740078847827686</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.474106225900119</v>
+        <v>-7.616651136601489</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1231369356143945</v>
+        <v>0.06611897133384659</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.9740078847827686</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.85710761464275</v>
+        <v>-7.99965252534412</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.03016572120424188</v>
+        <v>-0.08718368548478983</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.9740078847827686</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.861594059844139</v>
+        <v>-8.004138970545508</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.02938878331336747</v>
+        <v>-0.08640674759391498</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.9784943299841573</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.22112438234814</v>
+        <v>-8.363669293049512</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1678506090169183</v>
+        <v>-0.2248685732974658</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.9784943299841573</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.271473445802362</v>
+        <v>-8.414018356503734</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1800742144414293</v>
+        <v>-0.2370921787219773</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.028843393438379</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.369092723223758</v>
+        <v>-8.51163763392513</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2160801747882188</v>
+        <v>-0.2730981390687668</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.126462670859776</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.423164222732117</v>
+        <v>-8.565709133433488</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2348152182699903</v>
+        <v>-0.2918331825505383</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.180534170368135</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.627422398061981</v>
+        <v>-8.769967308763352</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3110052912832932</v>
+        <v>-0.3680232555638412</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.308173114982124</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.661075236570454</v>
+        <v>-8.803620147271825</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3199838722022466</v>
+        <v>-0.3770018364827945</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.408586482899162</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.587605404903005</v>
+        <v>-8.730150315604376</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2752242380418459</v>
+        <v>-0.3322422023223939</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.335116651231713</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.762729822289549</v>
+        <v>-8.90527473299092</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3307187842489467</v>
+        <v>-0.3877367485294942</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.510241068618257</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.997181916304038</v>
+        <v>-9.13972682700541</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4317187867563383</v>
+        <v>-0.4887367510368863</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.510241068618257</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.101556647330485</v>
+        <v>-9.244101558031856</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4801408699408931</v>
+        <v>-0.5371588342214411</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.614615799644703</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.264070113029069</v>
+        <v>-9.40661502373044</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5440304663817708</v>
+        <v>-0.6010484306623183</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.71224923006339</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.390106906397358</v>
+        <v>-9.53265181709873</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5917514550999718</v>
+        <v>-0.6487694193805194</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.686997607253647</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.333035134501428</v>
+        <v>-9.475580045202799</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5649324106551985</v>
+        <v>-0.6219503749357465</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.686997607253647</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.474706976225548</v>
+        <v>-9.617251886926919</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6230763742435883</v>
+        <v>-0.6800943385241363</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.686997607253647</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.425116131800714</v>
+        <v>-9.567661042502085</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5881866263087825</v>
+        <v>-0.64520459058933</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.637406762828813</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.276197797328857</v>
+        <v>-9.418742708030228</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5416704261667227</v>
+        <v>-0.5986883904472706</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.60615717209364</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.050352644609445</v>
+        <v>-9.192897555310818</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4417532920427494</v>
+        <v>-0.4987712563232978</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.564230496506477</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.925773988271853</v>
+        <v>-9.068318898973226</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3907826849516538</v>
+        <v>-0.4478006492322022</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.564230496506477</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.97866927631614</v>
+        <v>-9.121214187017513</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4093070260072604</v>
+        <v>-0.4663249902878093</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.55927515041803</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.906536101028259</v>
+        <v>-9.049081011729632</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3747200516534717</v>
+        <v>-0.4317380159340201</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.55927515041803</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.835169708418611</v>
+        <v>-8.977714619119984</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3559107570034779</v>
+        <v>-0.4129287212840262</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.487908757808382</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.741710674433387</v>
+        <v>-8.88425558513476</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3284106247222955</v>
+        <v>-0.3854285890028444</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.487908757808382</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.731057492879955</v>
+        <v>-8.873602403581328</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.325983912600297</v>
+        <v>-0.3830018768808454</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.487908757808382</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.633150454203465</v>
+        <v>-8.775695364904838</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2871214121031613</v>
+        <v>-0.3441393763837097</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.419923007947826</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.609196913227507</v>
+        <v>-8.75174182392888</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2768714895672848</v>
+        <v>-0.3338894538478332</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.395969466971869</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.34513697490471</v>
+        <v>-8.487681885606083</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1845078303999181</v>
+        <v>-0.2415257946804665</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.131909528649072</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.638057351399872</v>
+        <v>-7.780602262101245</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.09553698534171629</v>
+        <v>0.03851902106116789</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.131909528649072</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.597873053033681</v>
+        <v>-7.740417963735054</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1119543285760338</v>
+        <v>0.05493636429548543</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.091725230282881</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.434473182094319</v>
+        <v>-7.577018092795692</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1766810981725357</v>
+        <v>0.1196631338919873</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.928325359343519</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.20099195986472</v>
+        <v>-7.343536870566093</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2779980159022277</v>
+        <v>0.2209800516216793</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6948441371139205</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.051325568857205</v>
+        <v>-7.193870479558578</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3349723619922744</v>
+        <v>0.277954397711726</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6019406458713845</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.919050095226319</v>
+        <v>-7.061595005927692</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3832500381916559</v>
+        <v>0.3262320739111075</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4696651722404979</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.763311762666577</v>
+        <v>-6.90585667336795</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4483604319031897</v>
+        <v>0.3913424676226409</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3139268396807563</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.678347095937257</v>
+        <v>-6.82089200663863</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4952526398185761</v>
+        <v>0.4382346755380278</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2289621729514367</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.783937085710361</v>
+        <v>-6.926481996411734</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3250407143101159</v>
+        <v>0.2680227500295675</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3345521627245411</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.802671987828958</v>
+        <v>-6.945216898530331</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3660910953397636</v>
+        <v>0.3090731310592147</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3401481723846724</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.654731946421359</v>
+        <v>-6.797276857122732</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3053881892146357</v>
+        <v>0.2483702249340869</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3198272564761148</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.60176242416737</v>
+        <v>-6.744307334868743</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3178620118627529</v>
+        <v>0.2608440475822045</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2668577342221259</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.43597422820708</v>
+        <v>-6.578519138908453</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3772166781517758</v>
+        <v>0.3201987138712274</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2668577342221259</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.402611021728311</v>
+        <v>-6.545155932429684</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4050243151244266</v>
+        <v>0.3480063508438782</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2668577342221259</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.294351884605789</v>
+        <v>-6.436896795307162</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4428600904326303</v>
+        <v>0.3858421261520819</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2668577342221259</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.171060749788658</v>
+        <v>-6.313605660490031</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4896746383700594</v>
+        <v>0.432656674089511</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1435665994049954</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.118363882657367</v>
+        <v>-6.26090879335874</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.518454363459901</v>
+        <v>0.4614363991793526</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09086973227370426</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.874598440673923</v>
+        <v>-6.150180387503247</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6117412486003295</v>
+        <v>0.5015084698686008</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09086973227370426</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.772835620396628</v>
+        <v>-6.048417567225952</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6545706906312634</v>
+        <v>0.5443379118995346</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.07765066388127556</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.522985226447553</v>
+        <v>-5.798567173276878</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7472529231945955</v>
+        <v>0.6370201444628667</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.07765066388127556</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.34709313398012</v>
+        <v>-5.622675080809445</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8212088837022176</v>
+        <v>0.7109761049704884</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.07765066388127556</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.175646670957657</v>
+        <v>-5.451228617786982</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9031149749657565</v>
+        <v>0.7928821962340273</v>
       </c>
       <c r="F1921" t="n">
         <v>0.09379579914118757</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.101357105219318</v>
+        <v>-5.376939052048643</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9318512788773892</v>
+        <v>0.82161850014566</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1680853648795269</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.037721362985383</v>
+        <v>-5.313303309814708</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9620003768252801</v>
+        <v>0.8517675980935508</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2317211071134614</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.926294603659463</v>
+        <v>-5.201876550488788</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9877653393394439</v>
+        <v>0.8775325606077145</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2317211071134614</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.936797226724752</v>
+        <v>-5.212379173554077</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9853073667382057</v>
+        <v>0.8750745880064765</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2212184840481725</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.864554658553558</v>
+        <v>-5.140136605382883</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.018133707841504</v>
+        <v>0.9079009291097746</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2212184840481725</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.846840971675692</v>
+        <v>-5.122422918505017</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.02589776650999</v>
+        <v>0.9156649877782606</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2243998129450893</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.738036086195965</v>
+        <v>-5.01361803302529</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.066417791921874</v>
+        <v>0.956185013190145</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2243998129450893</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.518015288158955</v>
+        <v>-4.79359723498828</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.156005148147293</v>
+        <v>1.045772369415563</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3656196580130696</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.385147599095677</v>
+        <v>-4.660729545925002</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.225046406574427</v>
+        <v>1.114813627842698</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3656196580130696</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.264974515731178</v>
+        <v>-4.540556462560503</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.274261484360528</v>
+        <v>1.164028705628799</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4857927413775685</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.129721154401201</v>
+        <v>-4.405303101230526</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.338450931453959</v>
+        <v>1.22821815272223</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6210461027075456</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.189595981758893</v>
+        <v>-4.465177928588218</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.300538491912308</v>
+        <v>1.190305713180579</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5611712753498534</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.069775750848057</v>
+        <v>-4.345357697677382</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.363755753510851</v>
+        <v>1.253522974779122</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5611712753498534</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.072245457309863</v>
+        <v>-4.347827404139188</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.27041207024857</v>
+        <v>1.160179291516841</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5587015688880472</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.140615643633873</v>
+        <v>-4.416197590463198</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.162325857204268</v>
+        <v>1.052093078472538</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5679772679242622</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.154403696480919</v>
+        <v>-4.429985643310244</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.14724734469734</v>
+        <v>1.037014565965611</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5679772679242622</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.209923772373509</v>
+        <v>-4.485505719202834</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.262070151032507</v>
+        <v>1.151837372300778</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5679772679242622</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.034449512581039</v>
+        <v>-4.310031459410364</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.336827086941283</v>
+        <v>1.226594308209553</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5679772679242622</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.145385765222288</v>
+        <v>-4.420967712051613</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.26819461464599</v>
+        <v>1.157961835914261</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5679772679242622</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.111722219750006</v>
+        <v>-4.387304166579331</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.210198346236353</v>
+        <v>1.099965567504623</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6016408133965441</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.051869600546283</v>
+        <v>-4.327451547375608</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.244311780349974</v>
+        <v>1.134079001618245</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6016408133965441</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.965626137519905</v>
+        <v>-4.24120808434923</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.273755436134386</v>
+        <v>1.163522657402656</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6016408133965441</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.010932956918885</v>
+        <v>-4.28651490374821</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.247408483819319</v>
+        <v>1.13717570508759</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5608306503873133</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.039966061621186</v>
+        <v>-4.315548008450511</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.2363471149715</v>
+        <v>1.126114336239771</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5608306503873133</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.947155580170327</v>
+        <v>-4.222737526999651</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.20274399944321</v>
+        <v>1.092511220711481</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6536411318381726</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.991545049499754</v>
+        <v>-4.267126996329079</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.18686168763604</v>
+        <v>1.07662890890431</v>
       </c>
       <c r="F1947" t="n">
         <v>0.609251662508745</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.108086654605097</v>
+        <v>-4.383668601434421</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.135320754105625</v>
+        <v>1.025087975373896</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4927100574034022</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.995709653422425</v>
+        <v>-4.271291600251748</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.185762850409362</v>
+        <v>1.075530071677633</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4927100574034022</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.023490051323778</v>
+        <v>-4.299071998153101</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.186147893017359</v>
+        <v>1.075915114285631</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4649296595020492</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705329</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.141870724053916</v>
+        <v>-4.41745267088324</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9771513439259574</v>
+        <v>0.8669185651942288</v>
       </c>
       <c r="F1951" t="n">
         <v>0.397711807351073</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.250484802497247</v>
+        <v>-4.526066749326571</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.053855373267831</v>
+        <v>0.9436225945361021</v>
       </c>
       <c r="F1952" t="n">
         <v>0.397711807351073</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.215075764249105</v>
+        <v>-4.490657711078428</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082532014669411</v>
+        <v>0.9722992359376821</v>
       </c>
       <c r="F1953" t="n">
         <v>0.397711807351073</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.176692101690954</v>
+        <v>-4.452274048520277</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.09530492103504</v>
+        <v>0.9850721423033113</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4360954699092242</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.999575771655787</v>
+        <v>-4.275157718485111</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.162880481894408</v>
+        <v>1.05264770316268</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4360954699092242</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793907</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.044668016489333</v>
+        <v>-4.320249963318656</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145526975722903</v>
+        <v>1.035294196991174</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3741994267398344</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.865292595250565</v>
+        <v>-4.140874542079889</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.211064119524824</v>
+        <v>1.100831340793096</v>
       </c>
       <c r="F1957" t="n">
         <v>0.530976184910553</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.910306808771172</v>
+        <v>-4.185888755600494</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.173865889448172</v>
+        <v>1.063633110716443</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5006272895959484</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.177311319043607</v>
+        <v>-4.452893265872929</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.072755647678143</v>
+        <v>0.9625228689464151</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3062642515529998</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.27850910048078</v>
+        <v>-4.554091047310102</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031480456999776</v>
+        <v>0.9212476782680474</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2378554380076806</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.271998133866467</v>
+        <v>-4.54758008069579</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.031684805199817</v>
+        <v>0.9214520264680892</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2378554380076806</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.25296000615917</v>
+        <v>-4.528541952988492</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.035824775490981</v>
+        <v>0.925591996759253</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1796718266764861</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.30547580843399</v>
+        <v>-4.581057755263313</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.134112856215243</v>
+        <v>1.023880077483515</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1796718266764861</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.319342569767908</v>
+        <v>-4.594924516597231</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.12939948066781</v>
+        <v>1.019166701936081</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1418139099426631</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.274538398227978</v>
+        <v>-4.550120345057301</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.153329679680708</v>
+        <v>1.043096900948979</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1418139099426631</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.126795427992976</v>
+        <v>-4.402377374822298</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.110377089051908</v>
+        <v>1.00014431032018</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3096212671775463</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.210616649267674</v>
+        <v>-4.486198596096997</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.07964222207351</v>
+        <v>0.9694094433417817</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3096212671775463</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.20446394321489</v>
+        <v>-4.480045890044212</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.082765652886282</v>
+        <v>0.9725328741545538</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3157739732303306</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.221273241365392</v>
+        <v>-4.496855188194714</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.075122410366191</v>
+        <v>0.9648896316344633</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2989646750798289</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.158975242589269</v>
+        <v>-4.434557189418592</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.166377163673461</v>
+        <v>1.056144384941733</v>
       </c>
       <c r="F1970" t="n">
         <v>0.344258939354271</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.957185044924111</v>
+        <v>-4.232766991753434</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.049385244453652</v>
+        <v>0.9391524657219232</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5422771315234254</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.008071757610306</v>
+        <v>-4.283653704439629</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.099320791701349</v>
+        <v>0.9890880129696207</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4913904188372309</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.921461014960499</v>
+        <v>-4.197042961789822</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.148592824877315</v>
+        <v>1.038360046145587</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5700161500423891</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.981670312965783</v>
+        <v>-4.257252259795107</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.123045086499873</v>
+        <v>1.012812307768145</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5098068520371046</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.905248266533857</v>
+        <v>-4.18083021336318</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.152105523112573</v>
+        <v>1.041872744380844</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5098068520371046</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.860875134895288</v>
+        <v>-4.136457081724611</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.169717643203436</v>
+        <v>1.059484864471708</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5541799836756732</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.883355485754173</v>
+        <v>-4.158937432583496</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.155119296998473</v>
+        <v>1.044886518266744</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5541799836756732</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.835699755193117</v>
+        <v>-4.11128170202244</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.1805633462507</v>
+        <v>1.070330567518971</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6018357142367289</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.735181596694362</v>
+        <v>-4.010763543523685</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.225662983024926</v>
+        <v>1.115430204293198</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7023538727354834</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.71927626726201</v>
+        <v>-3.994858214091333</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.21877978727374</v>
+        <v>1.108547008542011</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6232412120262445</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.674437865653612</v>
+        <v>-3.950019812482935</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.240812850527727</v>
+        <v>1.130580071795999</v>
       </c>
       <c r="F1981" t="n">
         <v>0.627784644971114</v>
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917055</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.686352557018726</v>
+        <v>-3.969518268724943</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.24020791361276</v>
+        <v>1.126941628930274</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5642532065548681</v>
+        <v>0.5797000036912097</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.053657284666919</v>
+        <v>3.062925362948724</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405963</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.642149719932826</v>
+        <v>-3.925315431639043</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.263768650974957</v>
+        <v>1.150502366292471</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6084560436407686</v>
+        <v>0.6239028407771101</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.086058589446297</v>
+        <v>3.095326667728102</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265648</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.679128747596269</v>
+        <v>-3.962294459302486</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.247387040378827</v>
+        <v>1.134120755696341</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6454299454320991</v>
+        <v>0.6608767425684406</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.106652930990343</v>
+        <v>3.115921009272148</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.520837330056997</v>
+        <v>-3.804003041763214</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.361951372577576</v>
+        <v>1.24868508789509</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6454299454320991</v>
+        <v>0.6608767425684406</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.157900696173382</v>
+        <v>3.167168774455187</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.31319532642252</v>
+        <v>-3.596361038128737</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.443448878625619</v>
+        <v>1.330182593943133</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8530719490665752</v>
+        <v>0.8685187462029168</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.280926602948321</v>
+        <v>3.290194681230126</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.262163233699992</v>
+        <v>-3.545328945406209</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.458809943952901</v>
+        <v>1.345543659270415</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9041040417891032</v>
+        <v>0.9195508389254448</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.306494086820108</v>
+        <v>3.315762165101913</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.196939052572787</v>
+        <v>-3.480104764279004</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.502087020496488</v>
+        <v>1.388820735814002</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9693282229163088</v>
+        <v>0.9847750200526504</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.362815999589136</v>
+        <v>3.372084077870941</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.159512032501653</v>
+        <v>-3.44267774420787</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.513018800824222</v>
+        <v>1.399752516141736</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9745797609454905</v>
+        <v>0.9900265580818322</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.361927894705925</v>
+        <v>3.371195972987731</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.179623688536361</v>
+        <v>-3.462789400242578</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.506230930741579</v>
+        <v>1.392964646059093</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9856071059429097</v>
+        <v>1.001053903079251</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.369801094035617</v>
+        <v>3.379069172317422</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.125878874109156</v>
+        <v>-3.409044585815373</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.688286627533671</v>
+        <v>1.575020342851185</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9956704153833718</v>
+        <v>1.011117212519713</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.536396850721105</v>
+        <v>3.54566492900291</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.051096613084144</v>
+        <v>-3.334262324790361</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.838312441161494</v>
+        <v>1.725046156479008</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.070452676408384</v>
+        <v>1.085899473544726</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.70137911655393</v>
+        <v>3.710647194835735</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.025012528820336</v>
+        <v>-3.308178240526553</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.840454050880876</v>
+        <v>1.72718776619839</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.070452676408384</v>
+        <v>1.085899473544726</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.693087092567789</v>
+        <v>3.702355170849594</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.937134615711215</v>
+        <v>-3.220300327417432</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.873798411708304</v>
+        <v>1.760532127025817</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.186378318831736</v>
+        <v>1.201825115968077</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.760835673605579</v>
+        <v>3.770103751887384</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.928242154317932</v>
+        <v>-3.211407866024149</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.894909801992408</v>
+        <v>1.781643517309922</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.186378318831736</v>
+        <v>1.201825115968077</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.778390079332371</v>
+        <v>3.787658157614175</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.09671827128781</v>
+        <v>-3.379883982994027</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.819374402609041</v>
+        <v>1.706108117926555</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.158430483115155</v>
+        <v>1.173877280251497</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.753476425307006</v>
+        <v>3.762744503588811</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.398918742426226</v>
+        <v>-2.682084454132443</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.079763911341536</v>
+        <v>1.96649762665905</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.088082423744744</v>
+        <v>1.103529220881086</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.692537286872621</v>
+        <v>3.701805365154426</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.376197638743074</v>
+        <v>-2.659363350449291</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.079516375311702</v>
+        <v>1.966250090629216</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.088082423744744</v>
+        <v>1.103529220881086</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.683201309369526</v>
+        <v>3.692469387651331</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.505399452037116</v>
+        <v>-2.788565163743333</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.186741775845254</v>
+        <v>2.073475491162768</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9588806104507019</v>
+        <v>0.9743274075870436</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.76458634724427</v>
+        <v>3.773854425526075</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.660180458815372</v>
+        <v>-2.943346170521589</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.161907195627598</v>
+        <v>2.048640910945112</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9255129363962258</v>
+        <v>0.9409597335325675</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.78164356530523</v>
+        <v>3.790911643587036</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.653125768600198</v>
+        <v>-2.936291480306415</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.161404427703213</v>
+        <v>2.048138143020727</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9325676266113996</v>
+        <v>0.9480144237477413</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.78255173542388</v>
+        <v>3.791819813705685</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.62617454427371</v>
+        <v>-2.909340255979927</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.18219107107855</v>
+        <v>2.068924786396064</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9474479726391187</v>
+        <v>0.9628947697754604</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.801486096685253</v>
+        <v>3.810754174967058</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.762127552330027</v>
+        <v>-3.045293264036244</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.311913000000983</v>
+        <v>2.198646715318497</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9474479726391187</v>
+        <v>0.9628947697754604</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.985589228830213</v>
+        <v>3.994857307112018</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.784535670134899</v>
+        <v>-3.067701381841116</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.295066447782027</v>
+        <v>2.181800163099541</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9474479726391187</v>
+        <v>0.9628947697754604</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.977705923733206</v>
+        <v>3.986974002015011</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.812759905712499</v>
+        <v>-3.095925617418716</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.285830753100624</v>
+        <v>2.172564468418138</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9654247250904273</v>
+        <v>0.980871522226769</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.990545974753629</v>
+        <v>3.999814053035434</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.822200831601029</v>
+        <v>-3.105366543307246</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.33830810046706</v>
+        <v>2.225041815784573</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.087851842633819</v>
+        <v>1.103298639770161</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.120255963001511</v>
+        <v>4.129524041283315</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.87447443893667</v>
+        <v>-3.157640150642887</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.320289752078104</v>
+        <v>2.207023467395618</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.035578235298177</v>
+        <v>1.051025032434519</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.091782893145426</v>
+        <v>4.101050971427232</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.950804416537576</v>
+        <v>-3.233970128243793</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.287869573931517</v>
+        <v>2.17460328924903</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.035578235298177</v>
+        <v>1.051025032434519</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.089894706039201</v>
+        <v>4.099162784321007</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.153058136861929</v>
+        <v>-3.436223848568146</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.201788315404638</v>
+        <v>2.088522030722152</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.833324514973824</v>
+        <v>0.8487713121101657</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.963362703447452</v>
+        <v>3.972630781729257</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.314626562389185</v>
+        <v>-3.597792274095402</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.135594955403888</v>
+        <v>2.022328670721402</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7065415911759446</v>
+        <v>0.7219883883122863</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.885726959378877</v>
+        <v>3.894995037660682</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.446927854486738</v>
+        <v>-3.730093566192955</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.095747845430785</v>
+        <v>1.982481560748299</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7065415911759446</v>
+        <v>0.7219883883122863</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.898800366244795</v>
+        <v>3.908068444526601</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.632796165325968</v>
+        <v>-3.915961877032185</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.013405717878033</v>
+        <v>1.900139433195547</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5479759978559969</v>
+        <v>0.5634227949923386</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.795666207035767</v>
+        <v>3.804934285317572</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.660696952435441</v>
+        <v>-3.943862664141658</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.000769444161246</v>
+        <v>1.88750315947876</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5133790737130621</v>
+        <v>0.5288258708494038</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.773432093677008</v>
+        <v>3.782700171958813</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.783223055138335</v>
+        <v>-4.066388766844552</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.948523447057287</v>
+        <v>1.835257162374801</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3908529710101682</v>
+        <v>0.4062997681465099</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.69668087603247</v>
+        <v>3.705948954314275</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.013737551323923</v>
+        <v>-4.296903263030141</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.923023608173556</v>
+        <v>1.809757323491069</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1603384748245795</v>
+        <v>0.1757852719609212</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.625078137911621</v>
+        <v>3.634346216193426</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.270458369318748</v>
+        <v>-4.553624081024966</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.960646999977473</v>
+        <v>1.847380715294986</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.05192390068076469</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.700341112427179</v>
+        <v>3.709609190708984</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.424444787094888</v>
+        <v>-4.707610498801106</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.968032702012656</v>
+        <v>1.85476641733017</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.05192390068076469</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.769321381572819</v>
+        <v>3.778589459854624</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.373922883267222</v>
+        <v>-4.65708859497344</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.974292665663844</v>
+        <v>1.861026380981357</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.05192390068076469</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.75537258369294</v>
+        <v>3.764640661974745</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.626398037274947</v>
+        <v>-4.909563748981165</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.885173093116168</v>
+        <v>1.771906808433682</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.05192390068076469</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.767243072748354</v>
+        <v>3.776511151030159</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.919293793754359</v>
+        <v>-5.202459505460577</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.769225325043347</v>
+        <v>1.65595904036086</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.05192390068076469</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.768453607267297</v>
+        <v>3.777721685549102</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.0768378654838</v>
+        <v>-5.360003577190018</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.710329438578892</v>
+        <v>1.597063153896405</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.01497790445950981</v>
+        <v>0.0004688926768318669</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.732434266410454</v>
+        <v>3.741702344692259</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.354802261067074</v>
+        <v>-5.637967972773292</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.594221533081772</v>
+        <v>1.480955248399285</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1045976387449941</v>
+        <v>-0.08915084160865239</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.673740278575353</v>
+        <v>3.683008356857158</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.471769953705965</v>
+        <v>-5.754935665412183</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.709638512725259</v>
+        <v>1.596372228042773</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1045976387449941</v>
+        <v>-0.08915084160865239</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.835944335274397</v>
+        <v>3.845212413556202</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.556487895926918</v>
+        <v>-5.839653607633136</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.670597973800692</v>
+        <v>1.557331689118206</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1897136676730404</v>
+        <v>-0.1742668705366988</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.779721355881383</v>
+        <v>3.788989434163188</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.638422714195801</v>
+        <v>-5.921588425902019</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.64805346406163</v>
+        <v>1.534787179379144</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1996484132601206</v>
+        <v>-0.1842016161237789</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.783989926097627</v>
+        <v>3.793258004379431</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.740398836444209</v>
+        <v>-6.023564548150427</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.61618865361817</v>
+        <v>1.502922368935683</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.3016245355085282</v>
+        <v>-0.2861777383721865</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.731729891204485</v>
+        <v>3.740997969486289</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.630392552966987</v>
+        <v>-5.913558264673205</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.652344054253233</v>
+        <v>1.539077769570747</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.278419963591253</v>
+        <v>-0.2629731664549113</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.737805521599025</v>
+        <v>3.74707359988083</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.487332977226062</v>
+        <v>-5.77049868893228</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.713817895271578</v>
+        <v>1.600551610589092</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2704065370012737</v>
+        <v>-0.254959739864932</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.746863588274987</v>
+        <v>3.756131666556792</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.185886251754225</v>
+        <v>-5.469051963460442</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.841657468342849</v>
+        <v>1.728391183660362</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.03104018847056356</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.934992506440625</v>
+        <v>3.94426058472243</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.805998658009189</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.210476495989409</v>
+        <v>-5.493642207695626</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.721451635299678</v>
+        <v>1.719526263719</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.03104018847056356</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.824622771091528</v>
+        <v>3.945231762475141</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.806841562388945</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.159438119982888</v>
+        <v>-5.442603831689106</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.742709890082041</v>
+        <v>1.740784518501363</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.03104018847056356</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.825465675471283</v>
+        <v>3.946074666854896</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.82587966126309</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.118298825116257</v>
+        <v>-5.401464536822475</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.778203706902839</v>
+        <v>1.77627833532216</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.07217948333719437</v>
+        <v>0.08762628047353604</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.869187351265407</v>
+        <v>3.98979634264902</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.642063657387025</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.007692685036655</v>
+        <v>-5.290858396742873</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.638630159058615</v>
+        <v>1.636704787477936</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1827856234167964</v>
+        <v>0.1982324205531381</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.751735031437103</v>
+        <v>3.872344022820716</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.645565701460988</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.138273419567498</v>
+        <v>-5.421439131273716</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.589899909320241</v>
+        <v>1.587974537739563</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.05220488888595387</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.676888634792561</v>
+        <v>3.797497626176173</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.629992520537071</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.973777085376536</v>
+        <v>-5.256942797082754</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.640125262072708</v>
+        <v>1.63819989049203</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.05220488888595387</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.661315453868644</v>
+        <v>3.781924445252256</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.629180230973501</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.001147018060968</v>
+        <v>-5.284312729767186</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.628364999435365</v>
+        <v>1.626439627854686</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.05220488888595387</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.660503164305073</v>
+        <v>3.781112155688686</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.639049010098573</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.011532212950858</v>
+        <v>-5.294697924657076</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.634079700604482</v>
+        <v>1.632154329023803</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.04181969399606456</v>
+        <v>0.05726649113240623</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.664140826496212</v>
+        <v>3.784749817879825</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.709886015874998</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.030120371673083</v>
+        <v>-5.313286083379301</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.697481442892017</v>
+        <v>1.695556071311338</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.0232315352738392</v>
+        <v>0.03867833241018087</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.723824937039302</v>
+        <v>3.844433928422915</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.706755026693297</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.030418918369119</v>
+        <v>-5.313584630075336</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.694231035031901</v>
+        <v>1.692305663451223</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.0232315352738392</v>
+        <v>0.03867833241018087</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.720693947857601</v>
+        <v>3.841302939241213</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.711285921632688</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.929595784678691</v>
+        <v>-5.212761496384909</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.739091183447464</v>
+        <v>1.737165811866785</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.03569575075819303</v>
+        <v>0.05114254789453471</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.732703372087604</v>
+        <v>3.853312363471217</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.711415175111231</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.738814423926284</v>
+        <v>-5.021980135632502</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.81553298122697</v>
+        <v>1.813607609646291</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2264771115106004</v>
+        <v>0.2419239086469421</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.847301442017592</v>
+        <v>3.967910433401205</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.691252020848828</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.720297569884464</v>
+        <v>-5.003463281590681</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.802776568581295</v>
+        <v>1.800851197000616</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2394072409358086</v>
+        <v>0.2548540380721503</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.834896365410313</v>
+        <v>3.955505356793926</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.726218957460886</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.695104385383146</v>
+        <v>-4.978270097089363</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.84782077899388</v>
+        <v>1.845895407413201</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.264600425437127</v>
+        <v>0.2800472225734686</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.884979212723163</v>
+        <v>4.005588204106775</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.719905525362324</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.683050258470183</v>
+        <v>-4.966215970176401</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.846328997660503</v>
+        <v>1.844403626079824</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2766545523500898</v>
+        <v>0.2921013494864315</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.885898256772378</v>
+        <v>4.006507248155991</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.72178615554646</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.689673505160541</v>
+        <v>-4.972839216866759</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.845560329168496</v>
+        <v>1.843634957587817</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.2700313056597314</v>
+        <v>0.2854781027960731</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.883804938942299</v>
+        <v>4.004413930325912</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.734637181424342</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.586792915631948</v>
+        <v>-4.869958627338166</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.899563590857815</v>
+        <v>1.897638219277137</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.3729118951883243</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.958384318537338</v>
+        <v>4.07899330992095</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.754839851597937</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.610234954812035</v>
+        <v>-4.893400666518253</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.910389445359375</v>
+        <v>1.908464073778696</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.3729118951883243</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.978586988710932</v>
+        <v>4.099195980094544</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.754839851597937</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.628307463103646</v>
+        <v>-4.911473174809864</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.90316044204273</v>
+        <v>1.901235070462051</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.3729118951883243</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.978586988710932</v>
+        <v>4.099195980094544</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.715091765191403</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.859481256980279</v>
+        <v>-5.142646968686496</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.770942838085544</v>
+        <v>1.769017466504865</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.3729118951883243</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.938838902304398</v>
+        <v>4.059447893688011</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.722114384188343</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.828195236439823</v>
+        <v>-5.111360948146041</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.790479865298666</v>
+        <v>1.788554493717987</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4041979157287797</v>
+        <v>0.4196447128651214</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.964633133625611</v>
+        <v>4.085242125009224</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.821285383761248</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.816833678604566</v>
+        <v>-5.099999390310784</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.894195488005673</v>
+        <v>1.892270116424994</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.4155594735640366</v>
+        <v>0.4310062707003783</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.07062106789967</v>
+        <v>4.191230059283282</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.839895672009696</v>
+        <v>3.58649221705556</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.965621508548687</v>
+        <v>3.918235110616684</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.816833678604566</v>
+        <v>-5.099999390310784</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.894195488005673</v>
+        <v>1.892270116424994</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.4155594735640366</v>
+        <v>0.4310062707003783</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.958685305535055</v>
+        <v>3.911298907603052</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-628.0%</t>
+          <t>-627.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.2%</t>
+          <t>419.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-671.6%</t>
+          <t>-657.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-251.6%</t>
+          <t>-251.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-187.0%</t>
+          <t>-181.5%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6020243034993515</v>
+        <v>-0.5983743381632924</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.880162616613238</v>
+        <v>2.881622602747662</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.5906350668445501</v>
+        <v>-0.586985101508491</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.882543107394399</v>
+        <v>2.884003093528822</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.008389090391387</v>
+        <v>-1.004739125055328</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.713368389480727</v>
+        <v>2.714828375615151</v>
       </c>
       <c r="F1847" t="n">
         <v>1.126693817913202</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.298520756996818</v>
+        <v>-1.29487079166076</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.597181939437477</v>
+        <v>2.5986419255719</v>
       </c>
       <c r="F1848" t="n">
         <v>1.150775612653382</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.506524815349896</v>
+        <v>-1.502874850013837</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.518872460650171</v>
+        <v>2.520332446784594</v>
       </c>
       <c r="F1849" t="n">
         <v>1.150775612653382</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.568703226510866</v>
+        <v>-1.565053261174807</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.489082552523771</v>
+        <v>2.490542538658195</v>
       </c>
       <c r="F1850" t="n">
         <v>1.088597201492412</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.934771953655518</v>
+        <v>-1.93112198831946</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.335739360972359</v>
+        <v>2.337199347106782</v>
       </c>
       <c r="F1851" t="n">
         <v>0.722528474347759</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.143262735107203</v>
+        <v>-2.139612769771144</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.272681338130453</v>
+        <v>2.274141324264877</v>
       </c>
       <c r="F1852" t="n">
         <v>0.5140376928960746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.390463919872424</v>
+        <v>-2.386813954536366</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.181899614632933</v>
+        <v>2.183359600767357</v>
       </c>
       <c r="F1853" t="n">
         <v>0.534191046394887</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.882848947896521</v>
+        <v>-2.879198982560462</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.986051995467027</v>
+        <v>1.98751198160145</v>
       </c>
       <c r="F1854" t="n">
         <v>0.04180601837079029</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.268029338826594</v>
+        <v>-3.264379373490535</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.830522377907861</v>
+        <v>1.831982364042285</v>
       </c>
       <c r="F1855" t="n">
         <v>0.04180601837079029</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.517900018841175</v>
+        <v>-3.514250053505116</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.732343229356645</v>
+        <v>1.733803215491068</v>
       </c>
       <c r="F1856" t="n">
         <v>0.07806873820125354</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.724411795728197</v>
+        <v>-3.720761830392138</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.645844577258094</v>
+        <v>1.647304563392518</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.128443038685768</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.043755870808699</v>
+        <v>-4.04010590547264</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.519879873926153</v>
+        <v>1.521339860060576</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.128443038685768</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.429965702084474</v>
+        <v>-4.426315736748415</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.351728828883247</v>
+        <v>1.353188815017671</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.2192159784032113</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.664659696217027</v>
+        <v>-4.661009730880967</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.246136006232317</v>
+        <v>1.24759599236674</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.2128797111739561</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.000322343447479</v>
+        <v>-4.99667237811142</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.110451538996101</v>
+        <v>1.111911525130524</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.2808106966628609</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.076766673650351</v>
+        <v>-5.073116708314291</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.086361367149194</v>
+        <v>1.087821353283617</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.200365187569199</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.441894056289097</v>
+        <v>-5.438244090953038</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9395649290995265</v>
+        <v>0.94102491523395</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4966759718682116</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.850482833469776</v>
+        <v>-5.846832868133717</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7748909622420137</v>
+        <v>0.7763509483764377</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.90526474904889</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.964243245492641</v>
+        <v>-5.960593280156582</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7245722299043287</v>
+        <v>0.7260322160387522</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.90526474904889</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.380635119779638</v>
+        <v>-6.376985154443579</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.556009530798407</v>
+        <v>0.5574695169328305</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.90526474904889</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.741808749596626</v>
+        <v>-6.738158784260567</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4217987695402909</v>
+        <v>0.4232587556747145</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.90526474904889</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.085067269239645</v>
+        <v>-7.081417303903586</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2805949268287784</v>
+        <v>0.282054912963202</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.90526474904889</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.133270086481989</v>
+        <v>-7.12962012114593</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2597187199868416</v>
+        <v>0.2611787061212656</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.90526474904889</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.429931428292186</v>
+        <v>-7.426281462956127</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1448331591919709</v>
+        <v>0.1462931453263949</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.9740078847827686</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.616651136601489</v>
+        <v>-7.61300117126543</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.06611897133384659</v>
+        <v>0.06757895746827058</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.9740078847827686</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.99965252534412</v>
+        <v>-7.996002560008061</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.08718368548478983</v>
+        <v>-0.08572369935036583</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.9740078847827686</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.004138970545508</v>
+        <v>-8.000489005209449</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.08640674759391498</v>
+        <v>-0.08494676145949143</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.9784943299841573</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.363669293049512</v>
+        <v>-8.360019327713452</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2248685732974658</v>
+        <v>-0.2234085871630422</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.9784943299841573</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.414018356503734</v>
+        <v>-8.410368391167674</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2370921787219773</v>
+        <v>-0.2356321925875533</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.028843393438379</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.51163763392513</v>
+        <v>-8.50798766858907</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2730981390687668</v>
+        <v>-0.2716381529343432</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.126462670859776</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.565709133433488</v>
+        <v>-8.562059168097429</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2918331825505383</v>
+        <v>-0.2903731964161143</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.180534170368135</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.769967308763352</v>
+        <v>-8.766317343427293</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3680232555638412</v>
+        <v>-0.3665632694294176</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.308173114982124</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.803620147271825</v>
+        <v>-8.799970181935766</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3770018364827945</v>
+        <v>-0.375541850348371</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.408586482899162</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.730150315604376</v>
+        <v>-8.726500350268317</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3322422023223939</v>
+        <v>-0.3307822161879699</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.335116651231713</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.90527473299092</v>
+        <v>-8.901624767654861</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3877367485294942</v>
+        <v>-0.3862767623950707</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.510241068618257</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.13972682700541</v>
+        <v>-9.13607686166935</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4887367510368863</v>
+        <v>-0.4872767649024623</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.510241068618257</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.244101558031856</v>
+        <v>-9.240451592695797</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5371588342214411</v>
+        <v>-0.5356988480870171</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.614615799644703</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.40661502373044</v>
+        <v>-9.402965058394381</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6010484306623183</v>
+        <v>-0.5995884445278947</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.71224923006339</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.53265181709873</v>
+        <v>-9.52900185176267</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6487694193805194</v>
+        <v>-0.6473094332460958</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.686997607253647</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.475580045202799</v>
+        <v>-9.471930079866739</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6219503749357465</v>
+        <v>-0.6204903888013225</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.686997607253647</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.617251886926919</v>
+        <v>-9.61360192159086</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6800943385241363</v>
+        <v>-0.6786343523897123</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.686997607253647</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.567661042502085</v>
+        <v>-9.564011077166025</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.64520459058933</v>
+        <v>-0.6437446044549064</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.637406762828813</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.418742708030228</v>
+        <v>-9.415092742694169</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5986883904472706</v>
+        <v>-0.5972284043128466</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.60615717209364</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.192897555310818</v>
+        <v>-9.189247589974759</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4987712563232978</v>
+        <v>-0.4973112701888742</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.564230496506477</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.068318898973226</v>
+        <v>-9.064668933637167</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4478006492322022</v>
+        <v>-0.4463406630977782</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.564230496506477</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.121214187017513</v>
+        <v>-9.117564221681453</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4663249902878093</v>
+        <v>-0.4648650041533853</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.55927515041803</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.049081011729632</v>
+        <v>-9.045431046393572</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4317380159340201</v>
+        <v>-0.4302780297995965</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.55927515041803</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.977714619119984</v>
+        <v>-8.974064653783925</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4129287212840262</v>
+        <v>-0.4114687351496027</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.487908757808382</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.88425558513476</v>
+        <v>-8.8806056197987</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3854285890028444</v>
+        <v>-0.3839686028684204</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.487908757808382</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.873602403581328</v>
+        <v>-8.869952438245269</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3830018768808454</v>
+        <v>-0.3815418907464214</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.487908757808382</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.775695364904838</v>
+        <v>-8.772045399568778</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3441393763837097</v>
+        <v>-0.3426793902492862</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.419923007947826</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.75174182392888</v>
+        <v>-8.74809185859282</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3338894538478332</v>
+        <v>-0.3324294677134092</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.395969466971869</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.487681885606083</v>
+        <v>-8.484031920270024</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2415257946804665</v>
+        <v>-0.240065808546043</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.131909528649072</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.780602262101245</v>
+        <v>-7.776952296765185</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.03851902106116789</v>
+        <v>0.03997900719559144</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.131909528649072</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.740417963735054</v>
+        <v>-7.736767998398995</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.05493636429548543</v>
+        <v>0.05639635042990898</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.091725230282881</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.577018092795692</v>
+        <v>-7.573368127459633</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1196631338919873</v>
+        <v>0.1211231200264109</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.928325359343519</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.343536870566093</v>
+        <v>-7.339886905230034</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2209800516216793</v>
+        <v>0.2224400377561029</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6948441371139205</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.193870479558578</v>
+        <v>-7.190220514222519</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.277954397711726</v>
+        <v>0.2794143838461496</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6019406458713845</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.061595005927692</v>
+        <v>-7.057945040591632</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3262320739111075</v>
+        <v>0.3276920600455315</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4696651722404979</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.90585667336795</v>
+        <v>-6.902206708031891</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3913424676226409</v>
+        <v>0.3928024537570649</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3139268396807563</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.82089200663863</v>
+        <v>-6.81724204130257</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4382346755380278</v>
+        <v>0.4396946616724517</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2289621729514367</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.926481996411734</v>
+        <v>-6.922832031075675</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2680227500295675</v>
+        <v>0.2694827361639911</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3345521627245411</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.945216898530331</v>
+        <v>-6.941566933194272</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3090731310592147</v>
+        <v>0.3105331171936387</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3401481723846724</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.797276857122732</v>
+        <v>-6.793626891786673</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2483702249340869</v>
+        <v>0.2498302110685109</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3198272564761148</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.744307334868743</v>
+        <v>-6.740657369532684</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2608440475822045</v>
+        <v>0.262304033716628</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2668577342221259</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.578519138908453</v>
+        <v>-6.574869173572393</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3201987138712274</v>
+        <v>0.321658700005651</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2668577342221259</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.545155932429684</v>
+        <v>-6.541505967093625</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3480063508438782</v>
+        <v>0.3494663369783018</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2668577342221259</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.436896795307162</v>
+        <v>-6.433246829971103</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3858421261520819</v>
+        <v>0.3873021122865055</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2668577342221259</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.313605660490031</v>
+        <v>-6.309955695153972</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.432656674089511</v>
+        <v>0.4341166602239346</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1435665994049954</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.26090879335874</v>
+        <v>-6.257258828022681</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4614363991793526</v>
+        <v>0.4628963853137762</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09086973227370426</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.150180387503247</v>
+        <v>-6.013493386039237</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5015084698686008</v>
+        <v>0.5561832704542047</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09086973227370426</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.048417567225952</v>
+        <v>-5.911730565761942</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5443379118995346</v>
+        <v>0.599012712485139</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.07765066388127556</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.798567173276878</v>
+        <v>-5.661880171812867</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6370201444628667</v>
+        <v>0.6916949450484706</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.07765066388127556</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.622675080809445</v>
+        <v>-5.485988079345434</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7109761049704884</v>
+        <v>0.7656509055560927</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.07765066388127556</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.451228617786982</v>
+        <v>-5.314541616322971</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7928821962340273</v>
+        <v>0.8475569968196317</v>
       </c>
       <c r="F1921" t="n">
         <v>0.09379579914118757</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.376939052048643</v>
+        <v>-5.240252050584632</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.82161850014566</v>
+        <v>0.8762933007312643</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1680853648795269</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.313303309814708</v>
+        <v>-5.176616308350697</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8517675980935508</v>
+        <v>0.9064423986791557</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2317211071134614</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.201876550488788</v>
+        <v>-5.065189549024777</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8775325606077145</v>
+        <v>0.9322073611933193</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2317211071134614</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.212379173554077</v>
+        <v>-5.075692172090066</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8750745880064765</v>
+        <v>0.9297493885920809</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2212184840481725</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.140136605382883</v>
+        <v>-5.003449603918871</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9079009291097746</v>
+        <v>0.962575729695379</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2212184840481725</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.122422918505017</v>
+        <v>-4.985735917041006</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9156649877782606</v>
+        <v>0.9703397883638651</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2243998129450893</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.01361803302529</v>
+        <v>-4.876931031561279</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.956185013190145</v>
+        <v>1.010859813775749</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2243998129450893</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.79359723498828</v>
+        <v>-4.656910233524268</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.045772369415563</v>
+        <v>1.100447170001168</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3656196580130696</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.660729545925002</v>
+        <v>-4.524042544460991</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.114813627842698</v>
+        <v>1.169488428428302</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3656196580130696</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.540556462560503</v>
+        <v>-4.403869461096492</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.164028705628799</v>
+        <v>1.218703506214404</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4857927413775685</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.405303101230526</v>
+        <v>-4.268616099766515</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.22821815272223</v>
+        <v>1.282892953307834</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6210461027075456</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.465177928588218</v>
+        <v>-4.328490927124207</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.190305713180579</v>
+        <v>1.244980513766183</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5611712753498534</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.345357697677382</v>
+        <v>-4.20867069621337</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.253522974779122</v>
+        <v>1.308197775364726</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5611712753498534</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.347827404139188</v>
+        <v>-4.211140402675176</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.160179291516841</v>
+        <v>1.214854092102446</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5587015688880472</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.416197590463198</v>
+        <v>-4.279510588999186</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.052093078472538</v>
+        <v>1.106767879058143</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5679772679242622</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.429985643310244</v>
+        <v>-4.293298641846233</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.037014565965611</v>
+        <v>1.091689366551216</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5679772679242622</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.485505719202834</v>
+        <v>-4.348818717738823</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.151837372300778</v>
+        <v>1.206512172886382</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5679772679242622</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.310031459410364</v>
+        <v>-4.173344457946353</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.226594308209553</v>
+        <v>1.281269108795158</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5679772679242622</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.420967712051613</v>
+        <v>-4.284280710587602</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.157961835914261</v>
+        <v>1.212636636499865</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5679772679242622</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.387304166579331</v>
+        <v>-4.25061716511532</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.099965567504623</v>
+        <v>1.154640368090228</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6016408133965441</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.327451547375608</v>
+        <v>-4.190764545911597</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134079001618245</v>
+        <v>1.18875380220385</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6016408133965441</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.24120808434923</v>
+        <v>-4.104521082885219</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.163522657402656</v>
+        <v>1.218197457988261</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6016408133965441</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.28651490374821</v>
+        <v>-4.149827902284199</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.13717570508759</v>
+        <v>1.191850505673195</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5608306503873133</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.315548008450511</v>
+        <v>-4.1788610069865</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.126114336239771</v>
+        <v>1.180789136825376</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5608306503873133</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.222737526999651</v>
+        <v>-4.08605052553564</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.092511220711481</v>
+        <v>1.147186021297085</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6536411318381726</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.267126996329079</v>
+        <v>-4.130439994865068</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.07662890890431</v>
+        <v>1.131303709489915</v>
       </c>
       <c r="F1947" t="n">
         <v>0.609251662508745</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.383668601434421</v>
+        <v>-4.24698159997041</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.025087975373896</v>
+        <v>1.079762775959501</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4927100574034022</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.271291600251748</v>
+        <v>-4.134604598787737</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.075530071677633</v>
+        <v>1.130204872263237</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4927100574034022</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.299071998153101</v>
+        <v>-4.16238499668909</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.075915114285631</v>
+        <v>1.130589914871236</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4649296595020492</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.41745267088324</v>
+        <v>-4.280765669419228</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8669185651942288</v>
+        <v>0.9215933657798334</v>
       </c>
       <c r="F1951" t="n">
         <v>0.397711807351073</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.526066749326571</v>
+        <v>-4.389379747862559</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9436225945361021</v>
+        <v>0.9982973951217065</v>
       </c>
       <c r="F1952" t="n">
         <v>0.397711807351073</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.490657711078428</v>
+        <v>-4.353970709614416</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9722992359376821</v>
+        <v>1.026974036523287</v>
       </c>
       <c r="F1953" t="n">
         <v>0.397711807351073</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.452274048520277</v>
+        <v>-4.315587047056265</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9850721423033113</v>
+        <v>1.039746942888916</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4360954699092242</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.275157718485111</v>
+        <v>-4.138470717021099</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.05264770316268</v>
+        <v>1.107322503748284</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4360954699092242</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.320249963318656</v>
+        <v>-4.183562961854645</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.035294196991174</v>
+        <v>1.089968997576779</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3741994267398344</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.140874542079889</v>
+        <v>-4.004187540615877</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.100831340793096</v>
+        <v>1.1555061413787</v>
       </c>
       <c r="F1957" t="n">
         <v>0.530976184910553</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.185888755600494</v>
+        <v>-4.049201754136483</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.063633110716443</v>
+        <v>1.118307911302048</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5006272895959484</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.452893265872929</v>
+        <v>-4.316206264408918</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9625228689464151</v>
+        <v>1.01719766953202</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3062642515529998</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.554091047310102</v>
+        <v>-4.417404045846091</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9212476782680474</v>
+        <v>0.975922478853652</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2378554380076806</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.54758008069579</v>
+        <v>-4.410893079231778</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9214520264680892</v>
+        <v>0.9761268270536938</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2378554380076806</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.528541952988492</v>
+        <v>-4.391854951524481</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.925591996759253</v>
+        <v>0.9802667973448576</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1796718266764861</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.581057755263313</v>
+        <v>-4.444370753799301</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.023880077483515</v>
+        <v>1.07855487806912</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1796718266764861</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.594924516597231</v>
+        <v>-4.458237515133219</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.019166701936081</v>
+        <v>1.073841502521686</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1418139099426631</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.550120345057301</v>
+        <v>-4.413433343593289</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.043096900948979</v>
+        <v>1.097771701534584</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1418139099426631</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.402377374822298</v>
+        <v>-4.265690373358287</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.00014431032018</v>
+        <v>1.054819110905785</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3096212671775463</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.486198596096997</v>
+        <v>-4.349511594632985</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9694094433417817</v>
+        <v>1.024084243927386</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3096212671775463</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.480045890044212</v>
+        <v>-4.343358888580201</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9725328741545538</v>
+        <v>1.027207674740158</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3157739732303306</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.496855188194714</v>
+        <v>-4.360168186730703</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9648896316344633</v>
+        <v>1.019564432220068</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2989646750798289</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.434557189418592</v>
+        <v>-4.29787018795458</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.056144384941733</v>
+        <v>1.110819185527337</v>
       </c>
       <c r="F1970" t="n">
         <v>0.344258939354271</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.232766991753434</v>
+        <v>-4.096079990289422</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9391524657219232</v>
+        <v>0.9938272663075278</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5422771315234254</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.283653704439629</v>
+        <v>-4.146966702975617</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9890880129696207</v>
+        <v>1.043762813555225</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4913904188372309</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.197042961789822</v>
+        <v>-4.06035596032581</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.038360046145587</v>
+        <v>1.093034846731191</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5700161500423891</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.257252259795107</v>
+        <v>-4.120565258331095</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.012812307768145</v>
+        <v>1.067487108353749</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5098068520371046</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.18083021336318</v>
+        <v>-4.044143211899168</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.041872744380844</v>
+        <v>1.096547544966449</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5098068520371046</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.136457081724611</v>
+        <v>-3.9997700802606</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.059484864471708</v>
+        <v>1.114159665057312</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5541799836756732</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.158937432583496</v>
+        <v>-4.022250431119485</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.044886518266744</v>
+        <v>1.099561318852349</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5541799836756732</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.11128170202244</v>
+        <v>-3.974594700558429</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.070330567518971</v>
+        <v>1.125005368104576</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6018357142367289</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.010763543523685</v>
+        <v>-3.874076542059674</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.115430204293198</v>
+        <v>1.170105004878802</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7023538727354834</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.994858214091333</v>
+        <v>-3.858171212627322</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.108547008542011</v>
+        <v>1.163221809127616</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6232412120262445</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.950019812482935</v>
+        <v>-3.813332811018924</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.130580071795999</v>
+        <v>1.185254872381603</v>
       </c>
       <c r="F1981" t="n">
         <v>0.627784644971114</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.969518268724943</v>
+        <v>-3.832831267260932</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.126941628930274</v>
+        <v>1.181616429515878</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5797000036912097</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.925315431639043</v>
+        <v>-3.788628430175031</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.150502366292471</v>
+        <v>1.205177166878076</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6239028407771101</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.962294459302486</v>
+        <v>-3.825607457838474</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.134120755696341</v>
+        <v>1.188795556281946</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6608767425684406</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.804003041763214</v>
+        <v>-3.667316040299202</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.24868508789509</v>
+        <v>1.303359888480694</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6608767425684406</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.596361038128737</v>
+        <v>-3.459674036664726</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.330182593943133</v>
+        <v>1.384857394528738</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8685187462029168</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.545328945406209</v>
+        <v>-3.408641943942198</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.345543659270415</v>
+        <v>1.400218459856019</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9195508389254448</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.480104764279004</v>
+        <v>-3.343417762814992</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.388820735814002</v>
+        <v>1.443495536399606</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9847750200526504</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.44267774420787</v>
+        <v>-3.305990742743858</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.399752516141736</v>
+        <v>1.45442731672734</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9900265580818322</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.462789400242578</v>
+        <v>-3.326102398778567</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.392964646059093</v>
+        <v>1.447639446644697</v>
       </c>
       <c r="F1990" t="n">
         <v>1.001053903079251</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.409044585815373</v>
+        <v>-3.272357584351362</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.575020342851185</v>
+        <v>1.62969514343679</v>
       </c>
       <c r="F1991" t="n">
         <v>1.011117212519713</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.334262324790361</v>
+        <v>-3.197575323326349</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.725046156479008</v>
+        <v>1.779720957064612</v>
       </c>
       <c r="F1992" t="n">
         <v>1.085899473544726</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.308178240526553</v>
+        <v>-3.171491239062541</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.72718776619839</v>
+        <v>1.781862566783994</v>
       </c>
       <c r="F1993" t="n">
         <v>1.085899473544726</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.220300327417432</v>
+        <v>-3.083613325953421</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.760532127025817</v>
+        <v>1.815206927611422</v>
       </c>
       <c r="F1994" t="n">
         <v>1.201825115968077</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.211407866024149</v>
+        <v>-3.074720864560137</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.781643517309922</v>
+        <v>1.836318317895527</v>
       </c>
       <c r="F1995" t="n">
         <v>1.201825115968077</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.379883982994027</v>
+        <v>-3.243196981530015</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.706108117926555</v>
+        <v>1.76078291851216</v>
       </c>
       <c r="F1996" t="n">
         <v>1.173877280251497</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.682084454132443</v>
+        <v>-2.545397452668432</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.96649762665905</v>
+        <v>2.021172427244655</v>
       </c>
       <c r="F1997" t="n">
         <v>1.103529220881086</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.659363350449291</v>
+        <v>-2.522676348985279</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.966250090629216</v>
+        <v>2.02092489121482</v>
       </c>
       <c r="F1998" t="n">
         <v>1.103529220881086</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.788565163743333</v>
+        <v>-2.651878162279322</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.073475491162768</v>
+        <v>2.128150291748372</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9743274075870436</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.943346170521589</v>
+        <v>-2.806659169057578</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.048640910945112</v>
+        <v>2.103315711530716</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9409597335325675</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.936291480306415</v>
+        <v>-2.799604478842404</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.048138143020727</v>
+        <v>2.102812943606331</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9480144237477413</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.909340255979927</v>
+        <v>-2.772653254515916</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.068924786396064</v>
+        <v>2.123599586981668</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9628947697754604</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.045293264036244</v>
+        <v>-2.908606262572232</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.198646715318497</v>
+        <v>2.253321515904101</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9628947697754604</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.067701381841116</v>
+        <v>-2.931014380377104</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.181800163099541</v>
+        <v>2.236474963685145</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9628947697754604</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.095925617418716</v>
+        <v>-2.959238615954705</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.172564468418138</v>
+        <v>2.227239269003743</v>
       </c>
       <c r="F2005" t="n">
         <v>0.980871522226769</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.105366543307246</v>
+        <v>-2.968679541843235</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.225041815784573</v>
+        <v>2.279716616370178</v>
       </c>
       <c r="F2006" t="n">
         <v>1.103298639770161</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.157640150642887</v>
+        <v>-3.020953149178876</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.207023467395618</v>
+        <v>2.261698267981222</v>
       </c>
       <c r="F2007" t="n">
         <v>1.051025032434519</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.233970128243793</v>
+        <v>-3.097283126779782</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.17460328924903</v>
+        <v>2.229278089834635</v>
       </c>
       <c r="F2008" t="n">
         <v>1.051025032434519</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.436223848568146</v>
+        <v>-3.299536847104135</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.088522030722152</v>
+        <v>2.143196831307756</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8487713121101657</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.597792274095402</v>
+        <v>-3.46110527263139</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.022328670721402</v>
+        <v>2.077003471307006</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7219883883122863</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.730093566192955</v>
+        <v>-3.593406564728943</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.982481560748299</v>
+        <v>2.037156361333904</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7219883883122863</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.915961877032185</v>
+        <v>-3.779274875568174</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.900139433195547</v>
+        <v>1.954814233781152</v>
       </c>
       <c r="F2012" t="n">
         <v>0.5634227949923386</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.943862664141658</v>
+        <v>-3.807175662677647</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.88750315947876</v>
+        <v>1.942177960064364</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5288258708494038</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.066388766844552</v>
+        <v>-3.92970176538054</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.835257162374801</v>
+        <v>1.889931962960406</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4062997681465099</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.296903263030141</v>
+        <v>-4.160216261566129</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.809757323491069</v>
+        <v>1.864432124076674</v>
       </c>
       <c r="F2015" t="n">
         <v>0.1757852719609212</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.553624081024966</v>
+        <v>-4.416937079560952</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.847380715294986</v>
+        <v>1.902055515880592</v>
       </c>
       <c r="F2016" t="n">
         <v>0.06737069781710636</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.707610498801106</v>
+        <v>-4.570923497337093</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.85476641733017</v>
+        <v>1.909441217915775</v>
       </c>
       <c r="F2017" t="n">
         <v>0.06737069781710636</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.65708859497344</v>
+        <v>-4.520401593509427</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.861026380981357</v>
+        <v>1.915701181566963</v>
       </c>
       <c r="F2018" t="n">
         <v>0.06737069781710636</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.909563748981165</v>
+        <v>-4.772876747517151</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.771906808433682</v>
+        <v>1.826581609019287</v>
       </c>
       <c r="F2019" t="n">
         <v>0.06737069781710636</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.202459505460577</v>
+        <v>-5.065772503996564</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.65595904036086</v>
+        <v>1.710633840946465</v>
       </c>
       <c r="F2020" t="n">
         <v>0.06737069781710636</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.360003577190018</v>
+        <v>-5.223316575726005</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.597063153896405</v>
+        <v>1.651737954482011</v>
       </c>
       <c r="F2021" t="n">
         <v>0.0004688926768318669</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.637967972773292</v>
+        <v>-5.501280971309279</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.480955248399285</v>
+        <v>1.53563004898489</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.08915084160865239</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.754935665412183</v>
+        <v>-5.61824866394817</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.596372228042773</v>
+        <v>1.651047028628378</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.08915084160865239</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.839653607633136</v>
+        <v>-5.702966606169123</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.557331689118206</v>
+        <v>1.612006489703811</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.1742668705366988</v>
@@ -48126,10 +48126,10 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.921588425902019</v>
+        <v>-5.784901424438006</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.534787179379144</v>
+        <v>1.589461979964749</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.1842016161237789</v>
@@ -48149,10 +48149,10 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.023564548150427</v>
+        <v>-5.886877546686414</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.502922368935683</v>
+        <v>1.557597169521288</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.2861777383721865</v>
@@ -48172,10 +48172,10 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.913558264673205</v>
+        <v>-5.776871263209192</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.539077769570747</v>
+        <v>1.593752570156352</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.2629731664549113</v>
@@ -48195,10 +48195,10 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.77049868893228</v>
+        <v>-5.633811687468267</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.600551610589092</v>
+        <v>1.655226411174697</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.254959739864932</v>
@@ -48218,10 +48218,10 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.469051963460442</v>
+        <v>-5.332364961996429</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.728391183660362</v>
+        <v>1.783065984245968</v>
       </c>
       <c r="F2029" t="n">
         <v>0.04648698560690523</v>
@@ -48241,10 +48241,10 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.493642207695626</v>
+        <v>-5.356955206231613</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.719526263719</v>
+        <v>1.774201064304605</v>
       </c>
       <c r="F2030" t="n">
         <v>0.04648698560690523</v>
@@ -48264,10 +48264,10 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.442603831689106</v>
+        <v>-5.305916830225093</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.740784518501363</v>
+        <v>1.795459319086968</v>
       </c>
       <c r="F2031" t="n">
         <v>0.04648698560690523</v>
@@ -48287,10 +48287,10 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.401464536822475</v>
+        <v>-5.264777535358462</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.77627833532216</v>
+        <v>1.830953135907766</v>
       </c>
       <c r="F2032" t="n">
         <v>0.08762628047353604</v>
@@ -48310,10 +48310,10 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.290858396742873</v>
+        <v>-5.15417139527886</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.636704787477936</v>
+        <v>1.691379588063541</v>
       </c>
       <c r="F2033" t="n">
         <v>0.1982324205531381</v>
@@ -48333,10 +48333,10 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.421439131273716</v>
+        <v>-5.284752129809703</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.587974537739563</v>
+        <v>1.642649338325168</v>
       </c>
       <c r="F2034" t="n">
         <v>0.06765168602229554</v>
@@ -48356,10 +48356,10 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.256942797082754</v>
+        <v>-5.120255795618741</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.63819989049203</v>
+        <v>1.692874691077635</v>
       </c>
       <c r="F2035" t="n">
         <v>0.06765168602229554</v>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.284312729767186</v>
+        <v>-5.147625728303173</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.626439627854686</v>
+        <v>1.681114428440292</v>
       </c>
       <c r="F2036" t="n">
         <v>0.06765168602229554</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.294697924657076</v>
+        <v>-5.158010923193062</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.632154329023803</v>
+        <v>1.686829129609408</v>
       </c>
       <c r="F2037" t="n">
         <v>0.05726649113240623</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.313286083379301</v>
+        <v>-5.176599081915287</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.695556071311338</v>
+        <v>1.750230871896944</v>
       </c>
       <c r="F2038" t="n">
         <v>0.03867833241018087</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.313584630075336</v>
+        <v>-5.176897628611323</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.692305663451223</v>
+        <v>1.746980464036828</v>
       </c>
       <c r="F2039" t="n">
         <v>0.03867833241018087</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.212761496384909</v>
+        <v>-5.076074494920896</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.737165811866785</v>
+        <v>1.79184061245239</v>
       </c>
       <c r="F2040" t="n">
         <v>0.05114254789453471</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.021980135632502</v>
+        <v>-4.885293134168489</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.813607609646291</v>
+        <v>1.868282410231896</v>
       </c>
       <c r="F2041" t="n">
         <v>0.2419239086469421</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.003463281590681</v>
+        <v>-4.866776280126668</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.800851197000616</v>
+        <v>1.855525997586221</v>
       </c>
       <c r="F2042" t="n">
         <v>0.2548540380721503</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.978270097089363</v>
+        <v>-4.84158309562535</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.845895407413201</v>
+        <v>1.900570207998807</v>
       </c>
       <c r="F2043" t="n">
         <v>0.2800472225734686</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.966215970176401</v>
+        <v>-4.829528968712387</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.844403626079824</v>
+        <v>1.899078426665429</v>
       </c>
       <c r="F2044" t="n">
         <v>0.2921013494864315</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.972839216866759</v>
+        <v>-4.836152215402746</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.843634957587817</v>
+        <v>1.898309758173422</v>
       </c>
       <c r="F2045" t="n">
         <v>0.2854781027960731</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.869958627338166</v>
+        <v>-4.733271625874153</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.897638219277137</v>
+        <v>1.952313019862742</v>
       </c>
       <c r="F2046" t="n">
         <v>0.388358692324666</v>
@@ -48632,10 +48632,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.893400666518253</v>
+        <v>-4.75671366505424</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.908464073778696</v>
+        <v>1.963138874364301</v>
       </c>
       <c r="F2047" t="n">
         <v>0.388358692324666</v>
@@ -48655,10 +48655,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.911473174809864</v>
+        <v>-4.774786173345851</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901235070462051</v>
+        <v>1.955909871047656</v>
       </c>
       <c r="F2048" t="n">
         <v>0.388358692324666</v>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.142646968686496</v>
+        <v>-5.005959967222483</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.769017466504865</v>
+        <v>1.82369226709047</v>
       </c>
       <c r="F2049" t="n">
         <v>0.388358692324666</v>
@@ -48701,10 +48701,10 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.111360948146041</v>
+        <v>-4.974673946682028</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.788554493717987</v>
+        <v>1.843229294303593</v>
       </c>
       <c r="F2050" t="n">
         <v>0.4196447128651214</v>
@@ -48724,10 +48724,10 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.099999390310784</v>
+        <v>-4.963312388846771</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.892270116424994</v>
+        <v>1.946944917010599</v>
       </c>
       <c r="F2051" t="n">
         <v>0.4310062707003783</v>
@@ -48747,10 +48747,10 @@
         <v>3.918235110616684</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.099999390310784</v>
+        <v>-4.963312388846771</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.892270116424994</v>
+        <v>1.946944917010599</v>
       </c>
       <c r="F2052" t="n">
         <v>0.4310062707003783</v>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.2%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.3%</t>
+          <t>419.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.9%</t>
+          <t>-659.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.5%</t>
+          <t>-183.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.1%</t>
+          <t>-144.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-180.9%</t>
+          <t>-179.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.9%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803195</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705329</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793907</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917055</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405963</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265648</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284882</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.416937079560952</v>
+        <v>-4.491187423183629</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.902055515880592</v>
+        <v>1.872355378431521</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.08432196263373504</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.709609190708984</v>
+        <v>3.719779949598961</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.570923497337093</v>
+        <v>-4.645173840959769</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.909441217915775</v>
+        <v>1.879741080466705</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.08432196263373504</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.778589459854624</v>
+        <v>3.788760218744601</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.520401593509427</v>
+        <v>-4.594651937132103</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.915701181566963</v>
+        <v>1.886001044117892</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.08432196263373504</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.764640661974745</v>
+        <v>3.774811420864722</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.772876747517151</v>
+        <v>-4.847127091139828</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.826581609019287</v>
+        <v>1.796881471570216</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.08432196263373504</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.776511151030159</v>
+        <v>3.786681909920136</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.065772503996564</v>
+        <v>-5.14002284761924</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.710633840946465</v>
+        <v>1.680933703497395</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.06737069781710636</v>
+        <v>0.08432196263373504</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.777721685549102</v>
+        <v>3.78789244443908</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.223316575726005</v>
+        <v>-5.297566919348681</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.651737954482011</v>
+        <v>1.62203781703294</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.0004688926768318669</v>
+        <v>0.01742015749346054</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.741702344692259</v>
+        <v>3.751873103582236</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.501280971309279</v>
+        <v>-5.575531314931955</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.53563004898489</v>
+        <v>1.50592991153582</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.08915084160865239</v>
+        <v>-0.07219957679202371</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.683008356857158</v>
+        <v>3.693179115747135</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.61824866394817</v>
+        <v>-5.692499007570846</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.651047028628378</v>
+        <v>1.621346891179308</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.08915084160865239</v>
+        <v>-0.07219957679202371</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.845212413556202</v>
+        <v>3.855383172446179</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.702966606169123</v>
+        <v>-5.777216949791799</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.612006489703811</v>
+        <v>1.58230635225474</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1742668705366988</v>
+        <v>-0.1573156057200701</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.788989434163188</v>
+        <v>3.799160193053166</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.784901424438006</v>
+        <v>-5.859151768060682</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.589461979964749</v>
+        <v>1.559761842515679</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1842016161237789</v>
+        <v>-0.1672503513071503</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.793258004379431</v>
+        <v>3.803428763269409</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.886877546686414</v>
+        <v>-5.96112789030909</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.557597169521288</v>
+        <v>1.527897032072218</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2861777383721865</v>
+        <v>-0.2692264735555578</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.740997969486289</v>
+        <v>3.751168728376267</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.776871263209192</v>
+        <v>-5.851121606831868</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.593752570156352</v>
+        <v>1.564052432707282</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2629731664549113</v>
+        <v>-0.2460219016382826</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.74707359988083</v>
+        <v>3.757244358770807</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.633811687468267</v>
+        <v>-5.708062031090943</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.655226411174697</v>
+        <v>1.625526273725626</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.254959739864932</v>
+        <v>-0.2380084750483034</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.756131666556792</v>
+        <v>3.766302425446769</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.332364961996429</v>
+        <v>-5.406615305619106</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.783065984245968</v>
+        <v>1.753365846796897</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.0634382504235339</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.94426058472243</v>
+        <v>3.954431343612407</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.356955206231613</v>
+        <v>-5.431205549854289</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.774201064304605</v>
+        <v>1.744500926855534</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.0634382504235339</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.945231762475141</v>
+        <v>3.955402521365118</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.305916830225093</v>
+        <v>-5.380167173847769</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.795459319086968</v>
+        <v>1.765759181637897</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.04648698560690523</v>
+        <v>0.0634382504235339</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.946074666854896</v>
+        <v>3.956245425744873</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.264777535358462</v>
+        <v>-5.339027878981138</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.830953135907766</v>
+        <v>1.801252998458695</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.08762628047353604</v>
+        <v>0.1045775452901647</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.98979634264902</v>
+        <v>3.999967101538997</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.15417139527886</v>
+        <v>-5.228421738901536</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.691379588063541</v>
+        <v>1.661679450614471</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1982324205531381</v>
+        <v>0.2151836853697667</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.872344022820716</v>
+        <v>3.882514781710693</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.284752129809703</v>
+        <v>-5.359002473432379</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.642649338325168</v>
+        <v>1.612949200876097</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.08460295083892422</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.797497626176173</v>
+        <v>3.807668385066151</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.120255795618741</v>
+        <v>-5.194506139241417</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.692874691077635</v>
+        <v>1.663174553628564</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.08460295083892422</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781924445252256</v>
+        <v>3.792095204142234</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.147625728303173</v>
+        <v>-5.221876071925849</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.681114428440292</v>
+        <v>1.651414290991221</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.06765168602229554</v>
+        <v>0.08460295083892422</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.781112155688686</v>
+        <v>3.791282914578663</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.158010923193062</v>
+        <v>-5.232261266815739</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.686829129609408</v>
+        <v>1.657128992160338</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.05726649113240623</v>
+        <v>0.0742177559490349</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784749817879825</v>
+        <v>3.794920576769802</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.176599081915287</v>
+        <v>-5.250849425537964</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.750230871896944</v>
+        <v>1.720530734447873</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.03867833241018087</v>
+        <v>0.05562959722680955</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.844433928422915</v>
+        <v>3.854604687312892</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.176897628611323</v>
+        <v>-5.251147972234</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.746980464036828</v>
+        <v>1.717280326587757</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.03867833241018087</v>
+        <v>0.05562959722680955</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.841302939241213</v>
+        <v>3.851473698131191</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.076074494920896</v>
+        <v>-5.150324838543572</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.79184061245239</v>
+        <v>1.76214047500332</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.05114254789453471</v>
+        <v>0.06809381271116338</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.853312363471217</v>
+        <v>3.863483122361194</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.885293134168489</v>
+        <v>-4.959543477791165</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.868282410231896</v>
+        <v>1.838582272782826</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2419239086469421</v>
+        <v>0.2588751734635708</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.967910433401205</v>
+        <v>3.978081192291182</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.866776280126668</v>
+        <v>-4.941026623749345</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.855525997586221</v>
+        <v>1.825825860137151</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2548540380721503</v>
+        <v>0.271805302888779</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.955505356793926</v>
+        <v>3.965676115683904</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.84158309562535</v>
+        <v>-4.915833439248027</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.900570207998807</v>
+        <v>1.870870070549736</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2800472225734686</v>
+        <v>0.2969984873900973</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.005588204106775</v>
+        <v>4.015758962996753</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.829528968712387</v>
+        <v>-4.903779312335064</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.899078426665429</v>
+        <v>1.869378289216359</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2921013494864315</v>
+        <v>0.3090526143030601</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.006507248155991</v>
+        <v>4.016678007045968</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.836152215402746</v>
+        <v>-4.910402559025422</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.898309758173422</v>
+        <v>1.868609620724352</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.2854781027960731</v>
+        <v>0.3024293676127018</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.004413930325912</v>
+        <v>4.014584689215889</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.733271625874153</v>
+        <v>-4.807521969496829</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.952313019862742</v>
+        <v>1.922612882413671</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4053099571412947</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.07899330992095</v>
+        <v>4.089164068810927</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.75671366505424</v>
+        <v>-4.830964008676916</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.963138874364301</v>
+        <v>1.933438736915231</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4053099571412947</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.099195980094544</v>
+        <v>4.109366738984521</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.774786173345851</v>
+        <v>-4.849036516968527</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.955909871047656</v>
+        <v>1.926209733598586</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4053099571412947</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.099195980094544</v>
+        <v>4.109366738984521</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.005959967222483</v>
+        <v>-5.08021031084516</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.82369226709047</v>
+        <v>1.7939921296414</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.388358692324666</v>
+        <v>0.4053099571412947</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.059447893688011</v>
+        <v>4.069618652577988</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.974673946682028</v>
+        <v>-5.048924290304704</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.843229294303593</v>
+        <v>1.813529156854522</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4196447128651214</v>
+        <v>0.4365959776817501</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.085242125009224</v>
+        <v>4.095412883899201</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677819</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.963312388846771</v>
+        <v>-5.037562732469447</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.946944917010599</v>
+        <v>1.917244779561529</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.4310062707003783</v>
+        <v>0.447957535517007</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.191230059283282</v>
+        <v>4.201400818173259</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.58649221705556</v>
+        <v>3.774852822206141</v>
       </c>
       <c r="C2052" t="n">
         <v>3.918235110616684</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.963312388846771</v>
+        <v>-4.975895876008487</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.946944917010599</v>
+        <v>1.927520335899542</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.4310062707003783</v>
+        <v>0.447957535517007</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.911298907603052</v>
+        <v>4.187009631926888</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240810.xlsx
+++ b/tame_output/ON/bt/strategyON_20240810.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-627.7%</t>
+          <t>-613.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.9%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.2%</t>
+          <t>-642.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-251.5%</t>
+          <t>-245.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-183.5%</t>
+          <t>-175.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-144.5%</t>
+          <t>-151.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-179.2%</t>
+          <t>-180.9%</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5983743381632924</v>
+        <v>-0.4594793927979829</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.881622602747662</v>
+        <v>2.937180580893785</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.586985101508491</v>
+        <v>-0.4480901561431815</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.884003093528822</v>
+        <v>2.939561071674946</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.004739125055328</v>
+        <v>-0.8658441796900185</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.714828375615151</v>
+        <v>2.770386353761275</v>
       </c>
       <c r="F1847" t="n">
         <v>1.126693817913202</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.29487079166076</v>
+        <v>-1.15597584629545</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.5986419255719</v>
+        <v>2.654199903718024</v>
       </c>
       <c r="F1848" t="n">
         <v>1.150775612653382</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.502874850013837</v>
+        <v>-1.363979904648527</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.520332446784594</v>
+        <v>2.575890424930718</v>
       </c>
       <c r="F1849" t="n">
         <v>1.150775612653382</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.565053261174807</v>
+        <v>-1.426158315809497</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.490542538658195</v>
+        <v>2.546100516804318</v>
       </c>
       <c r="F1850" t="n">
         <v>1.088597201492412</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.93112198831946</v>
+        <v>-1.79222704295415</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.337199347106782</v>
+        <v>2.392757325252906</v>
       </c>
       <c r="F1851" t="n">
         <v>0.722528474347759</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.139612769771144</v>
+        <v>-2.000717824405834</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.274141324264877</v>
+        <v>2.329699302411001</v>
       </c>
       <c r="F1852" t="n">
         <v>0.5140376928960746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.386813954536366</v>
+        <v>-2.247919009171056</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.183359600767357</v>
+        <v>2.238917578913481</v>
       </c>
       <c r="F1853" t="n">
         <v>0.534191046394887</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.879198982560462</v>
+        <v>-2.740304037195153</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.98751198160145</v>
+        <v>2.043069959747574</v>
       </c>
       <c r="F1854" t="n">
         <v>0.04180601837079029</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.264379373490535</v>
+        <v>-3.125484428125225</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.831982364042285</v>
+        <v>1.887540342188408</v>
       </c>
       <c r="F1855" t="n">
         <v>0.04180601837079029</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.514250053505116</v>
+        <v>-3.375355108139807</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.733803215491068</v>
+        <v>1.789361193637192</v>
       </c>
       <c r="F1856" t="n">
         <v>0.07806873820125354</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.720761830392138</v>
+        <v>-3.581866885026828</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.647304563392518</v>
+        <v>1.702862541538641</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.128443038685768</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.04010590547264</v>
+        <v>-3.901210960107329</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.521339860060576</v>
+        <v>1.5768978382067</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.128443038685768</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.426315736748415</v>
+        <v>-4.287420791383104</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.353188815017671</v>
+        <v>1.408746793163795</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.2192159784032113</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.661009730880967</v>
+        <v>-4.522114785515656</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.24759599236674</v>
+        <v>1.303153970512864</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.2128797111739561</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.99667237811142</v>
+        <v>-4.857777432746109</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.111911525130524</v>
+        <v>1.167469503276648</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.2808106966628609</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.073116708314291</v>
+        <v>-4.93422176294898</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.087821353283617</v>
+        <v>1.143379331429741</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.200365187569199</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.438244090953038</v>
+        <v>-5.299349145587727</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.94102491523395</v>
+        <v>0.996582893380074</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4966759718682116</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.846832868133717</v>
+        <v>-5.707937922768406</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7763509483764377</v>
+        <v>0.8319089265225617</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.90526474904889</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.960593280156582</v>
+        <v>-5.821698334791271</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7260322160387522</v>
+        <v>0.7815901941848762</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.90526474904889</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.376985154443579</v>
+        <v>-6.238090209078268</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5574695169328305</v>
+        <v>0.6130274950789545</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.90526474904889</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.738158784260567</v>
+        <v>-6.599263838895256</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4232587556747145</v>
+        <v>0.4788167338208384</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.90526474904889</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.081417303903586</v>
+        <v>-6.942522358538275</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.282054912963202</v>
+        <v>0.3376128911093264</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.90526474904889</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.12962012114593</v>
+        <v>-6.990725175780619</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2611787061212656</v>
+        <v>0.3167366842673895</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.90526474904889</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.426281462956127</v>
+        <v>-7.287386517590816</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1462931453263949</v>
+        <v>0.2018511234725189</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.9740078847827686</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.61300117126543</v>
+        <v>-7.474106225900119</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.06757895746827058</v>
+        <v>0.1231369356143945</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.9740078847827686</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.996002560008061</v>
+        <v>-7.85710761464275</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.08572369935036583</v>
+        <v>-0.03016572120424188</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.9740078847827686</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.000489005209449</v>
+        <v>-7.861594059844139</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.08494676145949143</v>
+        <v>-0.02938878331336747</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.9784943299841573</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.360019327713452</v>
+        <v>-8.22112438234814</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2234085871630422</v>
+        <v>-0.1678506090169183</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.9784943299841573</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.410368391167674</v>
+        <v>-8.271473445802362</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2356321925875533</v>
+        <v>-0.1800742144414293</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.028843393438379</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.50798766858907</v>
+        <v>-8.369092723223758</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2716381529343432</v>
+        <v>-0.2160801747882188</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.126462670859776</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.562059168097429</v>
+        <v>-8.423164222732117</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2903731964161143</v>
+        <v>-0.2348152182699903</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.180534170368135</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.766317343427293</v>
+        <v>-8.627422398061981</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3665632694294176</v>
+        <v>-0.3110052912832932</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.308173114982124</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.799970181935766</v>
+        <v>-8.661075236570454</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.375541850348371</v>
+        <v>-0.3199838722022466</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.408586482899162</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.726500350268317</v>
+        <v>-8.587605404903005</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3307822161879699</v>
+        <v>-0.2752242380418459</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.335116651231713</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.901624767654861</v>
+        <v>-8.762729822289549</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3862767623950707</v>
+        <v>-0.3307187842489467</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.510241068618257</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.13607686166935</v>
+        <v>-8.997181916304038</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4872767649024623</v>
+        <v>-0.4317187867563383</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.510241068618257</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.240451592695797</v>
+        <v>-9.101556647330485</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5356988480870171</v>
+        <v>-0.4801408699408931</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.614615799644703</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.402965058394381</v>
+        <v>-9.264070113029069</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5995884445278947</v>
+        <v>-0.5440304663817708</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.71224923006339</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.52900185176267</v>
+        <v>-9.390106906397358</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6473094332460958</v>
+        <v>-0.5917514550999718</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.686997607253647</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.471930079866739</v>
+        <v>-9.333035134501428</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6204903888013225</v>
+        <v>-0.5649324106551985</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.686997607253647</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.61360192159086</v>
+        <v>-9.474706976225548</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6786343523897123</v>
+        <v>-0.6230763742435883</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.686997607253647</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.564011077166025</v>
+        <v>-9.425116131800714</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6437446044549064</v>
+        <v>-0.5881866263087825</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.637406762828813</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.415092742694169</v>
+        <v>-9.276197797328857</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5972284043128466</v>
+        <v>-0.5416704261667227</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.60615717209364</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.189247589974759</v>
+        <v>-9.050352644609445</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4973112701888742</v>
+        <v>-0.4417532920427494</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.564230496506477</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.064668933637167</v>
+        <v>-8.925773988271853</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4463406630977782</v>
+        <v>-0.3907826849516538</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.564230496506477</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.117564221681453</v>
+        <v>-8.97866927631614</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4648650041533853</v>
+        <v>-0.4093070260072604</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.55927515041803</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.045431046393572</v>
+        <v>-8.906536101028259</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4302780297995965</v>
+        <v>-0.3747200516534717</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.55927515041803</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.974064653783925</v>
+        <v>-8.835169708418611</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4114687351496027</v>
+        <v>-0.3559107570034779</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.487908757808382</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.8806056197987</v>
+        <v>-8.741710674433387</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3839686028684204</v>
+        <v>-0.3284106247222955</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.487908757808382</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.869952438245269</v>
+        <v>-8.731057492879955</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3815418907464214</v>
+        <v>-0.325983912600297</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.487908757808382</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.772045399568778</v>
+        <v>-8.633150454203465</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3426793902492862</v>
+        <v>-0.2871214121031613</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.419923007947826</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.74809185859282</v>
+        <v>-8.609196913227507</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3324294677134092</v>
+        <v>-0.2768714895672848</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.395969466971869</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.484031920270024</v>
+        <v>-8.34513697490471</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.240065808546043</v>
+        <v>-0.1845078303999181</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.131909528649072</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.776952296765185</v>
+        <v>-7.638057351399872</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.03997900719559144</v>
+        <v>0.09553698534171629</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.131909528649072</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.736767998398995</v>
+        <v>-7.597873053033681</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.05639635042990898</v>
+        <v>0.1119543285760338</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.091725230282881</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.573368127459633</v>
+        <v>-7.434473182094319</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1211231200264109</v>
+        <v>0.1766810981725357</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.928325359343519</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.339886905230034</v>
+        <v>-7.20099195986472</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2224400377561029</v>
+        <v>0.2779980159022277</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6948441371139205</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.190220514222519</v>
+        <v>-7.051325568857205</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2794143838461496</v>
+        <v>0.3349723619922744</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6019406458713845</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.057945040591632</v>
+        <v>-6.919050095226319</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3276920600455315</v>
+        <v>0.3832500381916559</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4696651722404979</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.902206708031891</v>
+        <v>-6.763311762666577</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3928024537570649</v>
+        <v>0.4483604319031897</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3139268396807563</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.81724204130257</v>
+        <v>-6.678347095937257</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4396946616724517</v>
+        <v>0.4952526398185761</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2289621729514367</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.922832031075675</v>
+        <v>-6.783937085710361</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2694827361639911</v>
+        <v>0.3250407143101159</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3345521627245411</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.941566933194272</v>
+        <v>-6.802671987828958</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3105331171936387</v>
+        <v>0.3660910953397636</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3401481723846724</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.793626891786673</v>
+        <v>-6.654731946421359</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2498302110685109</v>
+        <v>0.3053881892146357</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3198272564761148</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.740657369532684</v>
+        <v>-6.60176242416737</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.262304033716628</v>
+        <v>0.3178620118627529</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2668577342221259</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.574869173572393</v>
+        <v>-6.43597422820708</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.321658700005651</v>
+        <v>0.3772166781517758</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2668577342221259</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.541505967093625</v>
+        <v>-6.402611021728311</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3494663369783018</v>
+        <v>0.4050243151244266</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2668577342221259</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.433246829971103</v>
+        <v>-6.294351884605789</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3873021122865055</v>
+        <v>0.4428600904326303</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2668577342221259</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.309955695153972</v>
+        <v>-6.171060749788658</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4341166602239346</v>
+        <v>0.4896746383700594</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1435665994049954</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.257258828022681</v>
+        <v>-6.118363882657367</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4628963853137762</v>
+        <v>0.518454363459901</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09086973227370426</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.013493386039237</v>
+        <v>-5.874598440673923</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5561832704542047</v>
+        <v>0.6117412486003295</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09086973227370426</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.911730565761942</v>
+        <v>-5.772835620396628</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.599012712485139</v>
+        <v>0.6545706906312634</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.07765066388127556</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.661880171812867</v>
+        <v>-5.522985226447553</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6916949450484706</v>
+        <v>0.7472529231945955</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.07765066388127556</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.485988079345434</v>
+        <v>-5.34709313398012</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7656509055560927</v>
+        <v>0.8212088837022176</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.07765066388127556</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.314541616322971</v>
+        <v>-5.175646670957657</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8475569968196317</v>
+        <v>0.9031149749657565</v>
       </c>
       <c r="F1921" t="n">
         <v>0.09379579914118757</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.240252050584632</v>
+        <v>-5.101357105219318</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8762933007312643</v>
+        <v>0.9318512788773892</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1680853648795269</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.176616308350697</v>
+        <v>-5.037721362985383</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9064423986791557</v>
+        <v>0.9620003768252801</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2317211071134614</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.065189549024777</v>
+        <v>-4.926294603659463</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9322073611933193</v>
+        <v>0.9877653393394439</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2317211071134614</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.075692172090066</v>
+        <v>-4.936797226724752</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9297493885920809</v>
+        <v>0.9853073667382057</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2212184840481725</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.003449603918871</v>
+        <v>-4.864554658553558</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.962575729695379</v>
+        <v>1.018133707841504</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2212184840481725</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.985735917041006</v>
+        <v>-4.846840971675692</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9703397883638651</v>
+        <v>1.02589776650999</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2243998129450893</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.876931031561279</v>
+        <v>-4.738036086195965</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.010859813775749</v>
+        <v>1.066417791921874</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2243998129450893</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.656910233524268</v>
+        <v>-4.518015288158955</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.100447170001168</v>
+        <v>1.156005148147293</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3656196580130696</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.524042544460991</v>
+        <v>-4.385147599095677</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169488428428302</v>
+        <v>1.225046406574427</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3656196580130696</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.403869461096492</v>
+        <v>-4.264974515731178</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.218703506214404</v>
+        <v>1.274261484360528</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4857927413775685</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268616099766515</v>
+        <v>-4.129721154401201</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282892953307834</v>
+        <v>1.338450931453959</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6210461027075456</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328490927124207</v>
+        <v>-4.189595981758893</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.244980513766183</v>
+        <v>1.300538491912308</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5611712753498534</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.20867069621337</v>
+        <v>-4.069775750848057</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.308197775364726</v>
+        <v>1.363755753510851</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5611712753498534</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.211140402675176</v>
+        <v>-4.072245457309863</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214854092102446</v>
+        <v>1.27041207024857</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5587015688880472</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.279510588999186</v>
+        <v>-4.140615643633873</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.106767879058143</v>
+        <v>1.162325857204268</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5679772679242622</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.293298641846233</v>
+        <v>-4.154403696480919</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.091689366551216</v>
+        <v>1.14724734469734</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5679772679242622</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.348818717738823</v>
+        <v>-4.209923772373509</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.206512172886382</v>
+        <v>1.262070151032507</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5679772679242622</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.173344457946353</v>
+        <v>-4.034449512581039</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.281269108795158</v>
+        <v>1.336827086941283</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5679772679242622</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.284280710587602</v>
+        <v>-4.145385765222288</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.212636636499865</v>
+        <v>1.26819461464599</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5679772679242622</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.25061716511532</v>
+        <v>-4.111722219750006</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.154640368090228</v>
+        <v>1.210198346236353</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6016408133965441</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.190764545911597</v>
+        <v>-4.051869600546283</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.18875380220385</v>
+        <v>1.244311780349974</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6016408133965441</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.104521082885219</v>
+        <v>-3.965626137519905</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.218197457988261</v>
+        <v>1.273755436134386</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6016408133965441</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.149827902284199</v>
+        <v>-4.010932956918885</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.191850505673195</v>
+        <v>1.247408483819319</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5608306503873133</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.1788610069865</v>
+        <v>-4.039966061621186</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.180789136825376</v>
+        <v>1.2363471149715</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5608306503873133</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.08605052553564</v>
+        <v>-3.947155580170327</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.147186021297085</v>
+        <v>1.20274399944321</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6536411318381726</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.130439994865068</v>
+        <v>-3.991545049499754</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.131303709489915</v>
+        <v>1.18686168763604</v>
       </c>
       <c r="F1947" t="n">
         <v>0.609251662508745</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.24698159997041</v>
+        <v>-4.108086654605097</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.079762775959501</v>
+        <v>1.135320754105625</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4927100574034022</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.134604598787737</v>
+        <v>-4.148010749187669</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.130204872263237</v>
+        <v>1.124842412103264</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4927100574034022</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.16238499668909</v>
+        <v>-4.175791147089022</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.130589914871236</v>
+        <v>1.125227454711262</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4649296595020492</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705329</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.280765669419228</v>
+        <v>-4.294171819819161</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9215933657798334</v>
+        <v>0.9162309056198596</v>
       </c>
       <c r="F1951" t="n">
         <v>0.397711807351073</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.389379747862559</v>
+        <v>-4.402785898262492</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9982973951217065</v>
+        <v>0.9929349349617329</v>
       </c>
       <c r="F1952" t="n">
         <v>0.397711807351073</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.353970709614416</v>
+        <v>-4.367376860014349</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.026974036523287</v>
+        <v>1.021611576363313</v>
       </c>
       <c r="F1953" t="n">
         <v>0.397711807351073</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.315587047056265</v>
+        <v>-4.328993197456198</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.039746942888916</v>
+        <v>1.034384482728942</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4360954699092242</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.138470717021099</v>
+        <v>-4.151876867421032</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.107322503748284</v>
+        <v>1.101960043588311</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4360954699092242</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793907</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.183562961854645</v>
+        <v>-4.196969112254577</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.089968997576779</v>
+        <v>1.084606537416805</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3741994267398344</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.004187540615877</v>
+        <v>-4.01759369101581</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.1555061413787</v>
+        <v>1.150143681218727</v>
       </c>
       <c r="F1957" t="n">
         <v>0.530976184910553</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.049201754136483</v>
+        <v>-4.062607904536415</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.118307911302048</v>
+        <v>1.112945451142074</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5006272895959484</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.316206264408918</v>
+        <v>-4.32961241480885</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.01719766953202</v>
+        <v>1.011835209372046</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3062642515529998</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.417404045846091</v>
+        <v>-4.430810196246023</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.975922478853652</v>
+        <v>0.9705600186936783</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2378554380076806</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.410893079231778</v>
+        <v>-4.424299229631711</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9761268270536938</v>
+        <v>0.97076436689372</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2378554380076806</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.391854951524481</v>
+        <v>-4.405261101924413</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9802667973448576</v>
+        <v>0.974904337184884</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1796718266764861</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.444370753799301</v>
+        <v>-4.457776904199234</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.07855487806912</v>
+        <v>1.073192417909146</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1796718266764861</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.458237515133219</v>
+        <v>-4.471643665533152</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.073841502521686</v>
+        <v>1.068479042361713</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1418139099426631</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.413433343593289</v>
+        <v>-4.426839493993222</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.097771701534584</v>
+        <v>1.09240924137461</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1418139099426631</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.265690373358287</v>
+        <v>-4.279096523758219</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.054819110905785</v>
+        <v>1.049456650745811</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3096212671775463</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.349511594632985</v>
+        <v>-4.362917745032918</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.024084243927386</v>
+        <v>1.018721783767413</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3096212671775463</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.343358888580201</v>
+        <v>-4.356765038980133</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.027207674740158</v>
+        <v>1.021845214580185</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3157739732303306</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.360168186730703</v>
+        <v>-4.373574337130635</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.019564432220068</v>
+        <v>1.014201972060094</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2989646750798289</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.29787018795458</v>
+        <v>-4.311276338354513</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.110819185527337</v>
+        <v>1.105456725367364</v>
       </c>
       <c r="F1970" t="n">
         <v>0.344258939354271</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.096079990289422</v>
+        <v>-4.109486140689355</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9938272663075278</v>
+        <v>0.9884648061475541</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5422771315234254</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.146966702975617</v>
+        <v>-4.16037285337555</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.043762813555225</v>
+        <v>1.038400353395251</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4913904188372309</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.06035596032581</v>
+        <v>-4.073762110725743</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.093034846731191</v>
+        <v>1.087672386571218</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5700161500423891</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.120565258331095</v>
+        <v>-4.133971408731028</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.067487108353749</v>
+        <v>1.062124648193776</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5098068520371046</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.044143211899168</v>
+        <v>-4.057549362299101</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.096547544966449</v>
+        <v>1.091185084806475</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5098068520371046</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.9997700802606</v>
+        <v>-4.013176230660532</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.114159665057312</v>
+        <v>1.108797204897338</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5541799836756732</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.022250431119485</v>
+        <v>-4.035656581519417</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.099561318852349</v>
+        <v>1.094198858692375</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5541799836756732</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.974594700558429</v>
+        <v>-3.988000850958361</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.125005368104576</v>
+        <v>1.119642907944602</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6018357142367289</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.874076542059674</v>
+        <v>-3.887482692459606</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.170105004878802</v>
+        <v>1.164742544718829</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7023538727354834</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.858171212627322</v>
+        <v>-3.871577363027254</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.163221809127616</v>
+        <v>1.157859348967642</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6232412120262445</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.813332811018924</v>
+        <v>-3.826738961418856</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.185254872381603</v>
+        <v>1.17989241222163</v>
       </c>
       <c r="F1981" t="n">
         <v>0.627784644971114</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917055</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.832831267260932</v>
+        <v>-3.846237417660864</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.181616429515878</v>
+        <v>1.176253969355904</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5797000036912097</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405963</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.788628430175031</v>
+        <v>-3.802034580574964</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.205177166878076</v>
+        <v>1.199814706718102</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6239028407771101</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265648</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.825607457838474</v>
+        <v>-3.839013608238407</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.188795556281946</v>
+        <v>1.183433096121972</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6608767425684406</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.667316040299202</v>
+        <v>-3.680722190699135</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.303359888480694</v>
+        <v>1.297997428320721</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6608767425684406</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.459674036664726</v>
+        <v>-3.473080187064658</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.384857394528738</v>
+        <v>1.379494934368764</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8685187462029168</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.408641943942198</v>
+        <v>-3.42204809434213</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.400218459856019</v>
+        <v>1.394855999696045</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9195508389254448</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.343417762814992</v>
+        <v>-3.356823913214924</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.443495536399606</v>
+        <v>1.438133076239633</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9847750200526504</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.305990742743858</v>
+        <v>-3.319396893143791</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.45442731672734</v>
+        <v>1.449064856567367</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9900265580818322</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.326102398778567</v>
+        <v>-3.339508549178499</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.447639446644697</v>
+        <v>1.442276986484724</v>
       </c>
       <c r="F1990" t="n">
         <v>1.001053903079251</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.272357584351362</v>
+        <v>-3.285763734751294</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.62969514343679</v>
+        <v>1.624332683276816</v>
       </c>
       <c r="F1991" t="n">
         <v>1.011117212519713</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.197575323326349</v>
+        <v>-3.210981473726282</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.779720957064612</v>
+        <v>1.774358496904639</v>
       </c>
       <c r="F1992" t="n">
         <v>1.085899473544726</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.171491239062541</v>
+        <v>-3.184897389462474</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.781862566783994</v>
+        <v>1.776500106624021</v>
       </c>
       <c r="F1993" t="n">
         <v>1.085899473544726</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.083613325953421</v>
+        <v>-3.097019476353353</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.815206927611422</v>
+        <v>1.809844467451448</v>
       </c>
       <c r="F1994" t="n">
         <v>1.201825115968077</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.074720864560137</v>
+        <v>-3.08812701496007</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.836318317895527</v>
+        <v>1.830955857735553</v>
       </c>
       <c r="F1995" t="n">
         <v>1.201825115968077</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.243196981530015</v>
+        <v>-3.256603131929948</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.76078291851216</v>
+        <v>1.755420458352186</v>
       </c>
       <c r="F1996" t="n">
         <v>1.173877280251497</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.545397452668432</v>
+        <v>-2.558803603068364</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.021172427244655</v>
+        <v>2.015809967084681</v>
       </c>
       <c r="F1997" t="n">
         <v>1.103529220881086</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.522676348985279</v>
+        <v>-2.536082499385212</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.02092489121482</v>
+        <v>2.015562431054847</v>
       </c>
       <c r="F1998" t="n">
         <v>1.103529220881086</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.651878162279322</v>
+        <v>-2.665284312679254</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.128150291748372</v>
+        <v>2.122787831588399</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9743274075870436</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.806659169057578</v>
+        <v>-2.82006531945751</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.103315711530716</v>
+        <v>2.097953251370743</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9409597335325675</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.799604478842404</v>
+        <v>-2.813010629242336</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.102812943606331</v>
+        <v>2.097450483446358</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9480144237477413</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.772653254515916</v>
+        <v>-2.786059404915848</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.123599586981668</v>
+        <v>2.118237126821694</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9628947697754604</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.908606262572232</v>
+        <v>-2.922012412972165</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.253321515904101</v>
+        <v>2.247959055744127</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9628947697754604</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.931014380377104</v>
+        <v>-2.944420530777037</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.236474963685145</v>
+        <v>2.231112503525172</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9628947697754604</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.959238615954705</v>
+        <v>-2.972644766354637</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.227239269003743</v>
+        <v>2.221876808843769</v>
       </c>
       <c r="F2005" t="n">
         <v>0.980871522226769</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.968679541843235</v>
+        <v>-2.982085692243167</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.279716616370178</v>
+        <v>2.274354156210205</v>
       </c>
       <c r="F2006" t="n">
         <v>1.103298639770161</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.020953149178876</v>
+        <v>-3.034359299578808</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.261698267981222</v>
+        <v>2.256335807821249</v>
       </c>
       <c r="F2007" t="n">
         <v>1.051025032434519</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.097283126779782</v>
+        <v>-3.110689277179714</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.229278089834635</v>
+        <v>2.223915629674662</v>
       </c>
       <c r="F2008" t="n">
         <v>1.051025032434519</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.299536847104135</v>
+        <v>-3.312942997504067</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.143196831307756</v>
+        <v>2.137834371147783</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8487713121101657</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.46110527263139</v>
+        <v>-3.474511423031323</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.077003471307006</v>
+        <v>2.071641011147033</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7219883883122863</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.593406564728943</v>
+        <v>-3.606812715128876</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.037156361333904</v>
+        <v>2.03179390117393</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7219883883122863</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.779274875568174</v>
+        <v>-3.792681025968106</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.954814233781152</v>
+        <v>1.949451773621178</v>
       </c>
       <c r="F2012" t="n">
         <v>0.5634227949923386</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.807175662677647</v>
+        <v>-3.820581813077579</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.942177960064364</v>
+        <v>1.936815499904391</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5288258708494038</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.92970176538054</v>
+        <v>-3.943107915780473</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.889931962960406</v>
+        <v>1.884569502800432</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4062997681465099</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.160216261566129</v>
+        <v>-4.173622411966061</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.864432124076674</v>
+        <v>1.8590696639167</v>
       </c>
       <c r="F2015" t="n">
         <v>0.1757852719609212</v>
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.491187423183629</v>
+        <v>-4.430343229960885</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.872355378431521</v>
+        <v>1.896693055720618</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.08432196263373504</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.719779949598961</v>
+        <v>3.709609190708984</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.645173840959769</v>
+        <v>-4.584329647737025</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.879741080466705</v>
+        <v>1.904078757755802</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.08432196263373504</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.788760218744601</v>
+        <v>3.778589459854624</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.594651937132103</v>
+        <v>-4.533807743909359</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.886001044117892</v>
+        <v>1.910338721406989</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.08432196263373504</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.774811420864722</v>
+        <v>3.764640661974745</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.847127091139828</v>
+        <v>-4.786282897917084</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.796881471570216</v>
+        <v>1.821219148859313</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.08432196263373504</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.786681909920136</v>
+        <v>3.776511151030159</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.14002284761924</v>
+        <v>-5.079178654396496</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.680933703497395</v>
+        <v>1.705271380786492</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.08432196263373504</v>
+        <v>0.06737069781710636</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.78789244443908</v>
+        <v>3.777721685549102</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.297566919348681</v>
+        <v>-5.236722726125937</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.62203781703294</v>
+        <v>1.646375494322037</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.01742015749346054</v>
+        <v>0.0004688926768318669</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.751873103582236</v>
+        <v>3.741702344692259</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.575531314931955</v>
+        <v>-5.514687121709211</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.50592991153582</v>
+        <v>1.530267588824917</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.07219957679202371</v>
+        <v>-0.08915084160865239</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.693179115747135</v>
+        <v>3.683008356857158</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.692499007570846</v>
+        <v>-5.631654814348102</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.621346891179308</v>
+        <v>1.645684568468404</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.07219957679202371</v>
+        <v>-0.08915084160865239</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.855383172446179</v>
+        <v>3.845212413556202</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.777216949791799</v>
+        <v>-5.716372756569055</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.58230635225474</v>
+        <v>1.606644029543837</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1573156057200701</v>
+        <v>-0.1742668705366988</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.799160193053166</v>
+        <v>3.788989434163188</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.859151768060682</v>
+        <v>-5.798307574837938</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.559761842515679</v>
+        <v>1.584099519804775</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1672503513071503</v>
+        <v>-0.1842016161237789</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.803428763269409</v>
+        <v>3.793258004379431</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.96112789030909</v>
+        <v>-5.900283697086346</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.527897032072218</v>
+        <v>1.552234709361314</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2692264735555578</v>
+        <v>-0.2861777383721865</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.751168728376267</v>
+        <v>3.740997969486289</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.851121606831868</v>
+        <v>-5.790277413609124</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.564052432707282</v>
+        <v>1.588390109996379</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2460219016382826</v>
+        <v>-0.2629731664549113</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.757244358770807</v>
+        <v>3.74707359988083</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.708062031090943</v>
+        <v>-5.647217837868199</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.625526273725626</v>
+        <v>1.649863951014723</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2380084750483034</v>
+        <v>-0.254959739864932</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.766302425446769</v>
+        <v>3.756131666556792</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.406615305619106</v>
+        <v>-5.345771112396362</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.753365846796897</v>
+        <v>1.777703524085994</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.0634382504235339</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.954431343612407</v>
+        <v>3.94426058472243</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.431205549854289</v>
+        <v>-5.370361356631546</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.744500926855534</v>
+        <v>1.768838604144631</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.0634382504235339</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.955402521365118</v>
+        <v>3.945231762475141</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.380167173847769</v>
+        <v>-5.319322980625025</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.765759181637897</v>
+        <v>1.790096858926994</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.0634382504235339</v>
+        <v>0.04648698560690523</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.956245425744873</v>
+        <v>3.946074666854896</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.339027878981138</v>
+        <v>-5.278183685758394</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.801252998458695</v>
+        <v>1.825590675747792</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1045775452901647</v>
+        <v>0.08762628047353604</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.999967101538997</v>
+        <v>3.98979634264902</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.228421738901536</v>
+        <v>-5.167577545678792</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.661679450614471</v>
+        <v>1.686017127903567</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2151836853697667</v>
+        <v>0.1982324205531381</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.882514781710693</v>
+        <v>3.872344022820716</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.359002473432379</v>
+        <v>-5.298158280209635</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.612949200876097</v>
+        <v>1.637286878165194</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.08460295083892422</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.807668385066151</v>
+        <v>3.797497626176173</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.194506139241417</v>
+        <v>-5.133661946018673</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.663174553628564</v>
+        <v>1.687512230917661</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.08460295083892422</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.792095204142234</v>
+        <v>3.781924445252256</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.221876071925849</v>
+        <v>-5.161031878703105</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.651414290991221</v>
+        <v>1.675751968280318</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.08460295083892422</v>
+        <v>0.06765168602229554</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.791282914578663</v>
+        <v>3.781112155688686</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.232261266815739</v>
+        <v>-5.171417073592995</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.657128992160338</v>
+        <v>1.681466669449435</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.0742177559490349</v>
+        <v>0.05726649113240623</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.794920576769802</v>
+        <v>3.784749817879825</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.250849425537964</v>
+        <v>-5.19000523231522</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.720530734447873</v>
+        <v>1.74486841173697</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.05562959722680955</v>
+        <v>0.03867833241018087</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.854604687312892</v>
+        <v>3.844433928422915</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.251147972234</v>
+        <v>-5.190303779011256</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.717280326587757</v>
+        <v>1.741618003876854</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.05562959722680955</v>
+        <v>0.03867833241018087</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.851473698131191</v>
+        <v>3.841302939241213</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.150324838543572</v>
+        <v>-5.089480645320828</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.76214047500332</v>
+        <v>1.786478152292417</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.06809381271116338</v>
+        <v>0.05114254789453471</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.863483122361194</v>
+        <v>3.853312363471217</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.959543477791165</v>
+        <v>-4.898699284568421</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.838582272782826</v>
+        <v>1.862919950071923</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2588751734635708</v>
+        <v>0.2419239086469421</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.978081192291182</v>
+        <v>3.967910433401205</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.941026623749345</v>
+        <v>-4.880182430526601</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.825825860137151</v>
+        <v>1.850163537426248</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.271805302888779</v>
+        <v>0.2548540380721503</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.965676115683904</v>
+        <v>3.955505356793926</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.915833439248027</v>
+        <v>-4.854989246025283</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.870870070549736</v>
+        <v>1.895207747838833</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2969984873900973</v>
+        <v>0.2800472225734686</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.015758962996753</v>
+        <v>4.005588204106775</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.903779312335064</v>
+        <v>-4.84293511911232</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.869378289216359</v>
+        <v>1.893715966505456</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3090526143030601</v>
+        <v>0.2921013494864315</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.016678007045968</v>
+        <v>4.006507248155991</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.910402559025422</v>
+        <v>-4.849558365802678</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.868609620724352</v>
+        <v>1.892947298013449</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.3024293676127018</v>
+        <v>0.2854781027960731</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.014584689215889</v>
+        <v>4.004413930325912</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.807521969496829</v>
+        <v>-4.746677776274085</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.922612882413671</v>
+        <v>1.946950559702768</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4053099571412947</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.089164068810927</v>
+        <v>4.07899330992095</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.830964008676916</v>
+        <v>-4.770119815454172</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.933438736915231</v>
+        <v>1.957776414204328</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4053099571412947</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.109366738984521</v>
+        <v>4.099195980094544</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.849036516968527</v>
+        <v>-4.788192323745784</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.926209733598586</v>
+        <v>1.950547410887683</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4053099571412947</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.109366738984521</v>
+        <v>4.099195980094544</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.08021031084516</v>
+        <v>-5.019366117622416</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.7939921296414</v>
+        <v>1.818329806930497</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4053099571412947</v>
+        <v>0.388358692324666</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.069618652577988</v>
+        <v>4.059447893688011</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.048924290304704</v>
+        <v>-4.98808009708196</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.813529156854522</v>
+        <v>1.837866834143619</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4365959776817501</v>
+        <v>0.4196447128651214</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.095412883899201</v>
+        <v>4.085242125009224</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677819</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.037562732469447</v>
+        <v>-4.976718539246703</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.917244779561529</v>
+        <v>1.941582456850626</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.447957535517007</v>
+        <v>0.4310062707003783</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.201400818173259</v>
+        <v>4.191230059283282</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.774852822206141</v>
+        <v>3.438360541292774</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.918235110616684</v>
+        <v>3.928285974306183</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.975895876008487</v>
+        <v>-4.812393122219597</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.927520335899542</v>
+        <v>2.002972301104596</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.447957535517007</v>
+        <v>0.4310062707003783</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.187009631926888</v>
+        <v>4.18688973672641</v>
       </c>
     </row>
   </sheetData>
